--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -144,15 +144,12 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -536,7 +533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fecha del informe: 17/10/2026</t>
+          <t>Fecha del informe: 19/10/2026</t>
         </is>
       </c>
     </row>
@@ -560,7 +557,7 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Base de datos relacional de ejemplo (200 leads) construida para la sección 7 del plan de marketing del proyecto ibis Styles Armenia. Los datos de personas (nombres, correos, celulares) son 100 % ficticios: se inventaron para demostrar el funcionamiento del CRM. El detalle de la muestra y su justificación están en NOTA_METODOLOGICA_Muestra_CRM.md.</t>
+          <t>Base de datos relacional de ejemplo construida para la sección 7 del plan de marketing del proyecto ibis Styles Armenia. Los datos de personas (nombres, correos, celulares) son 100 % ficticios: se inventaron para demostrar el funcionamiento del CRM. El detalle de la muestra y su justificación están en NOTA_METODOLOGICA_Muestra_CRM.md.</t>
         </is>
       </c>
     </row>
@@ -611,7 +608,7 @@
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>200 leads | 1.156 interacciones | 32 leads calientes | 3 ventas (1.148 COP millones) | 2 opciones en curso | conversión 1,5 % (igual a la meta) | 2 clientes con baja y autorización revocada respetada.</t>
+          <t>Consulte la hoja KPIs para el detalle actualizado.</t>
         </is>
       </c>
     </row>
@@ -641,7 +638,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Operaciones de compraventa (5)</t>
+          <t>Operaciones de compraventa</t>
         </is>
       </c>
     </row>
@@ -652,7 +649,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>id_operacion</t>
@@ -690,165 +687,165 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Héctor Duque Herrera</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Promesa</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>2027-03-29</t>
         </is>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>374</v>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Piso 4 HAB-07</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Andrés Giraldo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Ricardo Montoya Castaño</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Opción</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>2027-04-28</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="10" t="n">
         <v>374</v>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Piso 7 HAB-02</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Andrés Giraldo</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Liliana Cardona Orozco</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Promesa</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>2027-05-03</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>395</v>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>Piso 4 HAB-08</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Carolina Mejía</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Fernando Quintero Rojas</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Promesa</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>2027-08-12</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="10" t="n">
         <v>379</v>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Piso 12 HAB-02</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Andrés Giraldo</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Viviana Zapata Jiménez</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Opción</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>2027-08-26</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>402</v>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>Piso 13 HAB-09</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Carolina Mejía</t>
         </is>
@@ -892,7 +889,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Alerta</t>
@@ -915,76 +912,76 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>No contactar (baja/revocada)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Juan Salazar Cardona</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>2027-03-25</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>No contactar (baja/revocada)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="10" t="n">
         <v>186</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Ricardo Carlos Vargas Restrepo</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>2027-10-10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Leads calificados sin asesor</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Revisar asignación en el CRM</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Interacciones con fecha inválida</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Ninguna: todas posteriores al registro</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr"/>
+      <c r="D8" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1021,11 +1018,11 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Los valores corresponden a la base de ejemplo: una muestra; las metas son del plan a 12 meses.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
+          <t>Los valores corresponden a la base: una muestra; las metas son del plan a 12 meses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>KPI</t>
@@ -1041,7 +1038,7 @@
           <t>Meta del plan</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -1053,76 +1050,76 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Leads en la base</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Por debajo de la meta (muestra)</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Base de ejemplo (muestra para el ejercicio); meta anual del plan: 6.000</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Suites vendidas</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Por debajo de la meta (muestra)</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Muestra de ejemplo; meta del plan: 90 suites en 12 meses</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Conversión lead a venta</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>0.015</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>0.015</v>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Cumple</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Alineada con la meta del plan (1,5%)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Leads por referidos</t>
         </is>
@@ -1130,61 +1127,61 @@
       <c r="B8" s="13" t="n">
         <v>0.095</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Por debajo de la meta (muestra)</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>9,5% vs meta 10%: muy cerca</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Clientes con autorización vigente o revocada documentada</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Cumple</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>100% de clientes con consentimiento documentado (Ley 1581)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Valor vendido (COP millones)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="10" t="n">
         <v>1148</v>
       </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>3 promesas de compraventa + 2 opciones en curso</t>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Promesas/escrituras + opciones en curso</t>
         </is>
       </c>
     </row>
@@ -1223,11 +1220,11 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Meta del plan: 1.000 leads/mes (6.000 en 12 meses). La base es una muestra de 200 leads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
+          <t>Meta del plan: 1.000 leads/mes (6.000 en 12 meses). La base es una muestra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>orden</t>
@@ -1255,30 +1252,30 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="10" t="n">
         <v>80</v>
       </c>
       <c r="D6" s="13" t="n">
@@ -1289,34 +1286,34 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="11" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="10" t="n">
         <v>20</v>
       </c>
       <c r="D8" s="13" t="n">
@@ -1327,34 +1324,34 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="11" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="13" t="n">
@@ -1379,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1399,11 +1396,11 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Conversión = ventas / leads del canal. En la muestra, las 3 ventas llegaron por Digital.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
+          <t>Conversión = ventas / leads del canal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>canal</t>
@@ -1431,80 +1428,97 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Digital</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="8" t="n">
         <v>114</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="14" t="n">
         <v>0.0263</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Eventos</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Referidos</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Alianzas y relaciones públicas</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="15" t="n">
         <v>0</v>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1546,7 +1560,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>segmento</t>
@@ -1579,112 +1593,112 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>A. Profesional o empresario urbano</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>395</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>B. Inversionista regional</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>C. Colombianos en el exterior</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>379</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>D. Comprador multi-suite</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>E. Planeación patrimonial</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>374</v>
       </c>
     </row>
@@ -1729,7 +1743,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>campana</t>
@@ -1767,127 +1781,127 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Fase 0. Preparación</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="8" t="n">
         <v>160</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>26.7</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>C1. Lanzamiento</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="10" t="n">
         <v>330</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="10" t="n">
         <v>76</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="10" t="n">
         <v>14.3</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>C2. Conoce tu suite</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="8" t="n">
         <v>290</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>1200</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>11.6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>C3. Colombia te espera</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="10" t="n">
         <v>1000</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="10" t="n">
         <v>10.7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>C4. Últimos pisos</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="8" t="n">
         <v>220</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>1400</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1918,7 +1932,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Inventario de 180 suites por estado</t>
+          <t>Inventario de suites por estado</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1943,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>estado</t>
@@ -1952,50 +1966,50 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Disponible</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="8" t="n">
         <v>175</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>69623.5</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>397.8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Separada</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="10" t="n">
         <v>776</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="10" t="n">
         <v>388</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Vendida</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>1148</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>382.7</v>
       </c>
     </row>
@@ -2036,7 +2050,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>clasificacion</t>
@@ -2054,25 +2068,25 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="11" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Caliente</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="10" t="n">
         <v>32</v>
       </c>
       <c r="C6" s="13" t="n">
@@ -2080,25 +2094,25 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Frío</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="11" t="n">
         <v>0.385</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Tibio</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="10" t="n">
         <v>89</v>
       </c>
       <c r="C8" s="13" t="n">
@@ -2133,7 +2147,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Leads calientes: llamar primero (top 32)</t>
+          <t>Leads calientes: llamar primero</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2158,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>cliente</t>
@@ -2172,800 +2186,800 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Daniel Gómez Salazar</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>125</v>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>2027-03-18</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Néstor Ricardo Jiménez Valencia</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Camila Henao Salazar</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Ricardo Montoya Castaño</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Daniel Mejía Torres</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Marcela Mónica Gómez Martínez</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>2027-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Viviana Montoya Cardona</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>2027-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Fernando Quintero Rojas</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>2027-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Viviana Zapata Jiménez</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>2027-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Julián Bedoya Cardona</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Héctor Duque Herrera</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>2027-03-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Néstor Ricardo Jiménez Valencia</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="D15" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>2027-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Laura Restrepo Jiménez</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Iván Duque Ramírez</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>2027-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Esteban Juan Betancur Montoya</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Gustavo Salazar Salazar</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Camilo Orozco Patiño</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>2027-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Claudia Moreno Betancur</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>2027-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Diana Liliana Gil Londoño</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Sebastián Alejandro Salazar Jiménez</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>105</v>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>2027-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Camila Henao Salazar</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="D23" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Andrea Acosta Orozco</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>2027-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Liliana Cardona Orozco</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>2027-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Juan Rojas Restrepo</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Esteban Restrepo Giraldo</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>2027-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Andrés Valencia Bedoya</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Ricardo Camilo Ruiz Cárdenas</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>2027-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Carolina Viviana Correa Ríos</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>2027-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Diego Jorge Cárdenas Londoño</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>2027-03-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Ricardo Montoya Castaño</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="D31" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>2027-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Diego Franco Duque</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Daniel Martínez Patiño</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Felipe Felipe Patiño Martínez</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Opción o separación</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>105</v>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>2027-04-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Daniel Mejía Torres</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>2027-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Marcela Mónica Gómez Martínez</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Reunión o visita</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>105</v>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>2027-05-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Viviana Montoya Cardona</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="D34" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Héctor Martínez Duque</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Reunión o visita</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>2027-07-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Fernando Quintero Rojas</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Venta</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>105</v>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>2027-08-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Viviana Zapata Jiménez</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Opción o separación</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>2027-08-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Julián Bedoya Cardona</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Reunión o visita</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>105</v>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>2027-10-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Laura Restrepo Jiménez</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Reunión o visita</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>2027-04-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Iván Duque Ramírez</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Reunión o visita</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>2027-07-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Esteban Juan Betancur Montoya</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Reunión o visita</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>2027-01-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Gustavo Salazar Salazar</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Paola Diana Martínez Salazar</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Reunión o visita</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>95</v>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>2027-03-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Camilo Orozco Patiño</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Reunión o visita</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>2027-06-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Claudia Moreno Betancur</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Reunión o visita</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>95</v>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>2027-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Diana Liliana Gil Londoño</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Reunión o visita</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>2027-10-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Sebastián Alejandro Salazar Jiménez</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>2027-03-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Andrea Acosta Orozco</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Oportunidad (SQL)</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>2027-03-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Liliana Cardona Orozco</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Venta</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>2027-04-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Juan Rojas Restrepo</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Oportunidad (SQL)</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Esteban Restrepo Giraldo</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Oportunidad (SQL)</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>2027-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Andrés Valencia Bedoya</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>Oportunidad (SQL)</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>2027-04-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Ricardo Camilo Ruiz Cárdenas</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Oportunidad (SQL)</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>2027-08-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Carolina Viviana Correa Ríos</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>Oportunidad (SQL)</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>2027-08-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>Diego Jorge Cárdenas Londoño</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Reunión o visita</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>2027-10-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Diego Franco Duque</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Oportunidad (SQL)</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>2026-12-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>Daniel Martínez Patiño</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Oportunidad (SQL)</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>2027-05-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>Felipe Felipe Patiño Martínez</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Reunión o visita</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>2027-10-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>Héctor Martínez Duque</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Lead calificado (MQL)</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="n">
+      <c r="D36" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>2026-11-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Paola Diana Martínez Salazar</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>Oportunidad (SQL)</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>2027-09-02</t>
         </is>

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -148,8 +148,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -866,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -954,34 +954,4146 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Leads calificados sin asesor</t>
+          <t>No contactar (baja/revocada)</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Revisar asignación en el CRM</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr"/>
+          <t>Andres Rojas</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>212</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Hector Martinez</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>219</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Moreno</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>220</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Carolina Martinez</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>226</v>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Sofia Morales</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>236</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Camila Vega</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>239</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Miguel Suarez</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>241</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Paula Jimenez</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>269</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Lina Cruz</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>272</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>David Romero</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>274</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Lina Ortiz</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>278</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Diego Romero</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>283</v>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Sofia Jimenez</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>288</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Mariana Ruiz</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Juan Ortiz</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>315</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Lina Lopez</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>322</v>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Andres Suarez</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>323</v>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Natalia Flores</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>328</v>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Juan Mendoza</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>338</v>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Maria Flores</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>341</v>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Moreno</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>346</v>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Carlos Moreno</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>351</v>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Luis Torres</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>352</v>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Paula Gutierrez</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>367</v>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Gabriela Mendoza</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>368</v>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Gabriela Ortiz</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>369</v>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Juliana Diaz</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>371</v>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Mariana Romero</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>393</v>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Paula Rojas</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>402</v>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Sofia Garcia</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>407</v>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Sebastian Suarez</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>409</v>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Ricardo Martinez</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>414</v>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Sebastian Silva</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>415</v>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Miguel Cruz</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>419</v>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Paula Morales</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n">
+        <v>420</v>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Jorge Vargas</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>426</v>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Diana Reyes</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>428</v>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Natalia Cruz</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>432</v>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Ricardo Diaz</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>435</v>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Daniela Romero</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>441</v>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Daniela Rios</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>443</v>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Felipe Vega</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>449</v>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Juliana Pena</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>455</v>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Paula Rojas</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>456</v>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Camila Hernandez</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n">
+        <v>465</v>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Lina Moreno</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>466</v>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Camila Alvarez</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="n">
+        <v>469</v>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Natalia Vargas</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>472</v>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Jorge Lopez</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n">
+        <v>515</v>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Cesar Ramirez</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>517</v>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Camila Gutierrez</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n">
+        <v>521</v>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Andres Flores</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>526</v>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Cesar Moreno</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n">
+        <v>529</v>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>Maria Hernandez</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>536</v>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Laura Vega</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n">
+        <v>539</v>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Luis Ramirez</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>551</v>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Alejandra Rojas</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>552</v>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Daniela Castro</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>556</v>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Sofia Torres</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="n">
+        <v>557</v>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Lina Rojas</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>564</v>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Flores</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="n">
+        <v>577</v>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Daniela Romero</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>591</v>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>Diego Romero</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="n">
+        <v>593</v>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Mariana Hernandez</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>594</v>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Valentina Garcia</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n">
+        <v>615</v>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Sofia Mendoza</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>629</v>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Juliana Lopez</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="n">
+        <v>654</v>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Diego Cruz</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>655</v>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Laura Mendoza</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="n">
+        <v>659</v>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Sofia Jimenez</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>682</v>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Sofia Martinez</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="n">
+        <v>684</v>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>David Gutierrez</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>688</v>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>Natalia Acosta</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="n">
+        <v>696</v>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Hector Gutierrez</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>699</v>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Vargas</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="n">
+        <v>709</v>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Miguel Vargas</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n">
+        <v>714</v>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>Fernando Jimenez</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="n">
+        <v>721</v>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Juliana Jimenez</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n">
+        <v>731</v>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>Diego Diaz</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="n">
+        <v>738</v>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Daniela Hernandez</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n">
+        <v>740</v>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>Paula Cruz</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="n">
+        <v>741</v>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Felipe Silva</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n">
+        <v>758</v>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>Andres Ruiz</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="n">
+        <v>764</v>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Natalia Mendoza</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n">
+        <v>769</v>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>Diego Castro</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="n">
+        <v>774</v>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Oscar Vega</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n">
+        <v>775</v>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>David Suarez</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="n">
+        <v>776</v>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>Hector Flores</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="n">
+        <v>785</v>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>Juan Vega</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="n">
+        <v>799</v>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>Alejandra Acosta</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>Ricardo Romero</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="n">
+        <v>808</v>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>Sebastian Silva</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="n">
+        <v>811</v>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>Carolina Lopez</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="n">
+        <v>817</v>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>Daniela Gomez</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="n">
+        <v>818</v>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>Felipe Vargas</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="n">
+        <v>819</v>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>Hector Romero</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="n">
+        <v>838</v>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>Miguel Suarez</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="n">
+        <v>845</v>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>Camila Reyes</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="n">
+        <v>848</v>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>Camila Flores</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="n">
+        <v>854</v>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>Paula Reyes</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="n">
+        <v>857</v>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>Miguel Rojas</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B108" s="10" t="n">
+        <v>858</v>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>Mariana Morales</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="n">
+        <v>861</v>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>Gabriela Garcia</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B110" s="10" t="n">
+        <v>869</v>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>Lina Mendoza</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="n">
+        <v>873</v>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>Oscar Martinez</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B112" s="10" t="n">
+        <v>874</v>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>Maria Romero</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="n">
+        <v>899</v>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>Jorge Suarez</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B114" s="10" t="n">
+        <v>904</v>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>Sofia Flores</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="n">
+        <v>908</v>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>Felipe Lopez</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="n">
+        <v>918</v>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>Fernando Ramirez</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="n">
+        <v>922</v>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>Sofia Suarez</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="n">
+        <v>923</v>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>Lina Vega</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="n">
+        <v>946</v>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>Alejandra Lopez</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="n">
+        <v>949</v>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>Sofia Hernandez</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="n">
+        <v>952</v>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>Camila Martinez</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="n">
+        <v>954</v>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>Paula Mendoza</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="n">
+        <v>957</v>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>Maria Flores</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="n">
+        <v>959</v>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>Diego Ortiz</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="n">
+        <v>967</v>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>Luis Vega</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="n">
+        <v>969</v>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>Gabriela Torres</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="n">
+        <v>972</v>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>Laura Ruiz</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="n">
+        <v>974</v>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>David Gomez</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="n">
+        <v>976</v>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>Cesar Castro</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="n">
+        <v>979</v>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>Daniela Suarez</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="n">
+        <v>989</v>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>Lina Suarez</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="n">
+        <v>991</v>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>Juan Castro</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="n">
+        <v>1004</v>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>Sofia Suarez</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="n">
+        <v>1005</v>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>Juan Morales</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="n">
+        <v>1009</v>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Jimenez</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="n">
+        <v>1024</v>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>Luis Moreno</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="n">
+        <v>1037</v>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>Luis Rodriguez</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="n">
+        <v>1040</v>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>Hector Mendoza</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="n">
+        <v>1059</v>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>Diana Ortiz</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="n">
+        <v>1061</v>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>Fernando Moreno</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="n">
+        <v>1081</v>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>Maria Flores</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B142" s="10" t="n">
+        <v>1087</v>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>Carlos Acosta</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="n">
+        <v>1097</v>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>Miguel Morales</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="n">
+        <v>1099</v>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>Hector Gomez</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="n">
+        <v>1107</v>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>Juliana Vargas</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B146" s="10" t="n">
+        <v>1125</v>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>David Vega</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="n">
+        <v>1131</v>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>Daniela Vargas</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B148" s="10" t="n">
+        <v>1139</v>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="n">
+        <v>1143</v>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>Ricardo Castro</t>
+        </is>
+      </c>
+      <c r="D149" s="8" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B150" s="10" t="n">
+        <v>1154</v>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>Sofia Gutierrez</t>
+        </is>
+      </c>
+      <c r="D150" s="10" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B151" s="8" t="n">
+        <v>1162</v>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t>David Castro</t>
+        </is>
+      </c>
+      <c r="D151" s="8" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="n">
+        <v>1174</v>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>Juliana Mendoza</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="n">
+        <v>1184</v>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>Laura Garcia</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="n">
+        <v>1189</v>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>Jorge Hernandez</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Ortiz</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="n">
+        <v>1225</v>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>Miguel Ramirez</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="n">
+        <v>1227</v>
+      </c>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>Gabriela Silva</t>
+        </is>
+      </c>
+      <c r="D157" s="8" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B158" s="10" t="n">
+        <v>1229</v>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>Diego Alvarez</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="n">
+        <v>1235</v>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>Alejandra Castro</t>
+        </is>
+      </c>
+      <c r="D159" s="8" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B160" s="10" t="n">
+        <v>1237</v>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>Diana Moreno</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B161" s="8" t="n">
+        <v>1240</v>
+      </c>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t>Ricardo Ortiz</t>
+        </is>
+      </c>
+      <c r="D161" s="8" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B162" s="10" t="n">
+        <v>1242</v>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>Sofia Acosta</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B163" s="8" t="n">
+        <v>1249</v>
+      </c>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t>Ricardo Acosta</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B164" s="10" t="n">
+        <v>1253</v>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>Miguel Ortiz</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="n">
+        <v>1255</v>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>Juliana Cruz</t>
+        </is>
+      </c>
+      <c r="D165" s="8" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B166" s="10" t="n">
+        <v>1283</v>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>Mariana Alvarez</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="n">
+        <v>1295</v>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>Daniela Diaz</t>
+        </is>
+      </c>
+      <c r="D167" s="8" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B168" s="10" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
+          <t>David Silva</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="n">
+        <v>1319</v>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t>Natalia Castro</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B170" s="10" t="n">
+        <v>1322</v>
+      </c>
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>Cesar Vargas</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="n">
+        <v>1330</v>
+      </c>
+      <c r="C171" s="8" t="inlineStr">
+        <is>
+          <t>Lina Martinez</t>
+        </is>
+      </c>
+      <c r="D171" s="8" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B172" s="10" t="n">
+        <v>1332</v>
+      </c>
+      <c r="C172" s="10" t="inlineStr">
+        <is>
+          <t>Hector Suarez</t>
+        </is>
+      </c>
+      <c r="D172" s="10" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B173" s="8" t="n">
+        <v>1334</v>
+      </c>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t>Mariana Diaz</t>
+        </is>
+      </c>
+      <c r="D173" s="8" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B174" s="10" t="n">
+        <v>1340</v>
+      </c>
+      <c r="C174" s="10" t="inlineStr">
+        <is>
+          <t>Valentina Pena</t>
+        </is>
+      </c>
+      <c r="D174" s="10" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B175" s="8" t="n">
+        <v>1348</v>
+      </c>
+      <c r="C175" s="8" t="inlineStr">
+        <is>
+          <t>Sofia Morales</t>
+        </is>
+      </c>
+      <c r="D175" s="8" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B176" s="10" t="n">
+        <v>1355</v>
+      </c>
+      <c r="C176" s="10" t="inlineStr">
+        <is>
+          <t>Daniela Ruiz</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="n">
+        <v>1356</v>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t>Paula Ortiz</t>
+        </is>
+      </c>
+      <c r="D177" s="8" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B178" s="10" t="n">
+        <v>1357</v>
+      </c>
+      <c r="C178" s="10" t="inlineStr">
+        <is>
+          <t>Luis Ramirez</t>
+        </is>
+      </c>
+      <c r="D178" s="10" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="n">
+        <v>1364</v>
+      </c>
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t>Sebastian Moreno</t>
+        </is>
+      </c>
+      <c r="D179" s="8" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B180" s="10" t="n">
+        <v>1367</v>
+      </c>
+      <c r="C180" s="10" t="inlineStr">
+        <is>
+          <t>Diego Ruiz</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="n">
+        <v>1378</v>
+      </c>
+      <c r="C181" s="8" t="inlineStr">
+        <is>
+          <t>Gabriela Alvarez</t>
+        </is>
+      </c>
+      <c r="D181" s="8" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B182" s="10" t="n">
+        <v>1383</v>
+      </c>
+      <c r="C182" s="10" t="inlineStr">
+        <is>
+          <t>Juliana Silva</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B183" s="8" t="n">
+        <v>1391</v>
+      </c>
+      <c r="C183" s="8" t="inlineStr">
+        <is>
+          <t>Daniela Garcia</t>
+        </is>
+      </c>
+      <c r="D183" s="8" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B184" s="10" t="n">
+        <v>1397</v>
+      </c>
+      <c r="C184" s="10" t="inlineStr">
+        <is>
+          <t>Natalia Vega</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B185" s="8" t="n">
+        <v>1402</v>
+      </c>
+      <c r="C185" s="8" t="inlineStr">
+        <is>
+          <t>Carolina Ramirez</t>
+        </is>
+      </c>
+      <c r="D185" s="8" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B186" s="10" t="n">
+        <v>1406</v>
+      </c>
+      <c r="C186" s="10" t="inlineStr">
+        <is>
+          <t>Alejandra Hernandez</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B187" s="8" t="n">
+        <v>1412</v>
+      </c>
+      <c r="C187" s="8" t="inlineStr">
+        <is>
+          <t>Hector Vega</t>
+        </is>
+      </c>
+      <c r="D187" s="8" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B188" s="10" t="n">
+        <v>1427</v>
+      </c>
+      <c r="C188" s="10" t="inlineStr">
+        <is>
+          <t>Fernando Flores</t>
+        </is>
+      </c>
+      <c r="D188" s="10" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B189" s="8" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>Sebastian Reyes</t>
+        </is>
+      </c>
+      <c r="D189" s="8" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B190" s="10" t="n">
+        <v>1435</v>
+      </c>
+      <c r="C190" s="10" t="inlineStr">
+        <is>
+          <t>Hector Alvarez</t>
+        </is>
+      </c>
+      <c r="D190" s="10" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B191" s="8" t="n">
+        <v>1458</v>
+      </c>
+      <c r="C191" s="8" t="inlineStr">
+        <is>
+          <t>Gabriela Garcia</t>
+        </is>
+      </c>
+      <c r="D191" s="8" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B192" s="10" t="n">
+        <v>1462</v>
+      </c>
+      <c r="C192" s="10" t="inlineStr">
+        <is>
+          <t>Luis Morales</t>
+        </is>
+      </c>
+      <c r="D192" s="10" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="n">
+        <v>1483</v>
+      </c>
+      <c r="C193" s="8" t="inlineStr">
+        <is>
+          <t>Fernando Jimenez</t>
+        </is>
+      </c>
+      <c r="D193" s="8" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B194" s="10" t="n">
+        <v>1486</v>
+      </c>
+      <c r="C194" s="10" t="inlineStr">
+        <is>
+          <t>Maria Torres</t>
+        </is>
+      </c>
+      <c r="D194" s="10" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B195" s="8" t="n">
+        <v>1491</v>
+      </c>
+      <c r="C195" s="8" t="inlineStr">
+        <is>
+          <t>Sofia Hernandez</t>
+        </is>
+      </c>
+      <c r="D195" s="8" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B196" s="10" t="n">
+        <v>1492</v>
+      </c>
+      <c r="C196" s="10" t="inlineStr">
+        <is>
+          <t>Cesar Rodriguez</t>
+        </is>
+      </c>
+      <c r="D196" s="10" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B197" s="8" t="n">
+        <v>1495</v>
+      </c>
+      <c r="C197" s="8" t="inlineStr">
+        <is>
+          <t>David Ruiz</t>
+        </is>
+      </c>
+      <c r="D197" s="8" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B198" s="10" t="n">
+        <v>1501</v>
+      </c>
+      <c r="C198" s="10" t="inlineStr">
+        <is>
+          <t>Felipe Ramirez</t>
+        </is>
+      </c>
+      <c r="D198" s="10" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B199" s="8" t="n">
+        <v>1521</v>
+      </c>
+      <c r="C199" s="8" t="inlineStr">
+        <is>
+          <t>Sebastian Castro</t>
+        </is>
+      </c>
+      <c r="D199" s="8" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B200" s="10" t="n">
+        <v>1537</v>
+      </c>
+      <c r="C200" s="10" t="inlineStr">
+        <is>
+          <t>Gabriela Romero</t>
+        </is>
+      </c>
+      <c r="D200" s="10" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B201" s="8" t="n">
+        <v>1554</v>
+      </c>
+      <c r="C201" s="8" t="inlineStr">
+        <is>
+          <t>Miguel Suarez</t>
+        </is>
+      </c>
+      <c r="D201" s="8" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B202" s="10" t="n">
+        <v>1558</v>
+      </c>
+      <c r="C202" s="10" t="inlineStr">
+        <is>
+          <t>David Gutierrez</t>
+        </is>
+      </c>
+      <c r="D202" s="10" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B203" s="8" t="n">
+        <v>1564</v>
+      </c>
+      <c r="C203" s="8" t="inlineStr">
+        <is>
+          <t>Diego Suarez</t>
+        </is>
+      </c>
+      <c r="D203" s="8" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B204" s="10" t="n">
+        <v>1565</v>
+      </c>
+      <c r="C204" s="10" t="inlineStr">
+        <is>
+          <t>Fernando Acosta</t>
+        </is>
+      </c>
+      <c r="D204" s="10" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B205" s="8" t="n">
+        <v>1568</v>
+      </c>
+      <c r="C205" s="8" t="inlineStr">
+        <is>
+          <t>Hector Gutierrez</t>
+        </is>
+      </c>
+      <c r="D205" s="8" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B206" s="10" t="n">
+        <v>1569</v>
+      </c>
+      <c r="C206" s="10" t="inlineStr">
+        <is>
+          <t>Juliana Cruz</t>
+        </is>
+      </c>
+      <c r="D206" s="10" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B207" s="8" t="n">
+        <v>1576</v>
+      </c>
+      <c r="C207" s="8" t="inlineStr">
+        <is>
+          <t>Maria Garcia</t>
+        </is>
+      </c>
+      <c r="D207" s="8" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B208" s="10" t="n">
+        <v>1585</v>
+      </c>
+      <c r="C208" s="10" t="inlineStr">
+        <is>
+          <t>Miguel Ruiz</t>
+        </is>
+      </c>
+      <c r="D208" s="10" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B209" s="8" t="n">
+        <v>1593</v>
+      </c>
+      <c r="C209" s="8" t="inlineStr">
+        <is>
+          <t>Camila Garcia</t>
+        </is>
+      </c>
+      <c r="D209" s="8" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B210" s="10" t="n">
+        <v>1597</v>
+      </c>
+      <c r="C210" s="10" t="inlineStr">
+        <is>
+          <t>Oscar Diaz</t>
+        </is>
+      </c>
+      <c r="D210" s="10" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B211" s="8" t="n">
+        <v>1598</v>
+      </c>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>Oscar Cruz</t>
+        </is>
+      </c>
+      <c r="D211" s="8" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B212" s="10" t="n">
+        <v>1601</v>
+      </c>
+      <c r="C212" s="10" t="inlineStr">
+        <is>
+          <t>Oscar Vargas</t>
+        </is>
+      </c>
+      <c r="D212" s="10" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B213" s="8" t="n">
+        <v>1604</v>
+      </c>
+      <c r="C213" s="8" t="inlineStr">
+        <is>
+          <t>Paula Mendoza</t>
+        </is>
+      </c>
+      <c r="D213" s="8" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B214" s="10" t="n">
+        <v>1605</v>
+      </c>
+      <c r="C214" s="10" t="inlineStr">
+        <is>
+          <t>Cesar Vargas</t>
+        </is>
+      </c>
+      <c r="D214" s="10" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B215" s="8" t="n">
+        <v>1607</v>
+      </c>
+      <c r="C215" s="8" t="inlineStr">
+        <is>
+          <t>Andres Morales</t>
+        </is>
+      </c>
+      <c r="D215" s="8" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B216" s="10" t="n">
+        <v>1609</v>
+      </c>
+      <c r="C216" s="10" t="inlineStr">
+        <is>
+          <t>Laura Garcia</t>
+        </is>
+      </c>
+      <c r="D216" s="10" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B217" s="8" t="n">
+        <v>1615</v>
+      </c>
+      <c r="C217" s="8" t="inlineStr">
+        <is>
+          <t>Oscar Cruz</t>
+        </is>
+      </c>
+      <c r="D217" s="8" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B218" s="10" t="n">
+        <v>1624</v>
+      </c>
+      <c r="C218" s="10" t="inlineStr">
+        <is>
+          <t>Luis Cruz</t>
+        </is>
+      </c>
+      <c r="D218" s="10" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B219" s="8" t="n">
+        <v>1625</v>
+      </c>
+      <c r="C219" s="8" t="inlineStr">
+        <is>
+          <t>Ricardo Morales</t>
+        </is>
+      </c>
+      <c r="D219" s="8" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B220" s="10" t="n">
+        <v>1645</v>
+      </c>
+      <c r="C220" s="10" t="inlineStr">
+        <is>
+          <t>Felipe Silva</t>
+        </is>
+      </c>
+      <c r="D220" s="10" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B221" s="8" t="n">
+        <v>1646</v>
+      </c>
+      <c r="C221" s="8" t="inlineStr">
+        <is>
+          <t>Daniela Pena</t>
+        </is>
+      </c>
+      <c r="D221" s="8" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B222" s="10" t="n">
+        <v>1665</v>
+      </c>
+      <c r="C222" s="10" t="inlineStr">
+        <is>
+          <t>Fernando Ortiz</t>
+        </is>
+      </c>
+      <c r="D222" s="10" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="n">
+        <v>1668</v>
+      </c>
+      <c r="C223" s="8" t="inlineStr">
+        <is>
+          <t>Maria Rojas</t>
+        </is>
+      </c>
+      <c r="D223" s="8" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B224" s="10" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C224" s="10" t="inlineStr">
+        <is>
+          <t>Gabriela Cruz</t>
+        </is>
+      </c>
+      <c r="D224" s="10" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B225" s="8" t="n">
+        <v>1684</v>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>Andres Pena</t>
+        </is>
+      </c>
+      <c r="D225" s="8" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B226" s="10" t="n">
+        <v>1687</v>
+      </c>
+      <c r="C226" s="10" t="inlineStr">
+        <is>
+          <t>Cesar Ruiz</t>
+        </is>
+      </c>
+      <c r="D226" s="10" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="n">
+        <v>1693</v>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>Alejandra Vargas</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B228" s="10" t="n">
+        <v>1696</v>
+      </c>
+      <c r="C228" s="10" t="inlineStr">
+        <is>
+          <t>Sebastian Suarez</t>
+        </is>
+      </c>
+      <c r="D228" s="10" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="n">
+        <v>1700</v>
+      </c>
+      <c r="C229" s="8" t="inlineStr">
+        <is>
+          <t>Diego Ruiz</t>
+        </is>
+      </c>
+      <c r="D229" s="8" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B230" s="10" t="n">
+        <v>1707</v>
+      </c>
+      <c r="C230" s="10" t="inlineStr">
+        <is>
+          <t>Mariana Reyes</t>
+        </is>
+      </c>
+      <c r="D230" s="10" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="n">
+        <v>1711</v>
+      </c>
+      <c r="C231" s="8" t="inlineStr">
+        <is>
+          <t>Daniela Pena</t>
+        </is>
+      </c>
+      <c r="D231" s="8" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B232" s="10" t="n">
+        <v>1714</v>
+      </c>
+      <c r="C232" s="10" t="inlineStr">
+        <is>
+          <t>Felipe Vega</t>
+        </is>
+      </c>
+      <c r="D232" s="10" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="n">
+        <v>1715</v>
+      </c>
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>Mariana Castro</t>
+        </is>
+      </c>
+      <c r="D233" s="8" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B234" s="10" t="n">
+        <v>1729</v>
+      </c>
+      <c r="C234" s="10" t="inlineStr">
+        <is>
+          <t>Camila Romero</t>
+        </is>
+      </c>
+      <c r="D234" s="10" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B235" s="8" t="n">
+        <v>1730</v>
+      </c>
+      <c r="C235" s="8" t="inlineStr">
+        <is>
+          <t>Lina Rojas</t>
+        </is>
+      </c>
+      <c r="D235" s="8" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B236" s="10" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C236" s="10" t="inlineStr">
+        <is>
+          <t>Miguel Garcia</t>
+        </is>
+      </c>
+      <c r="D236" s="10" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B237" s="8" t="n">
+        <v>1770</v>
+      </c>
+      <c r="C237" s="8" t="inlineStr">
+        <is>
+          <t>Fernando Moreno</t>
+        </is>
+      </c>
+      <c r="D237" s="8" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B238" s="10" t="n">
+        <v>1806</v>
+      </c>
+      <c r="C238" s="10" t="inlineStr">
+        <is>
+          <t>Cesar Ruiz</t>
+        </is>
+      </c>
+      <c r="D238" s="10" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="n">
+        <v>1814</v>
+      </c>
+      <c r="C239" s="8" t="inlineStr">
+        <is>
+          <t>Diana Diaz</t>
+        </is>
+      </c>
+      <c r="D239" s="8" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B240" s="10" t="n">
+        <v>1815</v>
+      </c>
+      <c r="C240" s="10" t="inlineStr">
+        <is>
+          <t>Paula Jimenez</t>
+        </is>
+      </c>
+      <c r="D240" s="10" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B241" s="8" t="n">
+        <v>1819</v>
+      </c>
+      <c r="C241" s="8" t="inlineStr">
+        <is>
+          <t>Mariana Gomez</t>
+        </is>
+      </c>
+      <c r="D241" s="8" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B242" s="10" t="n">
+        <v>1828</v>
+      </c>
+      <c r="C242" s="10" t="inlineStr">
+        <is>
+          <t>Hector Diaz</t>
+        </is>
+      </c>
+      <c r="D242" s="10" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="n">
+        <v>1830</v>
+      </c>
+      <c r="C243" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Gutierrez</t>
+        </is>
+      </c>
+      <c r="D243" s="8" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B244" s="10" t="n">
+        <v>1833</v>
+      </c>
+      <c r="C244" s="10" t="inlineStr">
+        <is>
+          <t>Fernando Lopez</t>
+        </is>
+      </c>
+      <c r="D244" s="10" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="n">
+        <v>1842</v>
+      </c>
+      <c r="C245" s="8" t="inlineStr">
+        <is>
+          <t>Oscar Torres</t>
+        </is>
+      </c>
+      <c r="D245" s="8" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B246" s="10" t="n">
+        <v>1851</v>
+      </c>
+      <c r="C246" s="10" t="inlineStr">
+        <is>
+          <t>Valentina Romero</t>
+        </is>
+      </c>
+      <c r="D246" s="10" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="n">
+        <v>1856</v>
+      </c>
+      <c r="C247" s="8" t="inlineStr">
+        <is>
+          <t>Maria Morales</t>
+        </is>
+      </c>
+      <c r="D247" s="8" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B248" s="10" t="n">
+        <v>1858</v>
+      </c>
+      <c r="C248" s="10" t="inlineStr">
+        <is>
+          <t>Luis Hernandez</t>
+        </is>
+      </c>
+      <c r="D248" s="10" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B249" s="8" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>Jorge Silva</t>
+        </is>
+      </c>
+      <c r="D249" s="8" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B250" s="10" t="n">
+        <v>1867</v>
+      </c>
+      <c r="C250" s="10" t="inlineStr">
+        <is>
+          <t>Maria Silva</t>
+        </is>
+      </c>
+      <c r="D250" s="10" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B251" s="8" t="n">
+        <v>1877</v>
+      </c>
+      <c r="C251" s="8" t="inlineStr">
+        <is>
+          <t>Cesar Morales</t>
+        </is>
+      </c>
+      <c r="D251" s="8" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B252" s="10" t="n">
+        <v>1887</v>
+      </c>
+      <c r="C252" s="10" t="inlineStr">
+        <is>
+          <t>Fernando Garcia</t>
+        </is>
+      </c>
+      <c r="D252" s="10" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B253" s="8" t="n">
+        <v>1896</v>
+      </c>
+      <c r="C253" s="8" t="inlineStr">
+        <is>
+          <t>Carolina Suarez</t>
+        </is>
+      </c>
+      <c r="D253" s="8" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B254" s="10" t="n">
+        <v>1899</v>
+      </c>
+      <c r="C254" s="10" t="inlineStr">
+        <is>
+          <t>Oscar Rodriguez</t>
+        </is>
+      </c>
+      <c r="D254" s="10" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B255" s="8" t="n">
+        <v>1911</v>
+      </c>
+      <c r="C255" s="8" t="inlineStr">
+        <is>
+          <t>Diana Mendoza</t>
+        </is>
+      </c>
+      <c r="D255" s="8" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B256" s="10" t="n">
+        <v>1926</v>
+      </c>
+      <c r="C256" s="10" t="inlineStr">
+        <is>
+          <t>Paula Jimenez</t>
+        </is>
+      </c>
+      <c r="D256" s="10" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B257" s="8" t="n">
+        <v>1928</v>
+      </c>
+      <c r="C257" s="8" t="inlineStr">
+        <is>
+          <t>Ricardo Cruz</t>
+        </is>
+      </c>
+      <c r="D257" s="8" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B258" s="10" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C258" s="10" t="inlineStr">
+        <is>
+          <t>Luis Alvarez</t>
+        </is>
+      </c>
+      <c r="D258" s="10" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B259" s="8" t="n">
+        <v>1949</v>
+      </c>
+      <c r="C259" s="8" t="inlineStr">
+        <is>
+          <t>Andres Jimenez</t>
+        </is>
+      </c>
+      <c r="D259" s="8" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B260" s="10" t="n">
+        <v>1966</v>
+      </c>
+      <c r="C260" s="10" t="inlineStr">
+        <is>
+          <t>Cesar Jimenez</t>
+        </is>
+      </c>
+      <c r="D260" s="10" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B261" s="8" t="n">
+        <v>1973</v>
+      </c>
+      <c r="C261" s="8" t="inlineStr">
+        <is>
+          <t>Luis Gutierrez</t>
+        </is>
+      </c>
+      <c r="D261" s="8" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B262" s="10" t="n">
+        <v>1983</v>
+      </c>
+      <c r="C262" s="10" t="inlineStr">
+        <is>
+          <t>Alejandra Torres</t>
+        </is>
+      </c>
+      <c r="D262" s="10" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B263" s="8" t="n">
+        <v>1988</v>
+      </c>
+      <c r="C263" s="8" t="inlineStr">
+        <is>
+          <t>Luis Lopez</t>
+        </is>
+      </c>
+      <c r="D263" s="8" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="10" t="inlineStr">
+        <is>
+          <t>Leads calificados sin asesor</t>
+        </is>
+      </c>
+      <c r="B264" s="10" t="n">
+        <v>382</v>
+      </c>
+      <c r="C264" s="10" t="inlineStr">
+        <is>
+          <t>Revisar asignación en el CRM</t>
+        </is>
+      </c>
+      <c r="D264" s="10" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="8" t="inlineStr">
+        <is>
           <t>Interacciones con fecha inválida</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B265" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C265" s="8" t="inlineStr">
         <is>
           <t>Ninguna: todas posteriores al registro</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr"/>
+      <c r="D265" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1056,7 +5168,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>6000</v>
@@ -1102,14 +5214,14 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>0.015</v>
+        <v>0.0015</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>0.015</v>
       </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Cumple</t>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Por debajo de la meta (muestra)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1124,15 +5236,15 @@
           <t>Leads por referidos</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
-        <v>0.095</v>
+      <c r="B8" s="12" t="n">
+        <v>0.133</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Por debajo de la meta (muestra)</t>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -1153,7 +5265,7 @@
       <c r="C9" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Cumple</t>
         </is>
@@ -1261,7 +5373,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="D5" s="11" t="n"/>
       <c r="E5" s="11" t="n"/>
@@ -1276,12 +5388,12 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E6" s="13" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1295,10 +5407,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>40</v>
+        <v>354</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>0.5</v>
+        <v>0.351</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0.5</v>
@@ -1316,10 +5428,10 @@
       <c r="C8" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="D8" s="13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="13" t="n">
+      <c r="D8" s="12" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="E8" s="12" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1354,10 +5466,10 @@
       <c r="C10" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="12" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -1376,7 +5488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1434,16 +5546,16 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>114</v>
+        <v>361</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>0.0263</v>
+        <v>0.0083</v>
       </c>
     </row>
     <row r="6">
@@ -1453,10 +5565,10 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>33</v>
+        <v>297</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>0</v>
@@ -1472,10 +5584,10 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>19</v>
+        <v>266</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>0</v>
@@ -1491,10 +5603,10 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>34</v>
+        <v>314</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>13</v>
+        <v>163</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>0</v>
@@ -1510,15 +5622,55 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="14" t="n"/>
+      <c r="E9" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Meta (Facebook/Instagram)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>253</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>126</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Meta Ads</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>248</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>123</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1602,7 +5754,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>9</v>
@@ -1624,7 +5776,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>48</v>
+        <v>384</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>3</v>
@@ -1646,7 +5798,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>32</v>
+        <v>409</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>3</v>
@@ -1668,7 +5820,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>2</v>
@@ -1690,7 +5842,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>20</v>
+        <v>394</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>3</v>
@@ -1793,7 +5945,7 @@
         <v>400</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>8</v>
+        <v>386</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0</v>
@@ -1818,7 +5970,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>76</v>
+        <v>438</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>1</v>
@@ -1843,7 +5995,7 @@
         <v>1200</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>45</v>
+        <v>401</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>1</v>
@@ -1868,7 +6020,7 @@
         <v>1000</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>29</v>
+        <v>376</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>1</v>
@@ -1893,7 +6045,7 @@
         <v>1400</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>42</v>
+        <v>399</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>0</v>
@@ -2077,7 +6229,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="6">
@@ -2087,10 +6239,10 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>0.16</v>
+        <v>58</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>0.029</v>
       </c>
     </row>
     <row r="7">
@@ -2100,10 +6252,10 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>77</v>
+        <v>978</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.385</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="8">
@@ -2113,10 +6265,10 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>89</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>0.445</v>
+        <v>962</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>0.481</v>
       </c>
     </row>
   </sheetData>
@@ -2134,14 +6286,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2982,6 +7134,656 @@
       <c r="E36" s="10" t="inlineStr">
         <is>
           <t>2027-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Vargas</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Jorge Diaz</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Felipe Jimenez</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Alejandra Ramirez</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Maria Silva</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Hector Silva</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Moreno</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>Maria Rios</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Sebastian Rodriguez</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>Laura Gomez</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Felipe Rios</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>Natalia Castro</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Juliana Hernandez</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>Carlos Morales</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Natalia Vega</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>Fernando Romero</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Diana Lopez</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>Maria Garcia</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Gabriela Cruz</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>Carolina Pena</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Juan Pena</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Luis Reyes</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Valentina Moreno</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>Valentina Romero</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Juan Pena</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Daniela Rojas</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
         </is>
       </c>
     </row>

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fecha del informe: 19/10/2026</t>
+          <t>Fecha del informe: 20/10/2026</t>
         </is>
       </c>
     </row>

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>6000</v>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.133</v>
+        <v>0.1329</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>0.1</v>
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="D5" s="11" t="n"/>
       <c r="E5" s="11" t="n"/>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>201</v>
@@ -5754,7 +5754,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>9</v>
@@ -5945,7 +5945,7 @@
         <v>400</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>0.489</v>

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>6000</v>
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="D5" s="11" t="n"/>
       <c r="E5" s="11" t="n"/>
@@ -5391,7 +5391,7 @@
         <v>1008</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.504</v>
+        <v>0.503</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>0.4</v>
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>123</v>
@@ -5754,7 +5754,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>9</v>
@@ -5945,7 +5945,7 @@
         <v>400</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0</v>
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.489</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="8">

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fecha del informe: 20/10/2026</t>
+          <t>Fecha del informe: 21/10/2026</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>6000</v>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.1329</v>
+        <v>0.1327</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>0.1</v>
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="D5" s="11" t="n"/>
       <c r="E5" s="11" t="n"/>
@@ -5622,7 +5622,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>120</v>
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>123</v>
@@ -5754,7 +5754,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>9</v>
@@ -5945,7 +5945,7 @@
         <v>400</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>0.49</v>
@@ -6268,7 +6268,7 @@
         <v>962</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -866,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D265"/>
+  <dimension ref="A1:D293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5066,34 +5066,594 @@
     <row r="264">
       <c r="A264" s="10" t="inlineStr">
         <is>
-          <t>Leads calificados sin asesor</t>
+          <t>No contactar (baja/revocada)</t>
         </is>
       </c>
       <c r="B264" s="10" t="n">
-        <v>382</v>
+        <v>2005</v>
       </c>
       <c r="C264" s="10" t="inlineStr">
         <is>
-          <t>Revisar asignación en el CRM</t>
-        </is>
-      </c>
-      <c r="D264" s="10" t="inlineStr"/>
+          <t>Julián Cárdenas Franco</t>
+        </is>
+      </c>
+      <c r="D264" s="10" t="inlineStr">
+        <is>
+          <t>2027-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="8" t="inlineStr">
         <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B265" s="8" t="n">
+        <v>2037</v>
+      </c>
+      <c r="C265" s="8" t="inlineStr">
+        <is>
+          <t>Francisco Henao</t>
+        </is>
+      </c>
+      <c r="D265" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B266" s="10" t="n">
+        <v>2098</v>
+      </c>
+      <c r="C266" s="10" t="inlineStr">
+        <is>
+          <t>Victoria Jiménez</t>
+        </is>
+      </c>
+      <c r="D266" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B267" s="8" t="n">
+        <v>2114</v>
+      </c>
+      <c r="C267" s="8" t="inlineStr">
+        <is>
+          <t>Felipe Cardona</t>
+        </is>
+      </c>
+      <c r="D267" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B268" s="10" t="n">
+        <v>2328</v>
+      </c>
+      <c r="C268" s="10" t="inlineStr">
+        <is>
+          <t>Laura Muñoz Mendoza</t>
+        </is>
+      </c>
+      <c r="D268" s="10" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B269" s="8" t="n">
+        <v>2415</v>
+      </c>
+      <c r="C269" s="8" t="inlineStr">
+        <is>
+          <t>Paula Salazar</t>
+        </is>
+      </c>
+      <c r="D269" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B270" s="10" t="n">
+        <v>2435</v>
+      </c>
+      <c r="C270" s="10" t="inlineStr">
+        <is>
+          <t>Victoria García</t>
+        </is>
+      </c>
+      <c r="D270" s="10" t="inlineStr">
+        <is>
+          <t>2027-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B271" s="8" t="n">
+        <v>2458</v>
+      </c>
+      <c r="C271" s="8" t="inlineStr">
+        <is>
+          <t>Felipe Londono Valencia</t>
+        </is>
+      </c>
+      <c r="D271" s="8" t="inlineStr">
+        <is>
+          <t>2027-02-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B272" s="10" t="n">
+        <v>2510</v>
+      </c>
+      <c r="C272" s="10" t="inlineStr">
+        <is>
+          <t>Diego Pérez</t>
+        </is>
+      </c>
+      <c r="D272" s="10" t="inlineStr">
+        <is>
+          <t>2027-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B273" s="8" t="n">
+        <v>2524</v>
+      </c>
+      <c r="C273" s="8" t="inlineStr">
+        <is>
+          <t>Fernanda Martínez</t>
+        </is>
+      </c>
+      <c r="D273" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B274" s="10" t="n">
+        <v>2534</v>
+      </c>
+      <c r="C274" s="10" t="inlineStr">
+        <is>
+          <t>Felipe Castro</t>
+        </is>
+      </c>
+      <c r="D274" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B275" s="8" t="n">
+        <v>2563</v>
+      </c>
+      <c r="C275" s="8" t="inlineStr">
+        <is>
+          <t>Martín Martínez Salazar</t>
+        </is>
+      </c>
+      <c r="D275" s="8" t="inlineStr">
+        <is>
+          <t>2027-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B276" s="10" t="n">
+        <v>2570</v>
+      </c>
+      <c r="C276" s="10" t="inlineStr">
+        <is>
+          <t>Diego Díaz</t>
+        </is>
+      </c>
+      <c r="D276" s="10" t="inlineStr">
+        <is>
+          <t>2027-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B277" s="8" t="n">
+        <v>2711</v>
+      </c>
+      <c r="C277" s="8" t="inlineStr">
+        <is>
+          <t>Andrés Acosta Londono</t>
+        </is>
+      </c>
+      <c r="D277" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B278" s="10" t="n">
+        <v>2738</v>
+      </c>
+      <c r="C278" s="10" t="inlineStr">
+        <is>
+          <t>Valeria Castro</t>
+        </is>
+      </c>
+      <c r="D278" s="10" t="inlineStr">
+        <is>
+          <t>2027-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B279" s="8" t="n">
+        <v>2853</v>
+      </c>
+      <c r="C279" s="8" t="inlineStr">
+        <is>
+          <t>Andrea Gutiérrez</t>
+        </is>
+      </c>
+      <c r="D279" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B280" s="10" t="n">
+        <v>2866</v>
+      </c>
+      <c r="C280" s="10" t="inlineStr">
+        <is>
+          <t>Daniela Cárdenas</t>
+        </is>
+      </c>
+      <c r="D280" s="10" t="inlineStr">
+        <is>
+          <t>2027-02-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B281" s="8" t="n">
+        <v>2898</v>
+      </c>
+      <c r="C281" s="8" t="inlineStr">
+        <is>
+          <t>Alejandro Arias Salazar</t>
+        </is>
+      </c>
+      <c r="D281" s="8" t="inlineStr">
+        <is>
+          <t>2027-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B282" s="10" t="n">
+        <v>3053</v>
+      </c>
+      <c r="C282" s="10" t="inlineStr">
+        <is>
+          <t>Angela Martínez</t>
+        </is>
+      </c>
+      <c r="D282" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B283" s="8" t="n">
+        <v>3131</v>
+      </c>
+      <c r="C283" s="8" t="inlineStr">
+        <is>
+          <t>Gabriela Muñoz</t>
+        </is>
+      </c>
+      <c r="D283" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B284" s="10" t="n">
+        <v>3151</v>
+      </c>
+      <c r="C284" s="10" t="inlineStr">
+        <is>
+          <t>Natalia Londono</t>
+        </is>
+      </c>
+      <c r="D284" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B285" s="8" t="n">
+        <v>3190</v>
+      </c>
+      <c r="C285" s="8" t="inlineStr">
+        <is>
+          <t>Carolina Acosta</t>
+        </is>
+      </c>
+      <c r="D285" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B286" s="10" t="n">
+        <v>3197</v>
+      </c>
+      <c r="C286" s="10" t="inlineStr">
+        <is>
+          <t>Andrés Patiño Salazar</t>
+        </is>
+      </c>
+      <c r="D286" s="10" t="inlineStr">
+        <is>
+          <t>2027-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B287" s="8" t="n">
+        <v>3206</v>
+      </c>
+      <c r="C287" s="8" t="inlineStr">
+        <is>
+          <t>Fernanda Jiménez Henao</t>
+        </is>
+      </c>
+      <c r="D287" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B288" s="10" t="n">
+        <v>3259</v>
+      </c>
+      <c r="C288" s="10" t="inlineStr">
+        <is>
+          <t>Carlos Cardona</t>
+        </is>
+      </c>
+      <c r="D288" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B289" s="8" t="n">
+        <v>3285</v>
+      </c>
+      <c r="C289" s="8" t="inlineStr">
+        <is>
+          <t>David Martínez Velasco</t>
+        </is>
+      </c>
+      <c r="D289" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="10" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B290" s="10" t="n">
+        <v>3291</v>
+      </c>
+      <c r="C290" s="10" t="inlineStr">
+        <is>
+          <t>Isabela Díaz</t>
+        </is>
+      </c>
+      <c r="D290" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="8" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B291" s="8" t="n">
+        <v>3349</v>
+      </c>
+      <c r="C291" s="8" t="inlineStr">
+        <is>
+          <t>Francisco Arias</t>
+        </is>
+      </c>
+      <c r="D291" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="10" t="inlineStr">
+        <is>
+          <t>Leads calificados sin asesor</t>
+        </is>
+      </c>
+      <c r="B292" s="10" t="n">
+        <v>632</v>
+      </c>
+      <c r="C292" s="10" t="inlineStr">
+        <is>
+          <t>Revisar asignación en el CRM</t>
+        </is>
+      </c>
+      <c r="D292" s="10" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="8" t="inlineStr">
+        <is>
           <t>Interacciones con fecha inválida</t>
         </is>
       </c>
-      <c r="B265" s="8" t="n">
+      <c r="B293" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C265" s="8" t="inlineStr">
+      <c r="C293" s="8" t="inlineStr">
         <is>
           <t>Ninguna: todas posteriores al registro</t>
         </is>
       </c>
-      <c r="D265" s="8" t="inlineStr"/>
+      <c r="D293" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5168,7 +5728,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>2004</v>
+        <v>3600</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>6000</v>
@@ -5214,7 +5774,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>0.0015</v>
+        <v>0.0008</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>0.015</v>
@@ -5237,7 +5797,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.1327</v>
+        <v>0.1422</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>0.1</v>
@@ -5373,7 +5933,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>2004</v>
+        <v>3600</v>
       </c>
       <c r="D5" s="11" t="n"/>
       <c r="E5" s="11" t="n"/>
@@ -5388,10 +5948,10 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1008</v>
+        <v>2344</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.503</v>
+        <v>0.651</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>0.4</v>
@@ -5407,10 +5967,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>354</v>
+        <v>1437</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>0.351</v>
+        <v>0.613</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0.5</v>
@@ -5426,10 +5986,10 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>20</v>
+        <v>840</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.056</v>
+        <v>0.585</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>0.5</v>
@@ -5445,10 +6005,10 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>5</v>
+        <v>562</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.25</v>
+        <v>0.669</v>
       </c>
       <c r="E9" s="11" t="n">
         <v>0.25</v>
@@ -5464,10 +6024,10 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3</v>
+        <v>274</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>0.6</v>
+        <v>0.488</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>0.6</v>
@@ -5546,16 +6106,16 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>362</v>
+        <v>573</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>201</v>
+        <v>372</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>0.0083</v>
+        <v>0.0716</v>
       </c>
     </row>
     <row r="6">
@@ -5565,16 +6125,16 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>297</v>
+        <v>498</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0</v>
+        <v>0.0683</v>
       </c>
     </row>
     <row r="7">
@@ -5584,16 +6144,16 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>266</v>
+        <v>512</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>125</v>
+        <v>326</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>0</v>
+        <v>0.0781</v>
       </c>
     </row>
     <row r="8">
@@ -5603,16 +6163,16 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>314</v>
+        <v>543</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>163</v>
+        <v>360</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>0</v>
+        <v>0.09760000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -5622,16 +6182,16 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>262</v>
+        <v>499</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>120</v>
+        <v>322</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>0</v>
+        <v>0.06809999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -5641,16 +6201,16 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>253</v>
+        <v>490</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>126</v>
+        <v>322</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0</v>
+        <v>0.0694</v>
       </c>
     </row>
     <row r="11">
@@ -5660,16 +6220,16 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>250</v>
+        <v>485</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>123</v>
+        <v>322</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>0</v>
+        <v>0.0784</v>
       </c>
     </row>
   </sheetData>
@@ -5754,13 +6314,13 @@
         <v>36</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>446</v>
+        <v>757</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>9</v>
+        <v>167</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>395</v>
@@ -5776,13 +6336,13 @@
         <v>22</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>384</v>
+        <v>710</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>3</v>
+        <v>168</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F6" s="10" t="n">
         <v>0</v>
@@ -5798,13 +6358,13 @@
         <v>14</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>409</v>
+        <v>721</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>379</v>
@@ -5820,13 +6380,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>371</v>
+        <v>689</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>0</v>
@@ -5842,13 +6402,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>394</v>
+        <v>723</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>3</v>
+        <v>164</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>374</v>
@@ -5945,10 +6505,10 @@
         <v>400</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>390</v>
+        <v>716</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>6</v>
@@ -5970,10 +6530,10 @@
         <v>2000</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>438</v>
+        <v>751</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F6" s="10" t="n">
         <v>23</v>
@@ -5995,10 +6555,10 @@
         <v>1200</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>401</v>
+        <v>741</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>25</v>
@@ -6020,10 +6580,10 @@
         <v>1000</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>376</v>
+        <v>688</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>14</v>
@@ -6045,10 +6605,10 @@
         <v>1400</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>399</v>
+        <v>704</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>22</v>
@@ -6226,10 +6786,10 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="6">
@@ -6239,10 +6799,10 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>58</v>
+        <v>297</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.029</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="7">
@@ -6252,10 +6812,10 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>982</v>
+        <v>1324</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.49</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="8">
@@ -6265,10 +6825,10 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>962</v>
+        <v>1949</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>0.48</v>
+        <v>0.541</v>
       </c>
     </row>
   </sheetData>
@@ -6286,7 +6846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -6365,42 +6925,42 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Néstor Ricardo Jiménez Valencia</t>
+          <t>Natalia Gómez Jiménez</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Oportunidad (SQL)</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Camila Henao Salazar</t>
+          <t>Néstor Ricardo Jiménez Valencia</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Reunión o visita</t>
+          <t>Oportunidad (SQL)</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
@@ -6408,24 +6968,24 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>2027-03-17</t>
+          <t>2027-03-01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Ricardo Montoya Castaño</t>
+          <t>Camila Henao Salazar</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Opción o separación</t>
+          <t>Reunión o visita</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
@@ -6433,14 +6993,14 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>2027-04-19</t>
+          <t>2027-03-17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Daniel Mejía Torres</t>
+          <t>Ricardo Montoya Castaño</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -6450,7 +7010,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Reunión o visita</t>
+          <t>Opción o separación</t>
         </is>
       </c>
       <c r="D9" s="8" t="n">
@@ -6458,19 +7018,19 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2027-05-07</t>
+          <t>2027-04-19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Marcela Mónica Gómez Martínez</t>
+          <t>Daniel Mejía Torres</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -6483,19 +7043,19 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>2027-05-09</t>
+          <t>2027-05-07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Viviana Montoya Cardona</t>
+          <t>Marcela Mónica Gómez Martínez</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -6508,24 +7068,24 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2027-07-27</t>
+          <t>2027-05-09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Fernando Quintero Rojas</t>
+          <t>Viviana Montoya Cardona</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Venta</t>
+          <t>Reunión o visita</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
@@ -6533,14 +7093,14 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>2027-08-09</t>
+          <t>2027-07-27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Viviana Zapata Jiménez</t>
+          <t>Fernando Quintero Rojas</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -6550,7 +7110,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Opción o separación</t>
+          <t>Venta</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
@@ -6558,24 +7118,24 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-08-09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Julián Bedoya Cardona</t>
+          <t>Viviana Zapata Jiménez</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Reunión o visita</t>
+          <t>Opción o separación</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
@@ -6583,28 +7143,28 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>2027-10-17</t>
+          <t>2027-08-15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Héctor Duque Herrera</t>
+          <t>Julián Bedoya Cardona</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Venta</t>
+          <t>Reunión o visita</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
@@ -6615,17 +7175,17 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Laura Restrepo Jiménez</t>
+          <t>Héctor Duque Herrera</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Reunión o visita</t>
+          <t>Venta</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
@@ -6633,19 +7193,19 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>2027-04-04</t>
+          <t>2027-10-17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Iván Duque Ramírez</t>
+          <t>Laura Restrepo Jiménez</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -6658,19 +7218,19 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>2027-07-30</t>
+          <t>2027-04-04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Esteban Juan Betancur Montoya</t>
+          <t>Iván Duque Ramírez</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -6679,118 +7239,118 @@
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-07-30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Salazar Salazar</t>
+          <t>Natalia García</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Reunión o visita</t>
+          <t>Lead calificado (MQL)</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>2027-03-06</t>
+          <t>2027-10-19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Camilo Orozco Patiño</t>
+          <t>Felipe Martínez Ramírez</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Reunión o visita</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>2027-06-10</t>
+          <t>2027-02-03</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Claudia Moreno Betancur</t>
+          <t>Angela Cardona</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Reunión o visita</t>
+          <t>Opción o separación</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>2027-07-20</t>
+          <t>2027-02-28</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Diana Liliana Gil Londoño</t>
+          <t>Julián Londono</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Reunión o visita</t>
+          <t>Lead calificado (MQL)</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>2027-10-17</t>
+          <t>2027-03-30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Sebastián Alejandro Salazar Jiménez</t>
+          <t>Santiago García Pérez</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -6800,47 +7360,47 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Oportunidad (SQL)</t>
+          <t>Opción o separación</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Andrea Acosta Orozco</t>
+          <t>Francisco Muñoz Salazar</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Oportunidad (SQL)</t>
+          <t>Venta</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>2027-03-30</t>
+          <t>2027-08-02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Liliana Cardona Orozco</t>
+          <t>Daniela Velasco Jiménez</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -6850,22 +7410,22 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Venta</t>
+          <t>Opción o separación</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>2027-04-23</t>
+          <t>2027-01-06</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Juan Rojas Restrepo</t>
+          <t>Andrea Acosta</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -6875,27 +7435,27 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Oportunidad (SQL)</t>
+          <t>Lead calificado (MQL)</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2027-05-06</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Esteban Restrepo Giraldo</t>
+          <t>Martín Jiménez García</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -6904,68 +7464,68 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>2027-04-06</t>
+          <t>2027-08-04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Andrés Valencia Bedoya</t>
+          <t>Angela Velasco</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Oportunidad (SQL)</t>
+          <t>Lead calificado (MQL)</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>2027-04-08</t>
+          <t>2027-01-10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Ricardo Camilo Ruiz Cárdenas</t>
+          <t>Isabela Díaz</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Oportunidad (SQL)</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>2027-08-27</t>
+          <t>2027-04-16</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Carolina Viviana Correa Ríos</t>
+          <t>Esteban Juan Betancur Montoya</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -6975,27 +7535,27 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Oportunidad (SQL)</t>
+          <t>Reunión o visita</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>2027-08-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Diego Jorge Cárdenas Londoño</t>
+          <t>Gustavo Salazar Salazar</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -7004,18 +7564,18 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>2027-10-17</t>
+          <t>2027-03-06</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Diego Franco Duque</t>
+          <t>Camilo Orozco Patiño</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -7025,47 +7585,47 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Oportunidad (SQL)</t>
+          <t>Reunión o visita</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2027-06-10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Daniel Martínez Patiño</t>
+          <t>Claudia Moreno Betancur</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Oportunidad (SQL)</t>
+          <t>Reunión o visita</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>2027-05-12</t>
+          <t>2027-07-20</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Felipe Felipe Patiño Martínez</t>
+          <t>Diana Liliana Gil Londoño</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -7079,7 +7639,7 @@
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
@@ -7090,7 +7650,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Héctor Martínez Duque</t>
+          <t>Victoria Sánchez</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -7100,102 +7660,102 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Lead calificado (MQL)</t>
+          <t>Opción o separación</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2027-07-11</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Paola Diana Martínez Salazar</t>
+          <t>Julián Valencia Díaz</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Oportunidad (SQL)</t>
+          <t>Venta</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>2027-09-02</t>
+          <t>2027-03-19</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Carlos Vargas</t>
+          <t>Andrés Muñoz Jiménez</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Lead calificado (MQL)</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-02-02</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Jorge Diaz</t>
+          <t>Valentina Duque Jiménez</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Lead calificado (MQL)</t>
+          <t>Reunión o visita</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-01-22</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Felipe Jimenez</t>
+          <t>Sebastián Alejandro Salazar Jiménez</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -7204,23 +7764,23 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-03-03</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Alejandra Ramirez</t>
+          <t>Andrea Acosta Orozco</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -7229,18 +7789,18 @@
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-03-30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Maria Silva</t>
+          <t>Liliana Cardona Orozco</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -7250,27 +7810,27 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Venta</t>
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-04-23</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Hector Silva</t>
+          <t>Juan Rojas Restrepo</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -7279,18 +7839,18 @@
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-04-01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>Carlos Moreno</t>
+          <t>Esteban Restrepo Giraldo</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -7300,97 +7860,97 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Oportunidad (SQL)</t>
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-04-06</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Maria Rios</t>
+          <t>Andrés Valencia Bedoya</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Lead calificado (MQL)</t>
+          <t>Oportunidad (SQL)</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-04-08</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>Sebastian Rodriguez</t>
+          <t>Ricardo Camilo Ruiz Cárdenas</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Oportunidad (SQL)</t>
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-08-27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>Laura Gomez</t>
+          <t>Carolina Viviana Correa Ríos</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Oportunidad (SQL)</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-08-26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>Felipe Rios</t>
+          <t>Diego Jorge Cárdenas Londoño</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -7400,102 +7960,102 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Reunión o visita</t>
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-10-17</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Natalia Castro</t>
+          <t>Sofía Henao</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Oportunidad (SQL)</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-02-15</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Juliana Hernandez</t>
+          <t>David Duque Henao</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Lead calificado (MQL)</t>
+          <t>Oportunidad (SQL)</t>
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-06-16</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Carlos Morales</t>
+          <t>Alejandro Velasco</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Lead calificado (MQL)</t>
+          <t>Reunión o visita</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-05-26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Natalia Vega</t>
+          <t>Martín Henao Patiño</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -7504,18 +8064,18 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-01-26</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Fernando Romero</t>
+          <t>Daniela Mendoza Pérez</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -7529,198 +8089,198 @@
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-03-28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>Diana Lopez</t>
+          <t>Angela Mendoza Henao</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Lead calificado (MQL)</t>
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-03-28</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Ximena López</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Oportunidad (SQL)</t>
+          <t>Reunión o visita</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-08-29</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>Gabriela Cruz</t>
+          <t>Laura Valencia</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Opción o separación</t>
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-03-19</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Carolina Pena</t>
+          <t>Paula Cárdenas</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Lead calificado (MQL)</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-11-20</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>Juan Pena</t>
+          <t>Andrea García</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Lead calificado (MQL)</t>
+          <t>Opción o separación</t>
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-08-11</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Luis Reyes</t>
+          <t>Camila Gutiérrez</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Lead calificado (MQL)</t>
+          <t>Reunión o visita</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-03-12</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>Valentina Moreno</t>
+          <t>Ximena Duque</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Lead calificado (MQL)</t>
+          <t>Reunión o visita</t>
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-03-09</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Valentina Romero</t>
+          <t>Angela Salazar</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -7729,18 +8289,18 @@
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2027-09-07</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>Juan Pena</t>
+          <t>Carolina Velasco Ramírez</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -7750,40 +8310,6015 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Lead calificado (MQL)</t>
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-12-17</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
+          <t>Martín Henao</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Martín Londono Patiño</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>2027-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>Diego Franco Duque</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Lucía Castro Londono</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>2027-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>Paula Gutiérrez</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>David Ríos Díaz</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Elena Vargas</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>2027-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Héctor Vargas Moreno</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>2027-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>Francisco Gómez Velasco</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>2027-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>Daniela Díaz García</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>2027-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>Fernanda López Henao</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>2027-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>Carlos García</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>2027-01-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>Sofía Gutiérrez</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>Laura Castillo</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>Isabela Acosta</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>2027-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>Carolina Acosta Londono</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>Diego López</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>Daniel López</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>Natalia López Mora</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>Isabela Cárdenas Duque</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>2027-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Daniel Martínez Patiño</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>2027-05-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>Felipe Felipe Patiño Martínez</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>2027-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>Santiago Arias</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>2027-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>Felipe Arias Sánchez</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>Julián Vargas</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>2027-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>Fernanda Mendoza</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>Elena Valencia</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>2027-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>Elena Velasco</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>Laura Ríos</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>2027-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>Victoria Duque</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>Felipe Pérez</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>2027-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>David Ramírez</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>Carolina Duque Castillo</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>Héctor Torres Castro</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>Alejandro Castro Martínez</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>Julián Salazar</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>2027-02-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>Camila Acosta</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>Angela Gómez</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>Lucía Cardona</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>2027-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>Isabela Vargas</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>Diego Jiménez Cardona</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>Felipe Sánchez</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>2027-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>Sofía Arias Valencia</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>Andrés Cárdenas</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>2027-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>Camila Duque</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>Ximena Cardona</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>Valentina Londono Pérez</t>
+        </is>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>Diego Castillo</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>Valeria Jiménez</t>
+        </is>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>Paula Pérez</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>2027-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>Daniel Martínez Martínez</t>
+        </is>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E112" s="10" t="inlineStr">
+        <is>
+          <t>2027-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>Andrea Vargas García</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>Victoria Arias</t>
+        </is>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E114" s="10" t="inlineStr">
+        <is>
+          <t>2027-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>Martín Cárdenas</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>Daniela Patiño Velasco</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E116" s="10" t="inlineStr">
+        <is>
+          <t>2027-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>Julián Henao</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>Andrés Sánchez</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E118" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>Andrés Torres</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>Francisco Muñoz Mora</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E120" s="10" t="inlineStr">
+        <is>
+          <t>2027-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>Diego Cárdenas</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>Julián Ramírez</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E122" s="10" t="inlineStr">
+        <is>
+          <t>2027-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>Diego Cardona Acosta</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>Diego Vargas</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E124" s="10" t="inlineStr">
+        <is>
+          <t>2027-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>Andrés Mora</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>2027-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>Daniel Cárdenas</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E126" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>Julián Cardona</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>Sofía Franco López</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E128" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>Diego Valencia</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>2027-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>Sofía Londono</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E130" s="10" t="inlineStr">
+        <is>
+          <t>2027-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>Martín Castro</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
+          <t>2027-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>Angela Henao</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E132" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>Sofía Arias</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t>2027-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>Martín Gutiérrez Ríos</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E134" s="10" t="inlineStr">
+        <is>
+          <t>2027-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>Gabriela Duque</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E135" s="8" t="inlineStr">
+        <is>
+          <t>2027-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>Victoria Jiménez Valencia</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E136" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>Alejandro Cardona</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
+          <t>2027-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>Isabela Jiménez</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>2027-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>Héctor Ríos Pérez</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E139" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
+          <t>David Pérez Cárdenas</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E140" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>Fernanda Velasco</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>2027-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
+          <t>Lucía Patiño</t>
+        </is>
+      </c>
+      <c r="B142" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E142" s="10" t="inlineStr">
+        <is>
+          <t>2027-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>Felipe Acosta Cárdenas</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t>2027-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>Valentina Salazar</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>Valentina Muñoz</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E145" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>Mateo Franco Henao</t>
+        </is>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E146" s="10" t="inlineStr">
+        <is>
+          <t>2027-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>David Londono</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t>2027-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
+          <t>Victoria Cardona Velasco</t>
+        </is>
+      </c>
+      <c r="B148" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E148" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t>Daniel Torres Pérez</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D149" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E149" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="inlineStr">
+        <is>
+          <t>Gabriela Pérez Gómez</t>
+        </is>
+      </c>
+      <c r="B150" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D150" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E150" s="10" t="inlineStr">
+        <is>
+          <t>2027-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="8" t="inlineStr">
+        <is>
+          <t>Valentina Mendoza Salazar</t>
+        </is>
+      </c>
+      <c r="B151" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D151" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>Victoria López</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E152" s="10" t="inlineStr">
+        <is>
+          <t>2027-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>Mariana Martínez</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
+          <t>2027-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="10" t="inlineStr">
+        <is>
+          <t>Natalia Salazar</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E154" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>Mateo Gutiérrez</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E155" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="10" t="inlineStr">
+        <is>
+          <t>Pedro Mora Ramírez</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E156" s="10" t="inlineStr">
+        <is>
+          <t>2027-05-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="8" t="inlineStr">
+        <is>
+          <t>Valentina Ramírez Vargas</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D157" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="10" t="inlineStr">
+        <is>
+          <t>Daniela López Cardona</t>
+        </is>
+      </c>
+      <c r="B158" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E158" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t>Paula Castro</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D159" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E159" s="8" t="inlineStr">
+        <is>
+          <t>2027-04-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="10" t="inlineStr">
+        <is>
+          <t>Andrés Velasco</t>
+        </is>
+      </c>
+      <c r="B160" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E160" s="10" t="inlineStr">
+        <is>
+          <t>2027-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
+          <t>Santiago Ramírez</t>
+        </is>
+      </c>
+      <c r="B161" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D161" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E161" s="8" t="inlineStr">
+        <is>
+          <t>2027-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="10" t="inlineStr">
+        <is>
+          <t>Valentina Sánchez</t>
+        </is>
+      </c>
+      <c r="B162" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E162" s="10" t="inlineStr">
+        <is>
+          <t>2027-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="8" t="inlineStr">
+        <is>
+          <t>Mateo Torres</t>
+        </is>
+      </c>
+      <c r="B163" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E163" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="10" t="inlineStr">
+        <is>
+          <t>Miguel Patiño Velasco</t>
+        </is>
+      </c>
+      <c r="B164" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E164" s="10" t="inlineStr">
+        <is>
+          <t>2027-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t>David Patiño</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D165" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E165" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="10" t="inlineStr">
+        <is>
+          <t>Elena Martínez</t>
+        </is>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E166" s="10" t="inlineStr">
+        <is>
+          <t>2027-02-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="8" t="inlineStr">
+        <is>
+          <t>Daniel Duque</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D167" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E167" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="10" t="inlineStr">
+        <is>
+          <t>Héctor Díaz</t>
+        </is>
+      </c>
+      <c r="B168" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E168" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t>Mariana Valencia</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E169" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="10" t="inlineStr">
+        <is>
+          <t>Héctor Vargas</t>
+        </is>
+      </c>
+      <c r="B170" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E170" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="8" t="inlineStr">
+        <is>
+          <t>Miguel Duque</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C171" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D171" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E171" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="10" t="inlineStr">
+        <is>
+          <t>Sofía Mora Torres</t>
+        </is>
+      </c>
+      <c r="B172" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C172" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D172" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E172" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="8" t="inlineStr">
+        <is>
+          <t>Natalia Patiño</t>
+        </is>
+      </c>
+      <c r="B173" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D173" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E173" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="10" t="inlineStr">
+        <is>
+          <t>Laura Castillo</t>
+        </is>
+      </c>
+      <c r="B174" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C174" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D174" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E174" s="10" t="inlineStr">
+        <is>
+          <t>2027-05-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="8" t="inlineStr">
+        <is>
+          <t>Martín Muñoz</t>
+        </is>
+      </c>
+      <c r="B175" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C175" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D175" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E175" s="8" t="inlineStr">
+        <is>
+          <t>2027-01-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="10" t="inlineStr">
+        <is>
+          <t>Daniel Muñoz</t>
+        </is>
+      </c>
+      <c r="B176" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C176" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E176" s="10" t="inlineStr">
+        <is>
+          <t>2027-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="8" t="inlineStr">
+        <is>
+          <t>Paula Muñoz Castillo</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D177" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E177" s="8" t="inlineStr">
+        <is>
+          <t>2027-01-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="10" t="inlineStr">
+        <is>
+          <t>Martín Torres Muñoz</t>
+        </is>
+      </c>
+      <c r="B178" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C178" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D178" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E178" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>Elena Ríos</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D179" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E179" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="10" t="inlineStr">
+        <is>
+          <t>Andrea Velasco</t>
+        </is>
+      </c>
+      <c r="B180" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C180" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E180" s="10" t="inlineStr">
+        <is>
+          <t>2027-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="8" t="inlineStr">
+        <is>
+          <t>Daniela Arias</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D181" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E181" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="10" t="inlineStr">
+        <is>
+          <t>Andrés Torres Gutiérrez</t>
+        </is>
+      </c>
+      <c r="B182" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C182" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E182" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
+        <is>
+          <t>Julián Gutiérrez</t>
+        </is>
+      </c>
+      <c r="B183" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C183" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D183" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E183" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="10" t="inlineStr">
+        <is>
+          <t>Daniela Cardona</t>
+        </is>
+      </c>
+      <c r="B184" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E184" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="8" t="inlineStr">
+        <is>
+          <t>Daniel Franco</t>
+        </is>
+      </c>
+      <c r="B185" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C185" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D185" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E185" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="inlineStr">
+        <is>
+          <t>Sofía Mendoza</t>
+        </is>
+      </c>
+      <c r="B186" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C186" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E186" s="10" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="8" t="inlineStr">
+        <is>
+          <t>Felipe Franco</t>
+        </is>
+      </c>
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C187" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D187" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E187" s="8" t="inlineStr">
+        <is>
+          <t>2027-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="10" t="inlineStr">
+        <is>
+          <t>Victoria Pérez Mora</t>
+        </is>
+      </c>
+      <c r="B188" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C188" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D188" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E188" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="8" t="inlineStr">
+        <is>
+          <t>Elena García</t>
+        </is>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D189" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="10" t="inlineStr">
+        <is>
+          <t>Felipe García</t>
+        </is>
+      </c>
+      <c r="B190" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C190" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D190" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E190" s="10" t="inlineStr">
+        <is>
+          <t>2027-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="8" t="inlineStr">
+        <is>
+          <t>Daniela López Gómez</t>
+        </is>
+      </c>
+      <c r="B191" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C191" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D191" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E191" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="10" t="inlineStr">
+        <is>
+          <t>Sofía Vargas</t>
+        </is>
+      </c>
+      <c r="B192" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C192" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D192" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E192" s="10" t="inlineStr">
+        <is>
+          <t>2027-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="8" t="inlineStr">
+        <is>
+          <t>Victoria Castro Cárdenas</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C193" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D193" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E193" s="8" t="inlineStr">
+        <is>
+          <t>2027-01-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="10" t="inlineStr">
+        <is>
+          <t>Miguel Patiño</t>
+        </is>
+      </c>
+      <c r="B194" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C194" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D194" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E194" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="8" t="inlineStr">
+        <is>
+          <t>Angela Castillo Londono</t>
+        </is>
+      </c>
+      <c r="B195" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C195" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D195" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E195" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="10" t="inlineStr">
+        <is>
+          <t>Carolina Valencia</t>
+        </is>
+      </c>
+      <c r="B196" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C196" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D196" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E196" s="10" t="inlineStr">
+        <is>
+          <t>2027-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="8" t="inlineStr">
+        <is>
+          <t>Miguel Arias</t>
+        </is>
+      </c>
+      <c r="B197" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C197" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D197" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E197" s="8" t="inlineStr">
+        <is>
+          <t>2027-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="10" t="inlineStr">
+        <is>
+          <t>Valentina Mora</t>
+        </is>
+      </c>
+      <c r="B198" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C198" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D198" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E198" s="10" t="inlineStr">
+        <is>
+          <t>2027-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="8" t="inlineStr">
+        <is>
+          <t>Carolina López Arias</t>
+        </is>
+      </c>
+      <c r="B199" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C199" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D199" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E199" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="10" t="inlineStr">
+        <is>
+          <t>Santiago Arias</t>
+        </is>
+      </c>
+      <c r="B200" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C200" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D200" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E200" s="10" t="inlineStr">
+        <is>
+          <t>2027-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="8" t="inlineStr">
+        <is>
+          <t>Andrea Franco Gómez</t>
+        </is>
+      </c>
+      <c r="B201" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C201" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D201" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E201" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="10" t="inlineStr">
+        <is>
+          <t>Natalia Cárdenas</t>
+        </is>
+      </c>
+      <c r="B202" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C202" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D202" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E202" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="8" t="inlineStr">
+        <is>
+          <t>Camila Pérez</t>
+        </is>
+      </c>
+      <c r="B203" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D203" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E203" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="10" t="inlineStr">
+        <is>
+          <t>Pedro Martínez</t>
+        </is>
+      </c>
+      <c r="B204" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C204" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D204" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E204" s="10" t="inlineStr">
+        <is>
+          <t>2027-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="8" t="inlineStr">
+        <is>
+          <t>Miguel Castro</t>
+        </is>
+      </c>
+      <c r="B205" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C205" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D205" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E205" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="10" t="inlineStr">
+        <is>
+          <t>Valeria Gómez Gómez</t>
+        </is>
+      </c>
+      <c r="B206" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C206" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D206" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E206" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="8" t="inlineStr">
+        <is>
+          <t>Paula Torres Moreno</t>
+        </is>
+      </c>
+      <c r="B207" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C207" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D207" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E207" s="8" t="inlineStr">
+        <is>
+          <t>2027-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="10" t="inlineStr">
+        <is>
+          <t>Fernanda Duque</t>
+        </is>
+      </c>
+      <c r="B208" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C208" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D208" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E208" s="10" t="inlineStr">
+        <is>
+          <t>2027-03-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="8" t="inlineStr">
+        <is>
+          <t>Isabela Moreno</t>
+        </is>
+      </c>
+      <c r="B209" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C209" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D209" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E209" s="8" t="inlineStr">
+        <is>
+          <t>2027-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="10" t="inlineStr">
+        <is>
+          <t>Mateo Henao</t>
+        </is>
+      </c>
+      <c r="B210" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C210" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D210" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E210" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="8" t="inlineStr">
+        <is>
+          <t>Pedro Martínez</t>
+        </is>
+      </c>
+      <c r="B211" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D211" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E211" s="8" t="inlineStr">
+        <is>
+          <t>2027-02-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="10" t="inlineStr">
+        <is>
+          <t>Daniel Muñoz</t>
+        </is>
+      </c>
+      <c r="B212" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C212" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D212" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E212" s="10" t="inlineStr">
+        <is>
+          <t>2027-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="8" t="inlineStr">
+        <is>
+          <t>Diego Muñoz</t>
+        </is>
+      </c>
+      <c r="B213" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C213" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D213" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E213" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="10" t="inlineStr">
+        <is>
+          <t>David Moreno</t>
+        </is>
+      </c>
+      <c r="B214" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C214" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D214" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E214" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="8" t="inlineStr">
+        <is>
+          <t>Daniel Ramírez</t>
+        </is>
+      </c>
+      <c r="B215" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C215" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D215" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E215" s="8" t="inlineStr">
+        <is>
+          <t>2027-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="10" t="inlineStr">
+        <is>
+          <t>Elena Moreno</t>
+        </is>
+      </c>
+      <c r="B216" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C216" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D216" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E216" s="10" t="inlineStr">
+        <is>
+          <t>2027-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="8" t="inlineStr">
+        <is>
+          <t>Valeria Sánchez</t>
+        </is>
+      </c>
+      <c r="B217" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C217" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D217" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E217" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="10" t="inlineStr">
+        <is>
+          <t>Martín Acosta Duque</t>
+        </is>
+      </c>
+      <c r="B218" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C218" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D218" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E218" s="10" t="inlineStr">
+        <is>
+          <t>2027-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="8" t="inlineStr">
+        <is>
+          <t>Francisco Díaz</t>
+        </is>
+      </c>
+      <c r="B219" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C219" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D219" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E219" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="10" t="inlineStr">
+        <is>
+          <t>Laura Arias</t>
+        </is>
+      </c>
+      <c r="B220" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C220" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D220" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="E220" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="inlineStr">
+        <is>
+          <t>Andrés Henao</t>
+        </is>
+      </c>
+      <c r="B221" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C221" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D221" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E221" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="10" t="inlineStr">
+        <is>
+          <t>Héctor Martínez Duque</t>
+        </is>
+      </c>
+      <c r="B222" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C222" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D222" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E222" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="8" t="inlineStr">
+        <is>
+          <t>Paola Diana Martínez Salazar</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C223" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D223" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E223" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="10" t="inlineStr">
+        <is>
+          <t>Carlos Vargas</t>
+        </is>
+      </c>
+      <c r="B224" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C224" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D224" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E224" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="8" t="inlineStr">
+        <is>
+          <t>Jorge Diaz</t>
+        </is>
+      </c>
+      <c r="B225" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D225" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E225" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="10" t="inlineStr">
+        <is>
+          <t>Felipe Jimenez</t>
+        </is>
+      </c>
+      <c r="B226" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C226" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D226" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E226" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>Alejandra Ramirez</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E227" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="10" t="inlineStr">
+        <is>
+          <t>Maria Silva</t>
+        </is>
+      </c>
+      <c r="B228" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C228" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D228" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E228" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>Hector Silva</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C229" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D229" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E229" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="10" t="inlineStr">
+        <is>
+          <t>Carlos Moreno</t>
+        </is>
+      </c>
+      <c r="B230" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C230" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D230" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E230" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>Maria Rios</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C231" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D231" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E231" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="10" t="inlineStr">
+        <is>
+          <t>Sebastian Rodriguez</t>
+        </is>
+      </c>
+      <c r="B232" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C232" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D232" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E232" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="8" t="inlineStr">
+        <is>
+          <t>Laura Gomez</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D233" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E233" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="10" t="inlineStr">
+        <is>
+          <t>Felipe Rios</t>
+        </is>
+      </c>
+      <c r="B234" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C234" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D234" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E234" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="8" t="inlineStr">
+        <is>
+          <t>Natalia Castro</t>
+        </is>
+      </c>
+      <c r="B235" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C235" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D235" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E235" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="10" t="inlineStr">
+        <is>
+          <t>Juliana Hernandez</t>
+        </is>
+      </c>
+      <c r="B236" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C236" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D236" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E236" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Morales</t>
+        </is>
+      </c>
+      <c r="B237" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C237" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D237" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E237" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="10" t="inlineStr">
+        <is>
+          <t>Natalia Vega</t>
+        </is>
+      </c>
+      <c r="B238" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C238" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D238" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E238" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="8" t="inlineStr">
+        <is>
+          <t>Fernando Romero</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C239" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D239" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E239" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="10" t="inlineStr">
+        <is>
+          <t>Diana Lopez</t>
+        </is>
+      </c>
+      <c r="B240" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C240" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D240" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E240" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="8" t="inlineStr">
+        <is>
+          <t>Maria Garcia</t>
+        </is>
+      </c>
+      <c r="B241" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C241" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D241" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E241" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="10" t="inlineStr">
+        <is>
+          <t>Gabriela Cruz</t>
+        </is>
+      </c>
+      <c r="B242" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C242" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D242" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E242" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="8" t="inlineStr">
+        <is>
+          <t>Carolina Pena</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C243" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D243" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E243" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="10" t="inlineStr">
+        <is>
+          <t>Juan Pena</t>
+        </is>
+      </c>
+      <c r="B244" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C244" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D244" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E244" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="8" t="inlineStr">
+        <is>
+          <t>Luis Reyes</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C245" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D245" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E245" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="10" t="inlineStr">
+        <is>
+          <t>Valentina Moreno</t>
+        </is>
+      </c>
+      <c r="B246" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C246" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D246" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E246" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="8" t="inlineStr">
+        <is>
+          <t>Valentina Romero</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C247" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D247" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E247" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="10" t="inlineStr">
+        <is>
+          <t>Juan Pena</t>
+        </is>
+      </c>
+      <c r="B248" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C248" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D248" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E248" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="8" t="inlineStr">
+        <is>
           <t>Daniela Rojas</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B249" s="8" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C249" s="8" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D62" s="10" t="n">
+      <c r="D249" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="E249" s="8" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="10" t="inlineStr">
+        <is>
+          <t>Elena Martínez</t>
+        </is>
+      </c>
+      <c r="B250" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C250" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D250" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E250" s="10" t="inlineStr">
+        <is>
+          <t>2027-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="8" t="inlineStr">
+        <is>
+          <t>Camila Pérez Vargas</t>
+        </is>
+      </c>
+      <c r="B251" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C251" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D251" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E251" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="10" t="inlineStr">
+        <is>
+          <t>Carlos Acosta</t>
+        </is>
+      </c>
+      <c r="B252" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C252" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D252" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E252" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="8" t="inlineStr">
+        <is>
+          <t>Valentina Mendoza</t>
+        </is>
+      </c>
+      <c r="B253" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C253" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D253" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E253" s="8" t="inlineStr">
+        <is>
+          <t>2027-04-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="10" t="inlineStr">
+        <is>
+          <t>Angela Acosta</t>
+        </is>
+      </c>
+      <c r="B254" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C254" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D254" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E254" s="10" t="inlineStr">
+        <is>
+          <t>2027-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="8" t="inlineStr">
+        <is>
+          <t>Sofía López</t>
+        </is>
+      </c>
+      <c r="B255" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C255" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D255" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E255" s="8" t="inlineStr">
+        <is>
+          <t>2027-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="10" t="inlineStr">
+        <is>
+          <t>Isabela Velasco</t>
+        </is>
+      </c>
+      <c r="B256" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C256" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D256" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E256" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="8" t="inlineStr">
+        <is>
+          <t>Alejandro Ríos</t>
+        </is>
+      </c>
+      <c r="B257" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C257" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D257" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E257" s="8" t="inlineStr">
+        <is>
+          <t>2027-04-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="inlineStr">
+        <is>
+          <t>Alejandro Salazar Acosta</t>
+        </is>
+      </c>
+      <c r="B258" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C258" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D258" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E258" s="10" t="inlineStr">
+        <is>
+          <t>2027-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="8" t="inlineStr">
+        <is>
+          <t>Gabriela Muñoz</t>
+        </is>
+      </c>
+      <c r="B259" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C259" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D259" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E259" s="8" t="inlineStr">
+        <is>
+          <t>2027-04-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="10" t="inlineStr">
+        <is>
+          <t>Carlos Franco Arias</t>
+        </is>
+      </c>
+      <c r="B260" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C260" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D260" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E260" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="8" t="inlineStr">
+        <is>
+          <t>Santiago Díaz</t>
+        </is>
+      </c>
+      <c r="B261" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C261" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D261" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E261" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="10" t="inlineStr">
+        <is>
+          <t>Carlos Ríos</t>
+        </is>
+      </c>
+      <c r="B262" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C262" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D262" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E262" s="10" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="8" t="inlineStr">
+        <is>
+          <t>Fernanda Franco</t>
+        </is>
+      </c>
+      <c r="B263" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C263" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D263" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E263" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="10" t="inlineStr">
+        <is>
+          <t>Mariana Valencia</t>
+        </is>
+      </c>
+      <c r="B264" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C264" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D264" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E264" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="8" t="inlineStr">
+        <is>
+          <t>Pedro Pérez Cárdenas</t>
+        </is>
+      </c>
+      <c r="B265" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C265" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D265" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E265" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="10" t="inlineStr">
+        <is>
+          <t>Carlos Velasco</t>
+        </is>
+      </c>
+      <c r="B266" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C266" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D266" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E266" s="10" t="inlineStr">
+        <is>
+          <t>2027-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="8" t="inlineStr">
+        <is>
+          <t>Valeria Muñoz Londono</t>
+        </is>
+      </c>
+      <c r="B267" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C267" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D267" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E267" s="8" t="inlineStr">
+        <is>
+          <t>2027-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="10" t="inlineStr">
+        <is>
+          <t>Lucía Vargas</t>
+        </is>
+      </c>
+      <c r="B268" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C268" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D268" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E268" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="8" t="inlineStr">
+        <is>
+          <t>Santiago Mora</t>
+        </is>
+      </c>
+      <c r="B269" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C269" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D269" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E269" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="10" t="inlineStr">
+        <is>
+          <t>Daniela Díaz García</t>
+        </is>
+      </c>
+      <c r="B270" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C270" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D270" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E270" s="10" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="8" t="inlineStr">
+        <is>
+          <t>Pedro Muñoz</t>
+        </is>
+      </c>
+      <c r="B271" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C271" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D271" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E271" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="10" t="inlineStr">
+        <is>
+          <t>Santiago Gómez</t>
+        </is>
+      </c>
+      <c r="B272" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C272" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D272" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E272" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="8" t="inlineStr">
+        <is>
+          <t>Gabriela Henao</t>
+        </is>
+      </c>
+      <c r="B273" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C273" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D273" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E273" s="8" t="inlineStr">
+        <is>
+          <t>2027-05-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="10" t="inlineStr">
+        <is>
+          <t>Paula Cárdenas</t>
+        </is>
+      </c>
+      <c r="B274" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C274" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D274" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E274" s="10" t="inlineStr">
+        <is>
+          <t>2027-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="8" t="inlineStr">
+        <is>
+          <t>Angela García Mora</t>
+        </is>
+      </c>
+      <c r="B275" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C275" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D275" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E275" s="8" t="inlineStr">
+        <is>
+          <t>2027-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="10" t="inlineStr">
+        <is>
+          <t>Carlos Patiño</t>
+        </is>
+      </c>
+      <c r="B276" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C276" s="10" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D276" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E276" s="10" t="inlineStr">
+        <is>
+          <t>2027-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="8" t="inlineStr">
+        <is>
+          <t>Valeria Henao</t>
+        </is>
+      </c>
+      <c r="B277" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C277" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D277" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E277" s="8" t="inlineStr">
+        <is>
+          <t>2027-02-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="10" t="inlineStr">
+        <is>
+          <t>Angela Martínez Sánchez</t>
+        </is>
+      </c>
+      <c r="B278" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C278" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D278" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E278" s="10" t="inlineStr">
+        <is>
+          <t>2027-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="8" t="inlineStr">
+        <is>
+          <t>Fernanda Moreno</t>
+        </is>
+      </c>
+      <c r="B279" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C279" s="8" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D279" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E279" s="8" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="10" t="inlineStr">
+        <is>
+          <t>Santiago Gómez</t>
+        </is>
+      </c>
+      <c r="B280" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C280" s="10" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D280" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E280" s="10" t="inlineStr">
+        <is>
+          <t>2027-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="8" t="inlineStr">
+        <is>
+          <t>Ximena Vargas Jiménez</t>
+        </is>
+      </c>
+      <c r="B281" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C281" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D281" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E281" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="10" t="inlineStr">
+        <is>
+          <t>Santiago Duque</t>
+        </is>
+      </c>
+      <c r="B282" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C282" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D282" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E282" s="10" t="inlineStr">
+        <is>
+          <t>2027-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="8" t="inlineStr">
+        <is>
+          <t>Martín Sánchez</t>
+        </is>
+      </c>
+      <c r="B283" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C283" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D283" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E283" s="8" t="inlineStr">
+        <is>
+          <t>2027-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="10" t="inlineStr">
+        <is>
+          <t>Diego Franco</t>
+        </is>
+      </c>
+      <c r="B284" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C284" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D284" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E284" s="10" t="inlineStr">
+        <is>
+          <t>2027-02-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="8" t="inlineStr">
+        <is>
+          <t>Mariana García Muñoz</t>
+        </is>
+      </c>
+      <c r="B285" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C285" s="8" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D285" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E285" s="8" t="inlineStr">
+        <is>
+          <t>2027-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="10" t="inlineStr">
+        <is>
+          <t>Pedro Pérez</t>
+        </is>
+      </c>
+      <c r="B286" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C286" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D286" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E286" s="10" t="inlineStr">
+        <is>
+          <t>2027-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="8" t="inlineStr">
+        <is>
+          <t>Héctor Henao Londono</t>
+        </is>
+      </c>
+      <c r="B287" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C287" s="8" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D287" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E287" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="10" t="inlineStr">
+        <is>
+          <t>Daniel Franco</t>
+        </is>
+      </c>
+      <c r="B288" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C288" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D288" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E288" s="10" t="inlineStr">
+        <is>
+          <t>2027-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="8" t="inlineStr">
+        <is>
+          <t>Angela Cárdenas Arias</t>
+        </is>
+      </c>
+      <c r="B289" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C289" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D289" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E289" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="10" t="inlineStr">
+        <is>
+          <t>Isabela Valencia</t>
+        </is>
+      </c>
+      <c r="B290" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C290" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D290" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E290" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="8" t="inlineStr">
+        <is>
+          <t>Mariana Sánchez Valencia</t>
+        </is>
+      </c>
+      <c r="B291" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C291" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D291" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E291" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="10" t="inlineStr">
+        <is>
+          <t>Santiago Vargas Mendoza</t>
+        </is>
+      </c>
+      <c r="B292" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C292" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D292" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E292" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="8" t="inlineStr">
+        <is>
+          <t>Carolina Jiménez</t>
+        </is>
+      </c>
+      <c r="B293" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C293" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D293" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E293" s="8" t="inlineStr">
+        <is>
+          <t>2027-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="10" t="inlineStr">
+        <is>
+          <t>Felipe García</t>
+        </is>
+      </c>
+      <c r="B294" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C294" s="10" t="inlineStr">
+        <is>
+          <t>Opción o separación</t>
+        </is>
+      </c>
+      <c r="D294" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E294" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Duque</t>
+        </is>
+      </c>
+      <c r="B295" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C295" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D295" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E295" s="8" t="inlineStr">
+        <is>
+          <t>2027-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="10" t="inlineStr">
+        <is>
+          <t>Carlos Torres Ramírez</t>
+        </is>
+      </c>
+      <c r="B296" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C296" s="10" t="inlineStr">
+        <is>
+          <t>Oportunidad (SQL)</t>
+        </is>
+      </c>
+      <c r="D296" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E296" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="8" t="inlineStr">
+        <is>
+          <t>Camila Mendoza</t>
+        </is>
+      </c>
+      <c r="B297" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C297" s="8" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D297" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E297" s="8" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="10" t="inlineStr">
+        <is>
+          <t>Natalia Velasco Vargas</t>
+        </is>
+      </c>
+      <c r="B298" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C298" s="10" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D298" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E298" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="8" t="inlineStr">
+        <is>
+          <t>Victoria López</t>
+        </is>
+      </c>
+      <c r="B299" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C299" s="8" t="inlineStr">
+        <is>
+          <t>Lead calificado (MQL)</t>
+        </is>
+      </c>
+      <c r="D299" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E299" s="8" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="10" t="inlineStr">
+        <is>
+          <t>Francisco Ramírez Henao</t>
+        </is>
+      </c>
+      <c r="B300" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C300" s="10" t="inlineStr">
+        <is>
+          <t>Reunión o visita</t>
+        </is>
+      </c>
+      <c r="D300" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E300" s="10" t="inlineStr">
+        <is>
+          <t>2027-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="8" t="inlineStr">
+        <is>
+          <t>Gabriela García</t>
+        </is>
+      </c>
+      <c r="B301" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C301" s="8" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D301" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E301" s="8" t="inlineStr">
+        <is>
+          <t>2027-07-11</t>
         </is>
       </c>
     </row>

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -147,8 +147,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5670,7 +5670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="59" customWidth="1" min="1" max="1"/>
@@ -5690,7 +5690,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Los valores corresponden a la base: una muestra; las metas son del plan a 12 meses.</t>
+          <t>Metas del plan a 12 meses a partir de la base de 3.600 leads potenciales.</t>
         </is>
       </c>
     </row>
@@ -5740,110 +5740,102 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Base de ejemplo (muestra para el ejercicio); meta anual del plan: 6.000</t>
+          <t>Base de ejemplo (3.600 leads potenciales); meta anual del plan: 6.000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Suites vendidas</t>
+          <t>Ventas (meta mensual)</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>90</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C6" s="10" t="n"/>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Por debajo de la meta (muestra)</t>
+          <t>Informativo</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>Muestra de ejemplo; meta del plan: 90 suites en 12 meses</t>
+          <t>Meta del plan: 6 suites vendidas por mes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Conversión lead a venta</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>0.015</v>
-      </c>
+          <t>Ventas (meta anual)</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="C7" s="8" t="n"/>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Por debajo de la meta (muestra)</t>
+          <t>Informativo</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Alineada con la meta del plan (1,5%)</t>
+          <t>Meta del plan: 72 suites en 12 meses (6 por mes)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Leads por referidos</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>0.1422</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>Cumple</t>
+          <t>Inventario a vender (meta)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Informativo</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>9,5% vs meta 10%: muy cerca</t>
+          <t>72 suites de las 180 del inventario (40%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Clientes con autorización vigente o revocada documentada</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Cumple</t>
+          <t>Conversión lead a venta (meta)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Informativo</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>100% de clientes con consentimiento documentado (Ley 1581)</t>
+          <t>72 ventas / 3.600 leads potenciales (2%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Valor vendido (COP millones)</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>1148</v>
+          <t>Leads por Meta Business (meta)</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>0.4</v>
       </c>
       <c r="C10" s="10" t="n"/>
       <c r="D10" s="9" t="inlineStr">
@@ -5853,7 +5845,72 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>Promesas/escrituras + opciones en curso</t>
+          <t>Meta: 40% de los leads desde el formulario de Meta Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Leads por WhatsApp (meta)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Informativo</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Meta: 60% de los leads desde WhatsApp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Valor vendido (meta mensual, COP millones)</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Informativo</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>6 ventas mensuales presupuestadas × 350 M COP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Clientes con autorización vigente o revocada documentada</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>100% de clientes con consentimiento documentado (Ley 1581)</t>
         </is>
       </c>
     </row>
@@ -5935,8 +5992,8 @@
       <c r="C5" s="8" t="n">
         <v>3600</v>
       </c>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
@@ -5950,10 +6007,10 @@
       <c r="C6" s="10" t="n">
         <v>2344</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="11" t="n">
         <v>0.651</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -5969,10 +6026,10 @@
       <c r="C7" s="8" t="n">
         <v>1437</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>0.613</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5988,10 +6045,10 @@
       <c r="C8" s="10" t="n">
         <v>840</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="11" t="n">
         <v>0.585</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="11" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6007,10 +6064,10 @@
       <c r="C9" s="8" t="n">
         <v>562</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>0.669</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -6026,10 +6083,10 @@
       <c r="C10" s="10" t="n">
         <v>274</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="11" t="n">
         <v>0.488</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="11" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -6788,7 +6845,7 @@
       <c r="B5" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>0.008</v>
       </c>
     </row>
@@ -6801,7 +6858,7 @@
       <c r="B6" s="10" t="n">
         <v>297</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="11" t="n">
         <v>0.083</v>
       </c>
     </row>
@@ -6814,7 +6871,7 @@
       <c r="B7" s="8" t="n">
         <v>1324</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -6827,7 +6884,7 @@
       <c r="B8" s="10" t="n">
         <v>1949</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="11" t="n">
         <v>0.541</v>
       </c>
     </row>

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -5934,22 +5934,22 @@
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Embudo de ventas: conversión real vs meta</t>
+          <t>Embudo de ventas: metas por etapa</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Meta del plan: 1.000 leads/mes (6.000 en 12 meses). La base es una muestra.</t>
+          <t>Metas a partir de 3.600 leads: 72 ventas en 12 meses (2% de conversion total).</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>leads_que_llegaron</t>
+          <t>leads_meta</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>conversion_real</t>
+          <t>conversion_acumulada</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>2344</v>
+        <v>1440</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0.651</v>
+        <v>0.4</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>0.4</v>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>1437</v>
+        <v>720</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>0.613</v>
+        <v>0.2</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>0.5</v>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>840</v>
+        <v>360</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.585</v>
+        <v>0.1</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>0.5</v>
@@ -6062,13 +6062,13 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>562</v>
+        <v>144</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.669</v>
+        <v>0.04</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10">
@@ -6081,13 +6081,13 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>274</v>
+        <v>72</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>0.488</v>
+        <v>0.02</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -94,12 +94,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -147,9 +147,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fecha del informe: 21/10/2026</t>
+          <t>Fecha del informe: 22/10/2026</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
     <col width="59" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -5728,19 +5728,19 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
+        <v>3601</v>
+      </c>
+      <c r="C5" s="8" t="n">
         <v>3600</v>
       </c>
-      <c r="C5" s="8" t="n">
-        <v>6000</v>
-      </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Por debajo de la meta (muestra)</t>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Base de ejemplo (3.600 leads potenciales); meta anual del plan: 6.000</t>
+          <t>Base de ejemplo (3.600 leads potenciales); meta anual del plan: 3600</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="10" t="n"/>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
@@ -5775,7 +5775,7 @@
         <v>72</v>
       </c>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
@@ -5792,11 +5792,11 @@
           <t>Inventario a vender (meta)</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
         <v>0.4</v>
       </c>
       <c r="C8" s="10" t="n"/>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
@@ -5813,11 +5813,11 @@
           <t>Conversión lead a venta (meta)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>0.02</v>
       </c>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
@@ -5834,18 +5834,18 @@
           <t>Leads por Meta Business (meta)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
-        <v>0.4</v>
+      <c r="B10" s="12" t="n">
+        <v>0.6</v>
       </c>
       <c r="C10" s="10" t="n"/>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>Meta: 40% de los leads desde el formulario de Meta Business</t>
+          <t>Meta: 60% de los leads desde el formulario de Meta Business</t>
         </is>
       </c>
     </row>
@@ -5855,18 +5855,18 @@
           <t>Leads por WhatsApp (meta)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
-        <v>0.6</v>
+      <c r="B11" s="13" t="n">
+        <v>0.4</v>
       </c>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Meta: 60% de los leads desde WhatsApp</t>
+          <t>Meta: 40% de los leads desde WhatsApp</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
         <v>2100</v>
       </c>
       <c r="C12" s="10" t="n"/>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Informativo</t>
         </is>
@@ -5897,13 +5897,13 @@
           <t>Clientes con autorización vigente o revocada documentada</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Cumple</t>
         </is>
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>3600</v>
-      </c>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
+        <v>3601</v>
+      </c>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
@@ -6007,10 +6007,10 @@
       <c r="C6" s="10" t="n">
         <v>1440</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>0.4</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -6026,10 +6026,10 @@
       <c r="C7" s="8" t="n">
         <v>720</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="13" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6045,10 +6045,10 @@
       <c r="C8" s="10" t="n">
         <v>360</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6064,10 +6064,10 @@
       <c r="C9" s="8" t="n">
         <v>144</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="13" t="n">
         <v>0.04</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="13" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -6083,10 +6083,10 @@
       <c r="C10" s="10" t="n">
         <v>72</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>322</v>
@@ -6248,7 +6248,7 @@
         <v>34</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="10">
@@ -6371,7 +6371,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>167</v>
@@ -6562,7 +6562,7 @@
         <v>400</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>54</v>
@@ -6845,7 +6845,7 @@
       <c r="B5" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="13" t="n">
         <v>0.008</v>
       </c>
     </row>
@@ -6858,8 +6858,8 @@
       <c r="B6" s="10" t="n">
         <v>297</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>0.083</v>
+      <c r="C6" s="12" t="n">
+        <v>0.082</v>
       </c>
     </row>
     <row r="7">
@@ -6869,9 +6869,9 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1324</v>
-      </c>
-      <c r="C7" s="12" t="n">
+        <v>1325</v>
+      </c>
+      <c r="C7" s="13" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       <c r="B8" s="10" t="n">
         <v>1949</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>0.541</v>
       </c>
     </row>

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -70,7 +70,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -95,11 +95,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -147,7 +142,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5676,7 +5670,7 @@
     <col width="59" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -5753,10 +5747,12 @@
       <c r="B6" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Informativo</t>
+      <c r="C6" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -5774,10 +5770,12 @@
       <c r="B7" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Informativo</t>
+      <c r="C7" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -5792,13 +5790,15 @@
           <t>Inventario a vender (meta)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="11" t="n">
         <v>0.4</v>
       </c>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Informativo</t>
+      <c r="C8" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -5813,13 +5813,15 @@
           <t>Conversión lead a venta (meta)</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Informativo</t>
+      <c r="C9" s="8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -5834,13 +5836,15 @@
           <t>Leads por Meta Business (meta)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="11" t="n">
         <v>0.6</v>
       </c>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Informativo</t>
+      <c r="C10" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -5855,13 +5859,15 @@
           <t>Leads por WhatsApp (meta)</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="12" t="n">
         <v>0.4</v>
       </c>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Informativo</t>
+      <c r="C11" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -5879,10 +5885,12 @@
       <c r="B12" s="10" t="n">
         <v>2100</v>
       </c>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Informativo</t>
+      <c r="C12" s="10" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -5897,7 +5905,7 @@
           <t>Clientes con autorización vigente o revocada documentada</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="8" t="n">
@@ -5992,8 +6000,8 @@
       <c r="C5" s="8" t="n">
         <v>3601</v>
       </c>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
@@ -6007,10 +6015,10 @@
       <c r="C6" s="10" t="n">
         <v>1440</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="11" t="n">
         <v>0.4</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -6026,10 +6034,10 @@
       <c r="C7" s="8" t="n">
         <v>720</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="12" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6045,10 +6053,10 @@
       <c r="C8" s="10" t="n">
         <v>360</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="11" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6064,10 +6072,10 @@
       <c r="C9" s="8" t="n">
         <v>144</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="12" t="n">
         <v>0.04</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="12" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -6083,10 +6091,10 @@
       <c r="C10" s="10" t="n">
         <v>72</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="11" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6171,7 +6179,7 @@
       <c r="D5" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="13" t="n">
         <v>0.0716</v>
       </c>
     </row>
@@ -6190,7 +6198,7 @@
       <c r="D6" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="14" t="n">
         <v>0.0683</v>
       </c>
     </row>
@@ -6209,7 +6217,7 @@
       <c r="D7" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="13" t="n">
         <v>0.0781</v>
       </c>
     </row>
@@ -6228,7 +6236,7 @@
       <c r="D8" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="14" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -6247,7 +6255,7 @@
       <c r="D9" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="13" t="n">
         <v>0.068</v>
       </c>
     </row>
@@ -6266,7 +6274,7 @@
       <c r="D10" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="14" t="n">
         <v>0.0694</v>
       </c>
     </row>
@@ -6285,7 +6293,7 @@
       <c r="D11" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="13" t="n">
         <v>0.0784</v>
       </c>
     </row>
@@ -6845,7 +6853,7 @@
       <c r="B5" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="12" t="n">
         <v>0.008</v>
       </c>
     </row>
@@ -6858,7 +6866,7 @@
       <c r="B6" s="10" t="n">
         <v>297</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="11" t="n">
         <v>0.082</v>
       </c>
     </row>
@@ -6871,7 +6879,7 @@
       <c r="B7" s="8" t="n">
         <v>1325</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="12" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -6884,7 +6892,7 @@
       <c r="B8" s="10" t="n">
         <v>1949</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="11" t="n">
         <v>0.541</v>
       </c>
     </row>

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>72 ventas / 3.600 leads potenciales (2%)</t>
+          <t>72 ventas / 3.600 leads potenciales (1.6%)</t>
         </is>
       </c>
     </row>

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -70,7 +70,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +95,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -124,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,10 +145,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -714,33 +720,33 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Ricardo Montoya Castaño</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Opción</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>2027-04-28</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <v>374</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Piso 7 HAB-02</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Andrés Giraldo</t>
         </is>
@@ -780,33 +786,33 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Fernando Quintero Rojas</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Promesa</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>2027-08-12</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="11" t="n">
         <v>379</v>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Piso 12 HAB-02</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Andrés Giraldo</t>
         </is>
@@ -926,20 +932,20 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
         <v>186</v>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Ricardo Carlos Vargas Restrepo</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>2027-10-10</t>
         </is>
@@ -962,20 +968,20 @@
       <c r="D7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
         <v>212</v>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Hector Martinez</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n"/>
+      <c r="D8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -994,20 +1000,20 @@
       <c r="D9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
         <v>220</v>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Carolina Martinez</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n"/>
+      <c r="D10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -1026,20 +1032,20 @@
       <c r="D11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
         <v>236</v>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Camila Vega</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n"/>
+      <c r="D12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -1058,20 +1064,20 @@
       <c r="D13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
         <v>241</v>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Paula Jimenez</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n"/>
+      <c r="D14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -1090,20 +1096,20 @@
       <c r="D15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
         <v>272</v>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>David Romero</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n"/>
+      <c r="D16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -1122,20 +1128,20 @@
       <c r="D17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
         <v>278</v>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Diego Romero</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n"/>
+      <c r="D18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -1154,20 +1160,20 @@
       <c r="D19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
         <v>288</v>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Mariana Ruiz</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n"/>
+      <c r="D20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1186,20 +1192,20 @@
       <c r="D21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="n">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
         <v>315</v>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Lina Lopez</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n"/>
+      <c r="D22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -1218,20 +1224,20 @@
       <c r="D23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="n">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
         <v>323</v>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>Natalia Flores</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n"/>
+      <c r="D24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -1250,20 +1256,20 @@
       <c r="D25" s="8" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="n">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
         <v>338</v>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>Maria Flores</t>
         </is>
       </c>
-      <c r="D26" s="10" t="n"/>
+      <c r="D26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1282,20 +1288,20 @@
       <c r="D27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
         <v>346</v>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>Carlos Moreno</t>
         </is>
       </c>
-      <c r="D28" s="10" t="n"/>
+      <c r="D28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -1314,20 +1320,20 @@
       <c r="D29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
         <v>352</v>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Paula Gutierrez</t>
         </is>
       </c>
-      <c r="D30" s="10" t="n"/>
+      <c r="D30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -1346,20 +1352,20 @@
       <c r="D31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
         <v>368</v>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Gabriela Ortiz</t>
         </is>
       </c>
-      <c r="D32" s="10" t="n"/>
+      <c r="D32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -1378,20 +1384,20 @@
       <c r="D33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
         <v>371</v>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>Mariana Romero</t>
         </is>
       </c>
-      <c r="D34" s="10" t="n"/>
+      <c r="D34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -1410,20 +1416,20 @@
       <c r="D35" s="8" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
         <v>402</v>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>Sofia Garcia</t>
         </is>
       </c>
-      <c r="D36" s="10" t="n"/>
+      <c r="D36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -1442,20 +1448,20 @@
       <c r="D37" s="8" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
         <v>409</v>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>Ricardo Martinez</t>
         </is>
       </c>
-      <c r="D38" s="10" t="n"/>
+      <c r="D38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -1474,20 +1480,20 @@
       <c r="D39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
         <v>415</v>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Miguel Cruz</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n"/>
+      <c r="D40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -1506,20 +1512,20 @@
       <c r="D41" s="8" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="n">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
         <v>420</v>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>Jorge Vargas</t>
         </is>
       </c>
-      <c r="D42" s="10" t="n"/>
+      <c r="D42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -1538,20 +1544,20 @@
       <c r="D43" s="8" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="n">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
         <v>428</v>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>Natalia Cruz</t>
         </is>
       </c>
-      <c r="D44" s="10" t="n"/>
+      <c r="D44" s="11" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -1570,20 +1576,20 @@
       <c r="D45" s="8" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
         <v>435</v>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>Daniela Romero</t>
         </is>
       </c>
-      <c r="D46" s="10" t="n"/>
+      <c r="D46" s="11" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -1602,20 +1608,20 @@
       <c r="D47" s="8" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="n">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
         <v>443</v>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>Felipe Vega</t>
         </is>
       </c>
-      <c r="D48" s="10" t="n"/>
+      <c r="D48" s="11" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -1634,20 +1640,20 @@
       <c r="D49" s="8" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="n">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
         <v>455</v>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>Paula Rojas</t>
         </is>
       </c>
-      <c r="D50" s="10" t="n"/>
+      <c r="D50" s="11" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -1666,20 +1672,20 @@
       <c r="D51" s="8" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="n">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
         <v>465</v>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>Lina Moreno</t>
         </is>
       </c>
-      <c r="D52" s="10" t="n"/>
+      <c r="D52" s="11" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -1698,20 +1704,20 @@
       <c r="D53" s="8" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="n">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
         <v>469</v>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>Natalia Vargas</t>
         </is>
       </c>
-      <c r="D54" s="10" t="n"/>
+      <c r="D54" s="11" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -1730,20 +1736,20 @@
       <c r="D55" s="8" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="n">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
         <v>515</v>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>Cesar Ramirez</t>
         </is>
       </c>
-      <c r="D56" s="10" t="n"/>
+      <c r="D56" s="11" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -1762,20 +1768,20 @@
       <c r="D57" s="8" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="n">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
         <v>521</v>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>Andres Flores</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n"/>
+      <c r="D58" s="11" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -1794,20 +1800,20 @@
       <c r="D59" s="8" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="n">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
         <v>529</v>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>Maria Hernandez</t>
         </is>
       </c>
-      <c r="D60" s="10" t="n"/>
+      <c r="D60" s="11" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -1826,20 +1832,20 @@
       <c r="D61" s="8" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="n">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
         <v>539</v>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>Luis Ramirez</t>
         </is>
       </c>
-      <c r="D62" s="10" t="n"/>
+      <c r="D62" s="11" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -1858,20 +1864,20 @@
       <c r="D63" s="8" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="n">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
         <v>552</v>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>Daniela Castro</t>
         </is>
       </c>
-      <c r="D64" s="10" t="n"/>
+      <c r="D64" s="11" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -1890,20 +1896,20 @@
       <c r="D65" s="8" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B66" s="10" t="n">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
         <v>557</v>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>Lina Rojas</t>
         </is>
       </c>
-      <c r="D66" s="10" t="n"/>
+      <c r="D66" s="11" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -1922,20 +1928,20 @@
       <c r="D67" s="8" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="n">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
         <v>577</v>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>Daniela Romero</t>
         </is>
       </c>
-      <c r="D68" s="10" t="n"/>
+      <c r="D68" s="11" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -1954,20 +1960,20 @@
       <c r="D69" s="8" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="n">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
         <v>593</v>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>Mariana Hernandez</t>
         </is>
       </c>
-      <c r="D70" s="10" t="n"/>
+      <c r="D70" s="11" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
@@ -1986,20 +1992,20 @@
       <c r="D71" s="8" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="n">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
         <v>615</v>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="11" t="inlineStr">
         <is>
           <t>Sofia Mendoza</t>
         </is>
       </c>
-      <c r="D72" s="10" t="n"/>
+      <c r="D72" s="11" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
@@ -2018,20 +2024,20 @@
       <c r="D73" s="8" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="n">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n">
         <v>654</v>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C74" s="11" t="inlineStr">
         <is>
           <t>Diego Cruz</t>
         </is>
       </c>
-      <c r="D74" s="10" t="n"/>
+      <c r="D74" s="11" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
@@ -2050,20 +2056,20 @@
       <c r="D75" s="8" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="n">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n">
         <v>659</v>
       </c>
-      <c r="C76" s="10" t="inlineStr">
+      <c r="C76" s="11" t="inlineStr">
         <is>
           <t>Sofia Jimenez</t>
         </is>
       </c>
-      <c r="D76" s="10" t="n"/>
+      <c r="D76" s="11" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
@@ -2082,20 +2088,20 @@
       <c r="D77" s="8" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="n">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n">
         <v>684</v>
       </c>
-      <c r="C78" s="10" t="inlineStr">
+      <c r="C78" s="11" t="inlineStr">
         <is>
           <t>David Gutierrez</t>
         </is>
       </c>
-      <c r="D78" s="10" t="n"/>
+      <c r="D78" s="11" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
@@ -2114,20 +2120,20 @@
       <c r="D79" s="8" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="n">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="n">
         <v>696</v>
       </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="C80" s="11" t="inlineStr">
         <is>
           <t>Hector Gutierrez</t>
         </is>
       </c>
-      <c r="D80" s="10" t="n"/>
+      <c r="D80" s="11" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -2146,20 +2152,20 @@
       <c r="D81" s="8" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B82" s="10" t="n">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="n">
         <v>709</v>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>Miguel Vargas</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n"/>
+      <c r="D82" s="11" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
@@ -2178,20 +2184,20 @@
       <c r="D83" s="8" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="n">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="n">
         <v>721</v>
       </c>
-      <c r="C84" s="10" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>Juliana Jimenez</t>
         </is>
       </c>
-      <c r="D84" s="10" t="n"/>
+      <c r="D84" s="11" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -2210,20 +2216,20 @@
       <c r="D85" s="8" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B86" s="10" t="n">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="n">
         <v>738</v>
       </c>
-      <c r="C86" s="10" t="inlineStr">
+      <c r="C86" s="11" t="inlineStr">
         <is>
           <t>Daniela Hernandez</t>
         </is>
       </c>
-      <c r="D86" s="10" t="n"/>
+      <c r="D86" s="11" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
@@ -2242,20 +2248,20 @@
       <c r="D87" s="8" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B88" s="10" t="n">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="n">
         <v>741</v>
       </c>
-      <c r="C88" s="10" t="inlineStr">
+      <c r="C88" s="11" t="inlineStr">
         <is>
           <t>Felipe Silva</t>
         </is>
       </c>
-      <c r="D88" s="10" t="n"/>
+      <c r="D88" s="11" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
@@ -2274,20 +2280,20 @@
       <c r="D89" s="8" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B90" s="10" t="n">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="n">
         <v>764</v>
       </c>
-      <c r="C90" s="10" t="inlineStr">
+      <c r="C90" s="11" t="inlineStr">
         <is>
           <t>Natalia Mendoza</t>
         </is>
       </c>
-      <c r="D90" s="10" t="n"/>
+      <c r="D90" s="11" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -2306,20 +2312,20 @@
       <c r="D91" s="8" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B92" s="10" t="n">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="n">
         <v>774</v>
       </c>
-      <c r="C92" s="10" t="inlineStr">
+      <c r="C92" s="11" t="inlineStr">
         <is>
           <t>Oscar Vega</t>
         </is>
       </c>
-      <c r="D92" s="10" t="n"/>
+      <c r="D92" s="11" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -2338,20 +2344,20 @@
       <c r="D93" s="8" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B94" s="10" t="n">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="n">
         <v>776</v>
       </c>
-      <c r="C94" s="10" t="inlineStr">
+      <c r="C94" s="11" t="inlineStr">
         <is>
           <t>Hector Flores</t>
         </is>
       </c>
-      <c r="D94" s="10" t="n"/>
+      <c r="D94" s="11" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -2370,20 +2376,20 @@
       <c r="D95" s="8" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B96" s="10" t="n">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="n">
         <v>799</v>
       </c>
-      <c r="C96" s="10" t="inlineStr">
+      <c r="C96" s="11" t="inlineStr">
         <is>
           <t>Alejandra Acosta</t>
         </is>
       </c>
-      <c r="D96" s="10" t="n"/>
+      <c r="D96" s="11" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -2402,20 +2408,20 @@
       <c r="D97" s="8" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B98" s="10" t="n">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="n">
         <v>808</v>
       </c>
-      <c r="C98" s="10" t="inlineStr">
+      <c r="C98" s="11" t="inlineStr">
         <is>
           <t>Sebastian Silva</t>
         </is>
       </c>
-      <c r="D98" s="10" t="n"/>
+      <c r="D98" s="11" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -2434,20 +2440,20 @@
       <c r="D99" s="8" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B100" s="10" t="n">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="n">
         <v>817</v>
       </c>
-      <c r="C100" s="10" t="inlineStr">
+      <c r="C100" s="11" t="inlineStr">
         <is>
           <t>Daniela Gomez</t>
         </is>
       </c>
-      <c r="D100" s="10" t="n"/>
+      <c r="D100" s="11" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -2466,20 +2472,20 @@
       <c r="D101" s="8" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B102" s="10" t="n">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="n">
         <v>819</v>
       </c>
-      <c r="C102" s="10" t="inlineStr">
+      <c r="C102" s="11" t="inlineStr">
         <is>
           <t>Hector Romero</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n"/>
+      <c r="D102" s="11" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
@@ -2498,20 +2504,20 @@
       <c r="D103" s="8" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B104" s="10" t="n">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="n">
         <v>845</v>
       </c>
-      <c r="C104" s="10" t="inlineStr">
+      <c r="C104" s="11" t="inlineStr">
         <is>
           <t>Camila Reyes</t>
         </is>
       </c>
-      <c r="D104" s="10" t="n"/>
+      <c r="D104" s="11" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -2530,20 +2536,20 @@
       <c r="D105" s="8" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B106" s="10" t="n">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="n">
         <v>854</v>
       </c>
-      <c r="C106" s="10" t="inlineStr">
+      <c r="C106" s="11" t="inlineStr">
         <is>
           <t>Paula Reyes</t>
         </is>
       </c>
-      <c r="D106" s="10" t="n"/>
+      <c r="D106" s="11" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
@@ -2562,20 +2568,20 @@
       <c r="D107" s="8" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B108" s="10" t="n">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="n">
         <v>858</v>
       </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="C108" s="11" t="inlineStr">
         <is>
           <t>Mariana Morales</t>
         </is>
       </c>
-      <c r="D108" s="10" t="n"/>
+      <c r="D108" s="11" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
@@ -2594,20 +2600,20 @@
       <c r="D109" s="8" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B110" s="10" t="n">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="n">
         <v>869</v>
       </c>
-      <c r="C110" s="10" t="inlineStr">
+      <c r="C110" s="11" t="inlineStr">
         <is>
           <t>Lina Mendoza</t>
         </is>
       </c>
-      <c r="D110" s="10" t="n"/>
+      <c r="D110" s="11" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
@@ -2626,20 +2632,20 @@
       <c r="D111" s="8" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B112" s="10" t="n">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="n">
         <v>874</v>
       </c>
-      <c r="C112" s="10" t="inlineStr">
+      <c r="C112" s="11" t="inlineStr">
         <is>
           <t>Maria Romero</t>
         </is>
       </c>
-      <c r="D112" s="10" t="n"/>
+      <c r="D112" s="11" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
@@ -2658,20 +2664,20 @@
       <c r="D113" s="8" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B114" s="10" t="n">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="n">
         <v>904</v>
       </c>
-      <c r="C114" s="10" t="inlineStr">
+      <c r="C114" s="11" t="inlineStr">
         <is>
           <t>Sofia Flores</t>
         </is>
       </c>
-      <c r="D114" s="10" t="n"/>
+      <c r="D114" s="11" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
@@ -2690,20 +2696,20 @@
       <c r="D115" s="8" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B116" s="10" t="n">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="n">
         <v>918</v>
       </c>
-      <c r="C116" s="10" t="inlineStr">
+      <c r="C116" s="11" t="inlineStr">
         <is>
           <t>Fernando Ramirez</t>
         </is>
       </c>
-      <c r="D116" s="10" t="n"/>
+      <c r="D116" s="11" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
@@ -2722,20 +2728,20 @@
       <c r="D117" s="8" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B118" s="10" t="n">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="n">
         <v>923</v>
       </c>
-      <c r="C118" s="10" t="inlineStr">
+      <c r="C118" s="11" t="inlineStr">
         <is>
           <t>Lina Vega</t>
         </is>
       </c>
-      <c r="D118" s="10" t="n"/>
+      <c r="D118" s="11" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -2754,20 +2760,20 @@
       <c r="D119" s="8" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B120" s="10" t="n">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="n">
         <v>949</v>
       </c>
-      <c r="C120" s="10" t="inlineStr">
+      <c r="C120" s="11" t="inlineStr">
         <is>
           <t>Sofia Hernandez</t>
         </is>
       </c>
-      <c r="D120" s="10" t="n"/>
+      <c r="D120" s="11" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
@@ -2786,20 +2792,20 @@
       <c r="D121" s="8" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B122" s="10" t="n">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="n">
         <v>954</v>
       </c>
-      <c r="C122" s="10" t="inlineStr">
+      <c r="C122" s="11" t="inlineStr">
         <is>
           <t>Paula Mendoza</t>
         </is>
       </c>
-      <c r="D122" s="10" t="n"/>
+      <c r="D122" s="11" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
@@ -2818,20 +2824,20 @@
       <c r="D123" s="8" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B124" s="10" t="n">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="n">
         <v>959</v>
       </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="C124" s="11" t="inlineStr">
         <is>
           <t>Diego Ortiz</t>
         </is>
       </c>
-      <c r="D124" s="10" t="n"/>
+      <c r="D124" s="11" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
@@ -2850,20 +2856,20 @@
       <c r="D125" s="8" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B126" s="10" t="n">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="n">
         <v>969</v>
       </c>
-      <c r="C126" s="10" t="inlineStr">
+      <c r="C126" s="11" t="inlineStr">
         <is>
           <t>Gabriela Torres</t>
         </is>
       </c>
-      <c r="D126" s="10" t="n"/>
+      <c r="D126" s="11" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
@@ -2882,20 +2888,20 @@
       <c r="D127" s="8" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B128" s="10" t="n">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="n">
         <v>974</v>
       </c>
-      <c r="C128" s="10" t="inlineStr">
+      <c r="C128" s="11" t="inlineStr">
         <is>
           <t>David Gomez</t>
         </is>
       </c>
-      <c r="D128" s="10" t="n"/>
+      <c r="D128" s="11" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
@@ -2914,20 +2920,20 @@
       <c r="D129" s="8" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B130" s="10" t="n">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="n">
         <v>979</v>
       </c>
-      <c r="C130" s="10" t="inlineStr">
+      <c r="C130" s="11" t="inlineStr">
         <is>
           <t>Daniela Suarez</t>
         </is>
       </c>
-      <c r="D130" s="10" t="n"/>
+      <c r="D130" s="11" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
@@ -2946,20 +2952,20 @@
       <c r="D131" s="8" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B132" s="10" t="n">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="n">
         <v>991</v>
       </c>
-      <c r="C132" s="10" t="inlineStr">
+      <c r="C132" s="11" t="inlineStr">
         <is>
           <t>Juan Castro</t>
         </is>
       </c>
-      <c r="D132" s="10" t="n"/>
+      <c r="D132" s="11" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
@@ -2978,20 +2984,20 @@
       <c r="D133" s="8" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B134" s="10" t="n">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="n">
         <v>1005</v>
       </c>
-      <c r="C134" s="10" t="inlineStr">
+      <c r="C134" s="11" t="inlineStr">
         <is>
           <t>Juan Morales</t>
         </is>
       </c>
-      <c r="D134" s="10" t="n"/>
+      <c r="D134" s="11" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
@@ -3010,20 +3016,20 @@
       <c r="D135" s="8" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B136" s="10" t="n">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="n">
         <v>1024</v>
       </c>
-      <c r="C136" s="10" t="inlineStr">
+      <c r="C136" s="11" t="inlineStr">
         <is>
           <t>Luis Moreno</t>
         </is>
       </c>
-      <c r="D136" s="10" t="n"/>
+      <c r="D136" s="11" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
@@ -3042,20 +3048,20 @@
       <c r="D137" s="8" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B138" s="10" t="n">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="n">
         <v>1040</v>
       </c>
-      <c r="C138" s="10" t="inlineStr">
+      <c r="C138" s="11" t="inlineStr">
         <is>
           <t>Hector Mendoza</t>
         </is>
       </c>
-      <c r="D138" s="10" t="n"/>
+      <c r="D138" s="11" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
@@ -3074,20 +3080,20 @@
       <c r="D139" s="8" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B140" s="10" t="n">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="n">
         <v>1061</v>
       </c>
-      <c r="C140" s="10" t="inlineStr">
+      <c r="C140" s="11" t="inlineStr">
         <is>
           <t>Fernando Moreno</t>
         </is>
       </c>
-      <c r="D140" s="10" t="n"/>
+      <c r="D140" s="11" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
@@ -3106,20 +3112,20 @@
       <c r="D141" s="8" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B142" s="10" t="n">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="n">
         <v>1087</v>
       </c>
-      <c r="C142" s="10" t="inlineStr">
+      <c r="C142" s="11" t="inlineStr">
         <is>
           <t>Carlos Acosta</t>
         </is>
       </c>
-      <c r="D142" s="10" t="n"/>
+      <c r="D142" s="11" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
@@ -3138,20 +3144,20 @@
       <c r="D143" s="8" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B144" s="10" t="n">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="n">
         <v>1099</v>
       </c>
-      <c r="C144" s="10" t="inlineStr">
+      <c r="C144" s="11" t="inlineStr">
         <is>
           <t>Hector Gomez</t>
         </is>
       </c>
-      <c r="D144" s="10" t="n"/>
+      <c r="D144" s="11" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
@@ -3170,20 +3176,20 @@
       <c r="D145" s="8" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B146" s="10" t="n">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="n">
         <v>1125</v>
       </c>
-      <c r="C146" s="10" t="inlineStr">
+      <c r="C146" s="11" t="inlineStr">
         <is>
           <t>David Vega</t>
         </is>
       </c>
-      <c r="D146" s="10" t="n"/>
+      <c r="D146" s="11" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
@@ -3202,20 +3208,20 @@
       <c r="D147" s="8" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B148" s="10" t="n">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="n">
         <v>1139</v>
       </c>
-      <c r="C148" s="10" t="inlineStr">
+      <c r="C148" s="11" t="inlineStr">
         <is>
           <t>Andres Gomez</t>
         </is>
       </c>
-      <c r="D148" s="10" t="n"/>
+      <c r="D148" s="11" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
@@ -3234,20 +3240,20 @@
       <c r="D149" s="8" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B150" s="10" t="n">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="n">
         <v>1154</v>
       </c>
-      <c r="C150" s="10" t="inlineStr">
+      <c r="C150" s="11" t="inlineStr">
         <is>
           <t>Sofia Gutierrez</t>
         </is>
       </c>
-      <c r="D150" s="10" t="n"/>
+      <c r="D150" s="11" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
@@ -3266,20 +3272,20 @@
       <c r="D151" s="8" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B152" s="10" t="n">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="n">
         <v>1174</v>
       </c>
-      <c r="C152" s="10" t="inlineStr">
+      <c r="C152" s="11" t="inlineStr">
         <is>
           <t>Juliana Mendoza</t>
         </is>
       </c>
-      <c r="D152" s="10" t="n"/>
+      <c r="D152" s="11" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
@@ -3298,20 +3304,20 @@
       <c r="D153" s="8" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B154" s="10" t="n">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="n">
         <v>1189</v>
       </c>
-      <c r="C154" s="10" t="inlineStr">
+      <c r="C154" s="11" t="inlineStr">
         <is>
           <t>Jorge Hernandez</t>
         </is>
       </c>
-      <c r="D154" s="10" t="n"/>
+      <c r="D154" s="11" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
@@ -3330,20 +3336,20 @@
       <c r="D155" s="8" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B156" s="10" t="n">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B156" s="11" t="n">
         <v>1225</v>
       </c>
-      <c r="C156" s="10" t="inlineStr">
+      <c r="C156" s="11" t="inlineStr">
         <is>
           <t>Miguel Ramirez</t>
         </is>
       </c>
-      <c r="D156" s="10" t="n"/>
+      <c r="D156" s="11" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
@@ -3362,20 +3368,20 @@
       <c r="D157" s="8" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B158" s="10" t="n">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B158" s="11" t="n">
         <v>1229</v>
       </c>
-      <c r="C158" s="10" t="inlineStr">
+      <c r="C158" s="11" t="inlineStr">
         <is>
           <t>Diego Alvarez</t>
         </is>
       </c>
-      <c r="D158" s="10" t="n"/>
+      <c r="D158" s="11" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
@@ -3394,20 +3400,20 @@
       <c r="D159" s="8" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B160" s="10" t="n">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B160" s="11" t="n">
         <v>1237</v>
       </c>
-      <c r="C160" s="10" t="inlineStr">
+      <c r="C160" s="11" t="inlineStr">
         <is>
           <t>Diana Moreno</t>
         </is>
       </c>
-      <c r="D160" s="10" t="n"/>
+      <c r="D160" s="11" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
@@ -3426,20 +3432,20 @@
       <c r="D161" s="8" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B162" s="10" t="n">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="n">
         <v>1242</v>
       </c>
-      <c r="C162" s="10" t="inlineStr">
+      <c r="C162" s="11" t="inlineStr">
         <is>
           <t>Sofia Acosta</t>
         </is>
       </c>
-      <c r="D162" s="10" t="n"/>
+      <c r="D162" s="11" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
@@ -3458,20 +3464,20 @@
       <c r="D163" s="8" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B164" s="10" t="n">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B164" s="11" t="n">
         <v>1253</v>
       </c>
-      <c r="C164" s="10" t="inlineStr">
+      <c r="C164" s="11" t="inlineStr">
         <is>
           <t>Miguel Ortiz</t>
         </is>
       </c>
-      <c r="D164" s="10" t="n"/>
+      <c r="D164" s="11" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="8" t="inlineStr">
@@ -3490,20 +3496,20 @@
       <c r="D165" s="8" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B166" s="10" t="n">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B166" s="11" t="n">
         <v>1283</v>
       </c>
-      <c r="C166" s="10" t="inlineStr">
+      <c r="C166" s="11" t="inlineStr">
         <is>
           <t>Mariana Alvarez</t>
         </is>
       </c>
-      <c r="D166" s="10" t="n"/>
+      <c r="D166" s="11" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
@@ -3522,20 +3528,20 @@
       <c r="D167" s="8" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B168" s="10" t="n">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B168" s="11" t="n">
         <v>1297</v>
       </c>
-      <c r="C168" s="10" t="inlineStr">
+      <c r="C168" s="11" t="inlineStr">
         <is>
           <t>David Silva</t>
         </is>
       </c>
-      <c r="D168" s="10" t="n"/>
+      <c r="D168" s="11" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="8" t="inlineStr">
@@ -3554,20 +3560,20 @@
       <c r="D169" s="8" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B170" s="10" t="n">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B170" s="11" t="n">
         <v>1322</v>
       </c>
-      <c r="C170" s="10" t="inlineStr">
+      <c r="C170" s="11" t="inlineStr">
         <is>
           <t>Cesar Vargas</t>
         </is>
       </c>
-      <c r="D170" s="10" t="n"/>
+      <c r="D170" s="11" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="8" t="inlineStr">
@@ -3586,20 +3592,20 @@
       <c r="D171" s="8" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B172" s="10" t="n">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B172" s="11" t="n">
         <v>1332</v>
       </c>
-      <c r="C172" s="10" t="inlineStr">
+      <c r="C172" s="11" t="inlineStr">
         <is>
           <t>Hector Suarez</t>
         </is>
       </c>
-      <c r="D172" s="10" t="n"/>
+      <c r="D172" s="11" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="8" t="inlineStr">
@@ -3618,20 +3624,20 @@
       <c r="D173" s="8" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B174" s="10" t="n">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B174" s="11" t="n">
         <v>1340</v>
       </c>
-      <c r="C174" s="10" t="inlineStr">
+      <c r="C174" s="11" t="inlineStr">
         <is>
           <t>Valentina Pena</t>
         </is>
       </c>
-      <c r="D174" s="10" t="n"/>
+      <c r="D174" s="11" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="8" t="inlineStr">
@@ -3650,20 +3656,20 @@
       <c r="D175" s="8" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B176" s="10" t="n">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="n">
         <v>1355</v>
       </c>
-      <c r="C176" s="10" t="inlineStr">
+      <c r="C176" s="11" t="inlineStr">
         <is>
           <t>Daniela Ruiz</t>
         </is>
       </c>
-      <c r="D176" s="10" t="n"/>
+      <c r="D176" s="11" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="8" t="inlineStr">
@@ -3682,20 +3688,20 @@
       <c r="D177" s="8" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B178" s="10" t="n">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B178" s="11" t="n">
         <v>1357</v>
       </c>
-      <c r="C178" s="10" t="inlineStr">
+      <c r="C178" s="11" t="inlineStr">
         <is>
           <t>Luis Ramirez</t>
         </is>
       </c>
-      <c r="D178" s="10" t="n"/>
+      <c r="D178" s="11" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="8" t="inlineStr">
@@ -3714,20 +3720,20 @@
       <c r="D179" s="8" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B180" s="10" t="n">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B180" s="11" t="n">
         <v>1367</v>
       </c>
-      <c r="C180" s="10" t="inlineStr">
+      <c r="C180" s="11" t="inlineStr">
         <is>
           <t>Diego Ruiz</t>
         </is>
       </c>
-      <c r="D180" s="10" t="n"/>
+      <c r="D180" s="11" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="8" t="inlineStr">
@@ -3746,20 +3752,20 @@
       <c r="D181" s="8" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B182" s="10" t="n">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B182" s="11" t="n">
         <v>1383</v>
       </c>
-      <c r="C182" s="10" t="inlineStr">
+      <c r="C182" s="11" t="inlineStr">
         <is>
           <t>Juliana Silva</t>
         </is>
       </c>
-      <c r="D182" s="10" t="n"/>
+      <c r="D182" s="11" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="8" t="inlineStr">
@@ -3778,20 +3784,20 @@
       <c r="D183" s="8" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B184" s="10" t="n">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B184" s="11" t="n">
         <v>1397</v>
       </c>
-      <c r="C184" s="10" t="inlineStr">
+      <c r="C184" s="11" t="inlineStr">
         <is>
           <t>Natalia Vega</t>
         </is>
       </c>
-      <c r="D184" s="10" t="n"/>
+      <c r="D184" s="11" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="8" t="inlineStr">
@@ -3810,20 +3816,20 @@
       <c r="D185" s="8" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B186" s="10" t="n">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B186" s="11" t="n">
         <v>1406</v>
       </c>
-      <c r="C186" s="10" t="inlineStr">
+      <c r="C186" s="11" t="inlineStr">
         <is>
           <t>Alejandra Hernandez</t>
         </is>
       </c>
-      <c r="D186" s="10" t="n"/>
+      <c r="D186" s="11" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="8" t="inlineStr">
@@ -3842,20 +3848,20 @@
       <c r="D187" s="8" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B188" s="10" t="n">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B188" s="11" t="n">
         <v>1427</v>
       </c>
-      <c r="C188" s="10" t="inlineStr">
+      <c r="C188" s="11" t="inlineStr">
         <is>
           <t>Fernando Flores</t>
         </is>
       </c>
-      <c r="D188" s="10" t="n"/>
+      <c r="D188" s="11" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="8" t="inlineStr">
@@ -3874,20 +3880,20 @@
       <c r="D189" s="8" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B190" s="10" t="n">
+      <c r="A190" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B190" s="11" t="n">
         <v>1435</v>
       </c>
-      <c r="C190" s="10" t="inlineStr">
+      <c r="C190" s="11" t="inlineStr">
         <is>
           <t>Hector Alvarez</t>
         </is>
       </c>
-      <c r="D190" s="10" t="n"/>
+      <c r="D190" s="11" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="8" t="inlineStr">
@@ -3906,20 +3912,20 @@
       <c r="D191" s="8" t="n"/>
     </row>
     <row r="192">
-      <c r="A192" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B192" s="10" t="n">
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B192" s="11" t="n">
         <v>1462</v>
       </c>
-      <c r="C192" s="10" t="inlineStr">
+      <c r="C192" s="11" t="inlineStr">
         <is>
           <t>Luis Morales</t>
         </is>
       </c>
-      <c r="D192" s="10" t="n"/>
+      <c r="D192" s="11" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="8" t="inlineStr">
@@ -3938,20 +3944,20 @@
       <c r="D193" s="8" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B194" s="10" t="n">
+      <c r="A194" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B194" s="11" t="n">
         <v>1486</v>
       </c>
-      <c r="C194" s="10" t="inlineStr">
+      <c r="C194" s="11" t="inlineStr">
         <is>
           <t>Maria Torres</t>
         </is>
       </c>
-      <c r="D194" s="10" t="n"/>
+      <c r="D194" s="11" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="8" t="inlineStr">
@@ -3970,20 +3976,20 @@
       <c r="D195" s="8" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B196" s="10" t="n">
+      <c r="A196" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B196" s="11" t="n">
         <v>1492</v>
       </c>
-      <c r="C196" s="10" t="inlineStr">
+      <c r="C196" s="11" t="inlineStr">
         <is>
           <t>Cesar Rodriguez</t>
         </is>
       </c>
-      <c r="D196" s="10" t="n"/>
+      <c r="D196" s="11" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="8" t="inlineStr">
@@ -4002,20 +4008,20 @@
       <c r="D197" s="8" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B198" s="10" t="n">
+      <c r="A198" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B198" s="11" t="n">
         <v>1501</v>
       </c>
-      <c r="C198" s="10" t="inlineStr">
+      <c r="C198" s="11" t="inlineStr">
         <is>
           <t>Felipe Ramirez</t>
         </is>
       </c>
-      <c r="D198" s="10" t="n"/>
+      <c r="D198" s="11" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="8" t="inlineStr">
@@ -4034,20 +4040,20 @@
       <c r="D199" s="8" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B200" s="10" t="n">
+      <c r="A200" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B200" s="11" t="n">
         <v>1537</v>
       </c>
-      <c r="C200" s="10" t="inlineStr">
+      <c r="C200" s="11" t="inlineStr">
         <is>
           <t>Gabriela Romero</t>
         </is>
       </c>
-      <c r="D200" s="10" t="n"/>
+      <c r="D200" s="11" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="8" t="inlineStr">
@@ -4066,20 +4072,20 @@
       <c r="D201" s="8" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B202" s="10" t="n">
+      <c r="A202" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B202" s="11" t="n">
         <v>1558</v>
       </c>
-      <c r="C202" s="10" t="inlineStr">
+      <c r="C202" s="11" t="inlineStr">
         <is>
           <t>David Gutierrez</t>
         </is>
       </c>
-      <c r="D202" s="10" t="n"/>
+      <c r="D202" s="11" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="8" t="inlineStr">
@@ -4098,20 +4104,20 @@
       <c r="D203" s="8" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B204" s="10" t="n">
+      <c r="A204" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B204" s="11" t="n">
         <v>1565</v>
       </c>
-      <c r="C204" s="10" t="inlineStr">
+      <c r="C204" s="11" t="inlineStr">
         <is>
           <t>Fernando Acosta</t>
         </is>
       </c>
-      <c r="D204" s="10" t="n"/>
+      <c r="D204" s="11" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="8" t="inlineStr">
@@ -4130,20 +4136,20 @@
       <c r="D205" s="8" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B206" s="10" t="n">
+      <c r="A206" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B206" s="11" t="n">
         <v>1569</v>
       </c>
-      <c r="C206" s="10" t="inlineStr">
+      <c r="C206" s="11" t="inlineStr">
         <is>
           <t>Juliana Cruz</t>
         </is>
       </c>
-      <c r="D206" s="10" t="n"/>
+      <c r="D206" s="11" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="8" t="inlineStr">
@@ -4162,20 +4168,20 @@
       <c r="D207" s="8" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B208" s="10" t="n">
+      <c r="A208" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B208" s="11" t="n">
         <v>1585</v>
       </c>
-      <c r="C208" s="10" t="inlineStr">
+      <c r="C208" s="11" t="inlineStr">
         <is>
           <t>Miguel Ruiz</t>
         </is>
       </c>
-      <c r="D208" s="10" t="n"/>
+      <c r="D208" s="11" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="8" t="inlineStr">
@@ -4194,20 +4200,20 @@
       <c r="D209" s="8" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B210" s="10" t="n">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B210" s="11" t="n">
         <v>1597</v>
       </c>
-      <c r="C210" s="10" t="inlineStr">
+      <c r="C210" s="11" t="inlineStr">
         <is>
           <t>Oscar Diaz</t>
         </is>
       </c>
-      <c r="D210" s="10" t="n"/>
+      <c r="D210" s="11" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="8" t="inlineStr">
@@ -4226,20 +4232,20 @@
       <c r="D211" s="8" t="n"/>
     </row>
     <row r="212">
-      <c r="A212" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B212" s="10" t="n">
+      <c r="A212" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B212" s="11" t="n">
         <v>1601</v>
       </c>
-      <c r="C212" s="10" t="inlineStr">
+      <c r="C212" s="11" t="inlineStr">
         <is>
           <t>Oscar Vargas</t>
         </is>
       </c>
-      <c r="D212" s="10" t="n"/>
+      <c r="D212" s="11" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="8" t="inlineStr">
@@ -4258,20 +4264,20 @@
       <c r="D213" s="8" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B214" s="10" t="n">
+      <c r="A214" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B214" s="11" t="n">
         <v>1605</v>
       </c>
-      <c r="C214" s="10" t="inlineStr">
+      <c r="C214" s="11" t="inlineStr">
         <is>
           <t>Cesar Vargas</t>
         </is>
       </c>
-      <c r="D214" s="10" t="n"/>
+      <c r="D214" s="11" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="8" t="inlineStr">
@@ -4290,20 +4296,20 @@
       <c r="D215" s="8" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B216" s="10" t="n">
+      <c r="A216" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B216" s="11" t="n">
         <v>1609</v>
       </c>
-      <c r="C216" s="10" t="inlineStr">
+      <c r="C216" s="11" t="inlineStr">
         <is>
           <t>Laura Garcia</t>
         </is>
       </c>
-      <c r="D216" s="10" t="n"/>
+      <c r="D216" s="11" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="8" t="inlineStr">
@@ -4322,20 +4328,20 @@
       <c r="D217" s="8" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B218" s="10" t="n">
+      <c r="A218" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B218" s="11" t="n">
         <v>1624</v>
       </c>
-      <c r="C218" s="10" t="inlineStr">
+      <c r="C218" s="11" t="inlineStr">
         <is>
           <t>Luis Cruz</t>
         </is>
       </c>
-      <c r="D218" s="10" t="n"/>
+      <c r="D218" s="11" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="8" t="inlineStr">
@@ -4354,20 +4360,20 @@
       <c r="D219" s="8" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B220" s="10" t="n">
+      <c r="A220" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B220" s="11" t="n">
         <v>1645</v>
       </c>
-      <c r="C220" s="10" t="inlineStr">
+      <c r="C220" s="11" t="inlineStr">
         <is>
           <t>Felipe Silva</t>
         </is>
       </c>
-      <c r="D220" s="10" t="n"/>
+      <c r="D220" s="11" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="8" t="inlineStr">
@@ -4386,20 +4392,20 @@
       <c r="D221" s="8" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B222" s="10" t="n">
+      <c r="A222" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B222" s="11" t="n">
         <v>1665</v>
       </c>
-      <c r="C222" s="10" t="inlineStr">
+      <c r="C222" s="11" t="inlineStr">
         <is>
           <t>Fernando Ortiz</t>
         </is>
       </c>
-      <c r="D222" s="10" t="n"/>
+      <c r="D222" s="11" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="8" t="inlineStr">
@@ -4418,20 +4424,20 @@
       <c r="D223" s="8" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B224" s="10" t="n">
+      <c r="A224" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B224" s="11" t="n">
         <v>1680</v>
       </c>
-      <c r="C224" s="10" t="inlineStr">
+      <c r="C224" s="11" t="inlineStr">
         <is>
           <t>Gabriela Cruz</t>
         </is>
       </c>
-      <c r="D224" s="10" t="n"/>
+      <c r="D224" s="11" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="8" t="inlineStr">
@@ -4450,20 +4456,20 @@
       <c r="D225" s="8" t="n"/>
     </row>
     <row r="226">
-      <c r="A226" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B226" s="10" t="n">
+      <c r="A226" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B226" s="11" t="n">
         <v>1687</v>
       </c>
-      <c r="C226" s="10" t="inlineStr">
+      <c r="C226" s="11" t="inlineStr">
         <is>
           <t>Cesar Ruiz</t>
         </is>
       </c>
-      <c r="D226" s="10" t="n"/>
+      <c r="D226" s="11" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="8" t="inlineStr">
@@ -4482,20 +4488,20 @@
       <c r="D227" s="8" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B228" s="10" t="n">
+      <c r="A228" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B228" s="11" t="n">
         <v>1696</v>
       </c>
-      <c r="C228" s="10" t="inlineStr">
+      <c r="C228" s="11" t="inlineStr">
         <is>
           <t>Sebastian Suarez</t>
         </is>
       </c>
-      <c r="D228" s="10" t="n"/>
+      <c r="D228" s="11" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="8" t="inlineStr">
@@ -4514,20 +4520,20 @@
       <c r="D229" s="8" t="n"/>
     </row>
     <row r="230">
-      <c r="A230" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B230" s="10" t="n">
+      <c r="A230" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B230" s="11" t="n">
         <v>1707</v>
       </c>
-      <c r="C230" s="10" t="inlineStr">
+      <c r="C230" s="11" t="inlineStr">
         <is>
           <t>Mariana Reyes</t>
         </is>
       </c>
-      <c r="D230" s="10" t="n"/>
+      <c r="D230" s="11" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="8" t="inlineStr">
@@ -4546,20 +4552,20 @@
       <c r="D231" s="8" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B232" s="10" t="n">
+      <c r="A232" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B232" s="11" t="n">
         <v>1714</v>
       </c>
-      <c r="C232" s="10" t="inlineStr">
+      <c r="C232" s="11" t="inlineStr">
         <is>
           <t>Felipe Vega</t>
         </is>
       </c>
-      <c r="D232" s="10" t="n"/>
+      <c r="D232" s="11" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="8" t="inlineStr">
@@ -4578,20 +4584,20 @@
       <c r="D233" s="8" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B234" s="10" t="n">
+      <c r="A234" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B234" s="11" t="n">
         <v>1729</v>
       </c>
-      <c r="C234" s="10" t="inlineStr">
+      <c r="C234" s="11" t="inlineStr">
         <is>
           <t>Camila Romero</t>
         </is>
       </c>
-      <c r="D234" s="10" t="n"/>
+      <c r="D234" s="11" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="8" t="inlineStr">
@@ -4610,20 +4616,20 @@
       <c r="D235" s="8" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B236" s="10" t="n">
+      <c r="A236" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B236" s="11" t="n">
         <v>1750</v>
       </c>
-      <c r="C236" s="10" t="inlineStr">
+      <c r="C236" s="11" t="inlineStr">
         <is>
           <t>Miguel Garcia</t>
         </is>
       </c>
-      <c r="D236" s="10" t="n"/>
+      <c r="D236" s="11" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="8" t="inlineStr">
@@ -4642,20 +4648,20 @@
       <c r="D237" s="8" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B238" s="10" t="n">
+      <c r="A238" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B238" s="11" t="n">
         <v>1806</v>
       </c>
-      <c r="C238" s="10" t="inlineStr">
+      <c r="C238" s="11" t="inlineStr">
         <is>
           <t>Cesar Ruiz</t>
         </is>
       </c>
-      <c r="D238" s="10" t="n"/>
+      <c r="D238" s="11" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="8" t="inlineStr">
@@ -4674,20 +4680,20 @@
       <c r="D239" s="8" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B240" s="10" t="n">
+      <c r="A240" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B240" s="11" t="n">
         <v>1815</v>
       </c>
-      <c r="C240" s="10" t="inlineStr">
+      <c r="C240" s="11" t="inlineStr">
         <is>
           <t>Paula Jimenez</t>
         </is>
       </c>
-      <c r="D240" s="10" t="n"/>
+      <c r="D240" s="11" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="8" t="inlineStr">
@@ -4706,20 +4712,20 @@
       <c r="D241" s="8" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B242" s="10" t="n">
+      <c r="A242" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B242" s="11" t="n">
         <v>1828</v>
       </c>
-      <c r="C242" s="10" t="inlineStr">
+      <c r="C242" s="11" t="inlineStr">
         <is>
           <t>Hector Diaz</t>
         </is>
       </c>
-      <c r="D242" s="10" t="n"/>
+      <c r="D242" s="11" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="8" t="inlineStr">
@@ -4738,20 +4744,20 @@
       <c r="D243" s="8" t="n"/>
     </row>
     <row r="244">
-      <c r="A244" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B244" s="10" t="n">
+      <c r="A244" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B244" s="11" t="n">
         <v>1833</v>
       </c>
-      <c r="C244" s="10" t="inlineStr">
+      <c r="C244" s="11" t="inlineStr">
         <is>
           <t>Fernando Lopez</t>
         </is>
       </c>
-      <c r="D244" s="10" t="n"/>
+      <c r="D244" s="11" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="8" t="inlineStr">
@@ -4770,20 +4776,20 @@
       <c r="D245" s="8" t="n"/>
     </row>
     <row r="246">
-      <c r="A246" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B246" s="10" t="n">
+      <c r="A246" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B246" s="11" t="n">
         <v>1851</v>
       </c>
-      <c r="C246" s="10" t="inlineStr">
+      <c r="C246" s="11" t="inlineStr">
         <is>
           <t>Valentina Romero</t>
         </is>
       </c>
-      <c r="D246" s="10" t="n"/>
+      <c r="D246" s="11" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="8" t="inlineStr">
@@ -4802,20 +4808,20 @@
       <c r="D247" s="8" t="n"/>
     </row>
     <row r="248">
-      <c r="A248" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B248" s="10" t="n">
+      <c r="A248" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B248" s="11" t="n">
         <v>1858</v>
       </c>
-      <c r="C248" s="10" t="inlineStr">
+      <c r="C248" s="11" t="inlineStr">
         <is>
           <t>Luis Hernandez</t>
         </is>
       </c>
-      <c r="D248" s="10" t="n"/>
+      <c r="D248" s="11" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="8" t="inlineStr">
@@ -4834,20 +4840,20 @@
       <c r="D249" s="8" t="n"/>
     </row>
     <row r="250">
-      <c r="A250" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B250" s="10" t="n">
+      <c r="A250" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B250" s="11" t="n">
         <v>1867</v>
       </c>
-      <c r="C250" s="10" t="inlineStr">
+      <c r="C250" s="11" t="inlineStr">
         <is>
           <t>Maria Silva</t>
         </is>
       </c>
-      <c r="D250" s="10" t="n"/>
+      <c r="D250" s="11" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="8" t="inlineStr">
@@ -4866,20 +4872,20 @@
       <c r="D251" s="8" t="n"/>
     </row>
     <row r="252">
-      <c r="A252" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B252" s="10" t="n">
+      <c r="A252" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B252" s="11" t="n">
         <v>1887</v>
       </c>
-      <c r="C252" s="10" t="inlineStr">
+      <c r="C252" s="11" t="inlineStr">
         <is>
           <t>Fernando Garcia</t>
         </is>
       </c>
-      <c r="D252" s="10" t="n"/>
+      <c r="D252" s="11" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="8" t="inlineStr">
@@ -4898,20 +4904,20 @@
       <c r="D253" s="8" t="n"/>
     </row>
     <row r="254">
-      <c r="A254" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B254" s="10" t="n">
+      <c r="A254" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B254" s="11" t="n">
         <v>1899</v>
       </c>
-      <c r="C254" s="10" t="inlineStr">
+      <c r="C254" s="11" t="inlineStr">
         <is>
           <t>Oscar Rodriguez</t>
         </is>
       </c>
-      <c r="D254" s="10" t="n"/>
+      <c r="D254" s="11" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="8" t="inlineStr">
@@ -4930,20 +4936,20 @@
       <c r="D255" s="8" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B256" s="10" t="n">
+      <c r="A256" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B256" s="11" t="n">
         <v>1926</v>
       </c>
-      <c r="C256" s="10" t="inlineStr">
+      <c r="C256" s="11" t="inlineStr">
         <is>
           <t>Paula Jimenez</t>
         </is>
       </c>
-      <c r="D256" s="10" t="n"/>
+      <c r="D256" s="11" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="8" t="inlineStr">
@@ -4962,20 +4968,20 @@
       <c r="D257" s="8" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B258" s="10" t="n">
+      <c r="A258" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B258" s="11" t="n">
         <v>1940</v>
       </c>
-      <c r="C258" s="10" t="inlineStr">
+      <c r="C258" s="11" t="inlineStr">
         <is>
           <t>Luis Alvarez</t>
         </is>
       </c>
-      <c r="D258" s="10" t="n"/>
+      <c r="D258" s="11" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="8" t="inlineStr">
@@ -4994,20 +5000,20 @@
       <c r="D259" s="8" t="n"/>
     </row>
     <row r="260">
-      <c r="A260" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B260" s="10" t="n">
+      <c r="A260" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B260" s="11" t="n">
         <v>1966</v>
       </c>
-      <c r="C260" s="10" t="inlineStr">
+      <c r="C260" s="11" t="inlineStr">
         <is>
           <t>Cesar Jimenez</t>
         </is>
       </c>
-      <c r="D260" s="10" t="n"/>
+      <c r="D260" s="11" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="8" t="inlineStr">
@@ -5026,20 +5032,20 @@
       <c r="D261" s="8" t="n"/>
     </row>
     <row r="262">
-      <c r="A262" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B262" s="10" t="n">
+      <c r="A262" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B262" s="11" t="n">
         <v>1983</v>
       </c>
-      <c r="C262" s="10" t="inlineStr">
+      <c r="C262" s="11" t="inlineStr">
         <is>
           <t>Alejandra Torres</t>
         </is>
       </c>
-      <c r="D262" s="10" t="n"/>
+      <c r="D262" s="11" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="8" t="inlineStr">
@@ -5058,20 +5064,20 @@
       <c r="D263" s="8" t="n"/>
     </row>
     <row r="264">
-      <c r="A264" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B264" s="10" t="n">
+      <c r="A264" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B264" s="11" t="n">
         <v>2005</v>
       </c>
-      <c r="C264" s="10" t="inlineStr">
+      <c r="C264" s="11" t="inlineStr">
         <is>
           <t>Julián Cárdenas Franco</t>
         </is>
       </c>
-      <c r="D264" s="10" t="inlineStr">
+      <c r="D264" s="11" t="inlineStr">
         <is>
           <t>2027-09-08</t>
         </is>
@@ -5098,20 +5104,20 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B266" s="10" t="n">
+      <c r="A266" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B266" s="11" t="n">
         <v>2098</v>
       </c>
-      <c r="C266" s="10" t="inlineStr">
+      <c r="C266" s="11" t="inlineStr">
         <is>
           <t>Victoria Jiménez</t>
         </is>
       </c>
-      <c r="D266" s="10" t="inlineStr">
+      <c r="D266" s="11" t="inlineStr">
         <is>
           <t>2027-01-14</t>
         </is>
@@ -5138,20 +5144,20 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B268" s="10" t="n">
+      <c r="A268" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B268" s="11" t="n">
         <v>2328</v>
       </c>
-      <c r="C268" s="10" t="inlineStr">
+      <c r="C268" s="11" t="inlineStr">
         <is>
           <t>Laura Muñoz Mendoza</t>
         </is>
       </c>
-      <c r="D268" s="10" t="inlineStr">
+      <c r="D268" s="11" t="inlineStr">
         <is>
           <t>2027-06-29</t>
         </is>
@@ -5178,20 +5184,20 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B270" s="10" t="n">
+      <c r="A270" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B270" s="11" t="n">
         <v>2435</v>
       </c>
-      <c r="C270" s="10" t="inlineStr">
+      <c r="C270" s="11" t="inlineStr">
         <is>
           <t>Victoria García</t>
         </is>
       </c>
-      <c r="D270" s="10" t="inlineStr">
+      <c r="D270" s="11" t="inlineStr">
         <is>
           <t>2027-05-02</t>
         </is>
@@ -5218,20 +5224,20 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B272" s="10" t="n">
+      <c r="A272" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B272" s="11" t="n">
         <v>2510</v>
       </c>
-      <c r="C272" s="10" t="inlineStr">
+      <c r="C272" s="11" t="inlineStr">
         <is>
           <t>Diego Pérez</t>
         </is>
       </c>
-      <c r="D272" s="10" t="inlineStr">
+      <c r="D272" s="11" t="inlineStr">
         <is>
           <t>2027-07-10</t>
         </is>
@@ -5258,20 +5264,20 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B274" s="10" t="n">
+      <c r="A274" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B274" s="11" t="n">
         <v>2534</v>
       </c>
-      <c r="C274" s="10" t="inlineStr">
+      <c r="C274" s="11" t="inlineStr">
         <is>
           <t>Felipe Castro</t>
         </is>
       </c>
-      <c r="D274" s="10" t="inlineStr">
+      <c r="D274" s="11" t="inlineStr">
         <is>
           <t>2027-10-23</t>
         </is>
@@ -5298,20 +5304,20 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B276" s="10" t="n">
+      <c r="A276" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B276" s="11" t="n">
         <v>2570</v>
       </c>
-      <c r="C276" s="10" t="inlineStr">
+      <c r="C276" s="11" t="inlineStr">
         <is>
           <t>Diego Díaz</t>
         </is>
       </c>
-      <c r="D276" s="10" t="inlineStr">
+      <c r="D276" s="11" t="inlineStr">
         <is>
           <t>2027-07-21</t>
         </is>
@@ -5338,20 +5344,20 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B278" s="10" t="n">
+      <c r="A278" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B278" s="11" t="n">
         <v>2738</v>
       </c>
-      <c r="C278" s="10" t="inlineStr">
+      <c r="C278" s="11" t="inlineStr">
         <is>
           <t>Valeria Castro</t>
         </is>
       </c>
-      <c r="D278" s="10" t="inlineStr">
+      <c r="D278" s="11" t="inlineStr">
         <is>
           <t>2027-03-10</t>
         </is>
@@ -5378,20 +5384,20 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B280" s="10" t="n">
+      <c r="A280" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B280" s="11" t="n">
         <v>2866</v>
       </c>
-      <c r="C280" s="10" t="inlineStr">
+      <c r="C280" s="11" t="inlineStr">
         <is>
           <t>Daniela Cárdenas</t>
         </is>
       </c>
-      <c r="D280" s="10" t="inlineStr">
+      <c r="D280" s="11" t="inlineStr">
         <is>
           <t>2027-02-15</t>
         </is>
@@ -5418,20 +5424,20 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B282" s="10" t="n">
+      <c r="A282" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B282" s="11" t="n">
         <v>3053</v>
       </c>
-      <c r="C282" s="10" t="inlineStr">
+      <c r="C282" s="11" t="inlineStr">
         <is>
           <t>Angela Martínez</t>
         </is>
       </c>
-      <c r="D282" s="10" t="inlineStr">
+      <c r="D282" s="11" t="inlineStr">
         <is>
           <t>2027-04-04</t>
         </is>
@@ -5458,20 +5464,20 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B284" s="10" t="n">
+      <c r="A284" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B284" s="11" t="n">
         <v>3151</v>
       </c>
-      <c r="C284" s="10" t="inlineStr">
+      <c r="C284" s="11" t="inlineStr">
         <is>
           <t>Natalia Londono</t>
         </is>
       </c>
-      <c r="D284" s="10" t="inlineStr">
+      <c r="D284" s="11" t="inlineStr">
         <is>
           <t>2027-04-26</t>
         </is>
@@ -5498,20 +5504,20 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B286" s="10" t="n">
+      <c r="A286" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B286" s="11" t="n">
         <v>3197</v>
       </c>
-      <c r="C286" s="10" t="inlineStr">
+      <c r="C286" s="11" t="inlineStr">
         <is>
           <t>Andrés Patiño Salazar</t>
         </is>
       </c>
-      <c r="D286" s="10" t="inlineStr">
+      <c r="D286" s="11" t="inlineStr">
         <is>
           <t>2027-05-19</t>
         </is>
@@ -5538,20 +5544,20 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B288" s="10" t="n">
+      <c r="A288" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B288" s="11" t="n">
         <v>3259</v>
       </c>
-      <c r="C288" s="10" t="inlineStr">
+      <c r="C288" s="11" t="inlineStr">
         <is>
           <t>Carlos Cardona</t>
         </is>
       </c>
-      <c r="D288" s="10" t="inlineStr">
+      <c r="D288" s="11" t="inlineStr">
         <is>
           <t>2027-01-04</t>
         </is>
@@ -5578,20 +5584,20 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="10" t="inlineStr">
-        <is>
-          <t>No contactar (baja/revocada)</t>
-        </is>
-      </c>
-      <c r="B290" s="10" t="n">
+      <c r="A290" s="11" t="inlineStr">
+        <is>
+          <t>No contactar (baja/revocada)</t>
+        </is>
+      </c>
+      <c r="B290" s="11" t="n">
         <v>3291</v>
       </c>
-      <c r="C290" s="10" t="inlineStr">
+      <c r="C290" s="11" t="inlineStr">
         <is>
           <t>Isabela Díaz</t>
         </is>
       </c>
-      <c r="D290" s="10" t="inlineStr">
+      <c r="D290" s="11" t="inlineStr">
         <is>
           <t>2026-12-16</t>
         </is>
@@ -5618,20 +5624,20 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="10" t="inlineStr">
+      <c r="A292" s="11" t="inlineStr">
         <is>
           <t>Leads calificados sin asesor</t>
         </is>
       </c>
-      <c r="B292" s="10" t="n">
+      <c r="B292" s="11" t="n">
         <v>632</v>
       </c>
-      <c r="C292" s="10" t="inlineStr">
+      <c r="C292" s="11" t="inlineStr">
         <is>
           <t>Revisar asignación en el CRM</t>
         </is>
       </c>
-      <c r="D292" s="10" t="inlineStr"/>
+      <c r="D292" s="11" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="8" t="inlineStr">
@@ -5670,7 +5676,7 @@
     <col width="59" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -5718,207 +5724,207 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Leads en la base</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>3601</v>
+          <t>Clientes con autorización vigente o revocada documentada</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>3600</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Cumple</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Base de ejemplo (3.600 leads potenciales); meta anual del plan: 3600</t>
+          <t>100% de clientes con consentimiento documentado (Ley 1581)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Ventas (meta mensual)</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Cumple</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>Meta del plan: 6 suites vendidas por mes</t>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Conversión lead a venta (meta)</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Por debajo de la meta (muestra)</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>72 ventas / 3.600 leads potenciales (1.6%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Ventas (meta anual)</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>72</v>
+          <t>Inventario a vender (meta)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>0.1333</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Cumple</t>
+        <v>0.4</v>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Por debajo de la meta (muestra)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Meta del plan: 72 suites en 12 meses (6 por mes)</t>
+          <t>72 suites de las 180 del inventario (40%)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Inventario a vender (meta)</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Leads en la base</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Cumple</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>72 suites de las 180 del inventario (40%)</t>
+        <v>1620</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>3600</v>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Por debajo de la meta (muestra)</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Base de ejemplo (3.600 leads potenciales); meta anual del plan: 3600</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Conversión lead a venta (meta)</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n">
-        <v>0.016</v>
+          <t>Leads por Meta Business (meta)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>0.27</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Cumple</t>
+        <v>0.6</v>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Por debajo de la meta (muestra)</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>72 ventas / 3.600 leads potenciales (1.6%)</t>
+          <t>Meta: 60% de los leads desde el formulario de Meta Business</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Leads por Meta Business (meta)</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Cumple</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>Meta: 60% de los leads desde el formulario de Meta Business</t>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Leads por WhatsApp (meta)</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Por debajo de la meta (muestra)</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Meta: 40% de los leads desde WhatsApp</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Leads por WhatsApp (meta)</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>0.4</v>
+          <t>Valor vendido (meta mensual, COP millones)</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>740</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Cumple</t>
+        <v>2100</v>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Por debajo de la meta (muestra)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Meta: 40% de los leads desde WhatsApp</t>
+          <t>6 ventas mensuales presupuestadas × 350 M COP</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Valor vendido (meta mensual, COP millones)</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>2100</v>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>2100</v>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Cumple</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>6 ventas mensuales presupuestadas × 350 M COP</t>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Ventas (meta anual)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Por debajo de la meta (muestra)</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Meta del plan: 72 suites en 12 meses (6 por mes)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Clientes con autorización vigente o revocada documentada</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>1</v>
+          <t>Ventas (meta mensual)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Cumple</t>
+        <v>6</v>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Por debajo de la meta (muestra)</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>100% de clientes con consentimiento documentado (Ley 1581)</t>
+          <t>Meta del plan: 6 suites vendidas por mes</t>
         </is>
       </c>
     </row>
@@ -6000,25 +6006,25 @@
       <c r="C5" s="8" t="n">
         <v>3601</v>
       </c>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="11" t="n">
         <v>1440</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>0.4</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -6034,29 +6040,29 @@
       <c r="C7" s="8" t="n">
         <v>720</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="9" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="11" t="n">
         <v>360</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6072,29 +6078,29 @@
       <c r="C9" s="8" t="n">
         <v>144</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="9" t="n">
         <v>0.04</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="9" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6179,26 +6185,26 @@
       <c r="D5" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="14" t="n">
         <v>0.0716</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Eventos</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>498</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="11" t="n">
         <v>320</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>0.0683</v>
       </c>
     </row>
@@ -6217,26 +6223,26 @@
       <c r="D7" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>0.0781</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Alianzas y relaciones públicas</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <v>543</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="11" t="n">
         <v>360</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>53</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -6255,26 +6261,26 @@
       <c r="D9" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <v>0.068</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Meta (Facebook/Instagram)</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="11" t="n">
         <v>490</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="11" t="n">
         <v>322</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <v>0.0694</v>
       </c>
     </row>
@@ -6293,7 +6299,7 @@
       <c r="D11" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="14" t="n">
         <v>0.0784</v>
       </c>
     </row>
@@ -6392,24 +6398,24 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>B. Inversionista regional</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="11" t="n">
         <v>710</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>168</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <v>58</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6436,24 +6442,24 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>D. Comprador multi-suite</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="11" t="n">
         <v>689</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>166</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6583,27 +6589,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>C1. Lanzamiento</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>330</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="11" t="n">
         <v>2000</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>751</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="11" t="n">
         <v>14.3</v>
       </c>
     </row>
@@ -6633,27 +6639,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>C3. Colombia te espera</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>688</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="11" t="n">
         <v>54</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="11" t="n">
         <v>10.7</v>
       </c>
     </row>
@@ -6759,18 +6765,18 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Separada</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="11" t="n">
         <v>776</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>388</v>
       </c>
     </row>
@@ -6853,20 +6859,20 @@
       <c r="B5" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="9" t="n">
         <v>0.008</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Caliente</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>297</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>0.082</v>
       </c>
     </row>
@@ -6879,20 +6885,20 @@
       <c r="B7" s="8" t="n">
         <v>1325</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="9" t="n">
         <v>0.368</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Tibio</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <v>1949</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>0.541</v>
       </c>
     </row>
@@ -6988,25 +6994,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Natalia Gómez Jiménez</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>2026-11-02</t>
         </is>
@@ -7038,25 +7044,25 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Camila Henao Salazar</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>2027-03-17</t>
         </is>
@@ -7088,25 +7094,25 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Daniel Mejía Torres</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>2027-05-07</t>
         </is>
@@ -7138,25 +7144,25 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Viviana Montoya Cardona</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>2027-07-27</t>
         </is>
@@ -7188,25 +7194,25 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Viviana Zapata Jiménez</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>2027-08-15</t>
         </is>
@@ -7238,25 +7244,25 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Héctor Duque Herrera</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>2027-10-17</t>
         </is>
@@ -7288,25 +7294,25 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Iván Duque Ramírez</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>2027-07-30</t>
         </is>
@@ -7338,25 +7344,25 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Felipe Martínez Ramírez</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
@@ -7388,25 +7394,25 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Julián Londono</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>2027-03-30</t>
         </is>
@@ -7438,25 +7444,25 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Francisco Muñoz Salazar</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>2027-08-02</t>
         </is>
@@ -7488,25 +7494,25 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Andrea Acosta</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>2027-05-06</t>
         </is>
@@ -7538,25 +7544,25 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Angela Velasco</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>2027-01-10</t>
         </is>
@@ -7588,25 +7594,25 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Esteban Juan Betancur Montoya</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D30" s="10" t="n">
+      <c r="D30" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>2027-01-27</t>
         </is>
@@ -7638,25 +7644,25 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Camilo Orozco Patiño</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D32" s="10" t="n">
+      <c r="D32" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>2027-06-10</t>
         </is>
@@ -7688,25 +7694,25 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>Diana Liliana Gil Londoño</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="D34" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>2027-10-17</t>
         </is>
@@ -7738,25 +7744,25 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Julián Valencia Díaz</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="D36" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>2027-03-19</t>
         </is>
@@ -7788,25 +7794,25 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Valentina Duque Jiménez</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>2027-01-22</t>
         </is>
@@ -7838,25 +7844,25 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Andrea Acosta Orozco</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D40" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>2027-03-30</t>
         </is>
@@ -7888,25 +7894,25 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Juan Rojas Restrepo</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>2027-04-01</t>
         </is>
@@ -7938,25 +7944,25 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Andrés Valencia Bedoya</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>2027-04-08</t>
         </is>
@@ -7988,25 +7994,25 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Carolina Viviana Correa Ríos</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>2027-08-26</t>
         </is>
@@ -8038,25 +8044,25 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Sofía Henao</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D48" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>2027-02-15</t>
         </is>
@@ -8088,25 +8094,25 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Alejandro Velasco</t>
         </is>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D50" s="10" t="n">
+      <c r="D50" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>2027-05-26</t>
         </is>
@@ -8138,25 +8144,25 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Daniela Mendoza Pérez</t>
         </is>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D52" s="10" t="n">
+      <c r="D52" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>2027-03-28</t>
         </is>
@@ -8188,25 +8194,25 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>Ximena López</t>
         </is>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D54" s="10" t="n">
+      <c r="D54" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="E54" s="10" t="inlineStr">
+      <c r="E54" s="11" t="inlineStr">
         <is>
           <t>2027-08-29</t>
         </is>
@@ -8238,25 +8244,25 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>Paula Cárdenas</t>
         </is>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D56" s="10" t="n">
+      <c r="D56" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="E56" s="10" t="inlineStr">
+      <c r="E56" s="11" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
@@ -8288,25 +8294,25 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>Camila Gutiérrez</t>
         </is>
       </c>
-      <c r="B58" s="10" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n">
+      <c r="D58" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="E58" s="10" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t>2027-03-12</t>
         </is>
@@ -8338,25 +8344,25 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>Angela Salazar</t>
         </is>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D60" s="10" t="n">
+      <c r="D60" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="E60" s="10" t="inlineStr">
+      <c r="E60" s="11" t="inlineStr">
         <is>
           <t>2027-09-07</t>
         </is>
@@ -8388,25 +8394,25 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>Martín Henao</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D62" s="10" t="n">
+      <c r="D62" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="E62" s="11" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
@@ -8438,25 +8444,25 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>Diego Franco Duque</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D64" s="10" t="n">
+      <c r="D64" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E64" s="11" t="inlineStr">
         <is>
           <t>2026-12-25</t>
         </is>
@@ -8488,25 +8494,25 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>Paula Gutiérrez</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D66" s="10" t="n">
+      <c r="D66" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="E66" s="10" t="inlineStr">
+      <c r="E66" s="11" t="inlineStr">
         <is>
           <t>2026-11-06</t>
         </is>
@@ -8538,25 +8544,25 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>Elena Vargas</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D68" s="10" t="n">
+      <c r="D68" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="E68" s="11" t="inlineStr">
         <is>
           <t>2027-07-29</t>
         </is>
@@ -8588,25 +8594,25 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="inlineStr">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>Francisco Gómez Velasco</t>
         </is>
       </c>
-      <c r="B70" s="10" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D70" s="10" t="n">
+      <c r="D70" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="E70" s="10" t="inlineStr">
+      <c r="E70" s="11" t="inlineStr">
         <is>
           <t>2027-07-20</t>
         </is>
@@ -8638,25 +8644,25 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="inlineStr">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t>Fernanda López Henao</t>
         </is>
       </c>
-      <c r="B72" s="10" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D72" s="10" t="n">
+      <c r="D72" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="E72" s="10" t="inlineStr">
+      <c r="E72" s="11" t="inlineStr">
         <is>
           <t>2027-07-26</t>
         </is>
@@ -8688,25 +8694,25 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="inlineStr">
+      <c r="A74" s="11" t="inlineStr">
         <is>
           <t>Sofía Gutiérrez</t>
         </is>
       </c>
-      <c r="B74" s="10" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C74" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D74" s="10" t="n">
+      <c r="D74" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="E74" s="10" t="inlineStr">
+      <c r="E74" s="11" t="inlineStr">
         <is>
           <t>2026-12-09</t>
         </is>
@@ -8738,25 +8744,25 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="inlineStr">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t>Isabela Acosta</t>
         </is>
       </c>
-      <c r="B76" s="10" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C76" s="10" t="inlineStr">
+      <c r="C76" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D76" s="10" t="n">
+      <c r="D76" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="E76" s="10" t="inlineStr">
+      <c r="E76" s="11" t="inlineStr">
         <is>
           <t>2027-03-18</t>
         </is>
@@ -8788,25 +8794,25 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t>Diego López</t>
         </is>
       </c>
-      <c r="B78" s="10" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C78" s="10" t="inlineStr">
+      <c r="C78" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D78" s="10" t="n">
+      <c r="D78" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="E78" s="10" t="inlineStr">
+      <c r="E78" s="11" t="inlineStr">
         <is>
           <t>2027-06-30</t>
         </is>
@@ -8838,25 +8844,25 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t>Natalia López Mora</t>
         </is>
       </c>
-      <c r="B80" s="10" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="C80" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D80" s="10" t="n">
+      <c r="D80" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="E80" s="10" t="inlineStr">
+      <c r="E80" s="11" t="inlineStr">
         <is>
           <t>2027-01-02</t>
         </is>
@@ -8888,25 +8894,25 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="inlineStr">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t>Daniel Martínez Patiño</t>
         </is>
       </c>
-      <c r="B82" s="10" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n">
+      <c r="D82" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E82" s="10" t="inlineStr">
+      <c r="E82" s="11" t="inlineStr">
         <is>
           <t>2027-05-12</t>
         </is>
@@ -8938,25 +8944,25 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>Santiago Arias</t>
         </is>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C84" s="10" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D84" s="10" t="n">
+      <c r="D84" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E84" s="10" t="inlineStr">
+      <c r="E84" s="11" t="inlineStr">
         <is>
           <t>2027-02-24</t>
         </is>
@@ -8988,25 +8994,25 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>Julián Vargas</t>
         </is>
       </c>
-      <c r="B86" s="10" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C86" s="10" t="inlineStr">
+      <c r="C86" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D86" s="10" t="n">
+      <c r="D86" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E86" s="10" t="inlineStr">
+      <c r="E86" s="11" t="inlineStr">
         <is>
           <t>2027-02-16</t>
         </is>
@@ -9038,25 +9044,25 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="inlineStr">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>Elena Valencia</t>
         </is>
       </c>
-      <c r="B88" s="10" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C88" s="10" t="inlineStr">
+      <c r="C88" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D88" s="10" t="n">
+      <c r="D88" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E88" s="10" t="inlineStr">
+      <c r="E88" s="11" t="inlineStr">
         <is>
           <t>2027-03-07</t>
         </is>
@@ -9088,25 +9094,25 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="inlineStr">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>Laura Ríos</t>
         </is>
       </c>
-      <c r="B90" s="10" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C90" s="10" t="inlineStr">
+      <c r="C90" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D90" s="10" t="n">
+      <c r="D90" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E90" s="10" t="inlineStr">
+      <c r="E90" s="11" t="inlineStr">
         <is>
           <t>2027-07-09</t>
         </is>
@@ -9138,25 +9144,25 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>Felipe Pérez</t>
         </is>
       </c>
-      <c r="B92" s="10" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C92" s="10" t="inlineStr">
+      <c r="C92" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D92" s="10" t="n">
+      <c r="D92" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E92" s="10" t="inlineStr">
+      <c r="E92" s="11" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
@@ -9188,25 +9194,25 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="inlineStr">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t>Carolina Duque Castillo</t>
         </is>
       </c>
-      <c r="B94" s="10" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C94" s="10" t="inlineStr">
+      <c r="C94" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D94" s="10" t="n">
+      <c r="D94" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E94" s="10" t="inlineStr">
+      <c r="E94" s="11" t="inlineStr">
         <is>
           <t>2026-11-12</t>
         </is>
@@ -9238,25 +9244,25 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>Alejandro Castro Martínez</t>
         </is>
       </c>
-      <c r="B96" s="10" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C96" s="10" t="inlineStr">
+      <c r="C96" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D96" s="10" t="n">
+      <c r="D96" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E96" s="10" t="inlineStr">
+      <c r="E96" s="11" t="inlineStr">
         <is>
           <t>2027-10-27</t>
         </is>
@@ -9288,25 +9294,25 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t>Camila Acosta</t>
         </is>
       </c>
-      <c r="B98" s="10" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C98" s="10" t="inlineStr">
+      <c r="C98" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D98" s="10" t="n">
+      <c r="D98" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E98" s="10" t="inlineStr">
+      <c r="E98" s="11" t="inlineStr">
         <is>
           <t>2027-01-05</t>
         </is>
@@ -9338,25 +9344,25 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>Lucía Cardona</t>
         </is>
       </c>
-      <c r="B100" s="10" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C100" s="10" t="inlineStr">
+      <c r="C100" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D100" s="10" t="n">
+      <c r="D100" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E100" s="10" t="inlineStr">
+      <c r="E100" s="11" t="inlineStr">
         <is>
           <t>2027-07-16</t>
         </is>
@@ -9388,25 +9394,25 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>Diego Jiménez Cardona</t>
         </is>
       </c>
-      <c r="B102" s="10" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C102" s="10" t="inlineStr">
+      <c r="C102" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n">
+      <c r="D102" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E102" s="10" t="inlineStr">
+      <c r="E102" s="11" t="inlineStr">
         <is>
           <t>2027-10-28</t>
         </is>
@@ -9438,25 +9444,25 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="inlineStr">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t>Sofía Arias Valencia</t>
         </is>
       </c>
-      <c r="B104" s="10" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C104" s="10" t="inlineStr">
+      <c r="C104" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D104" s="10" t="n">
+      <c r="D104" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E104" s="10" t="inlineStr">
+      <c r="E104" s="11" t="inlineStr">
         <is>
           <t>2027-10-05</t>
         </is>
@@ -9488,25 +9494,25 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="10" t="inlineStr">
+      <c r="A106" s="11" t="inlineStr">
         <is>
           <t>Camila Duque</t>
         </is>
       </c>
-      <c r="B106" s="10" t="inlineStr">
+      <c r="B106" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C106" s="10" t="inlineStr">
+      <c r="C106" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D106" s="10" t="n">
+      <c r="D106" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E106" s="10" t="inlineStr">
+      <c r="E106" s="11" t="inlineStr">
         <is>
           <t>2026-12-10</t>
         </is>
@@ -9538,25 +9544,25 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="10" t="inlineStr">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t>Valentina Londono Pérez</t>
         </is>
       </c>
-      <c r="B108" s="10" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="C108" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D108" s="10" t="n">
+      <c r="D108" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E108" s="10" t="inlineStr">
+      <c r="E108" s="11" t="inlineStr">
         <is>
           <t>2026-11-28</t>
         </is>
@@ -9588,25 +9594,25 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="10" t="inlineStr">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t>Valeria Jiménez</t>
         </is>
       </c>
-      <c r="B110" s="10" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C110" s="10" t="inlineStr">
+      <c r="C110" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D110" s="10" t="n">
+      <c r="D110" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E110" s="10" t="inlineStr">
+      <c r="E110" s="11" t="inlineStr">
         <is>
           <t>2027-01-20</t>
         </is>
@@ -9638,25 +9644,25 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="10" t="inlineStr">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t>Daniel Martínez Martínez</t>
         </is>
       </c>
-      <c r="B112" s="10" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C112" s="10" t="inlineStr">
+      <c r="C112" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D112" s="10" t="n">
+      <c r="D112" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E112" s="10" t="inlineStr">
+      <c r="E112" s="11" t="inlineStr">
         <is>
           <t>2027-08-21</t>
         </is>
@@ -9688,25 +9694,25 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="10" t="inlineStr">
+      <c r="A114" s="11" t="inlineStr">
         <is>
           <t>Victoria Arias</t>
         </is>
       </c>
-      <c r="B114" s="10" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C114" s="10" t="inlineStr">
+      <c r="C114" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D114" s="10" t="n">
+      <c r="D114" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E114" s="10" t="inlineStr">
+      <c r="E114" s="11" t="inlineStr">
         <is>
           <t>2027-08-17</t>
         </is>
@@ -9738,25 +9744,25 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="10" t="inlineStr">
+      <c r="A116" s="11" t="inlineStr">
         <is>
           <t>Daniela Patiño Velasco</t>
         </is>
       </c>
-      <c r="B116" s="10" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C116" s="10" t="inlineStr">
+      <c r="C116" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D116" s="10" t="n">
+      <c r="D116" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E116" s="10" t="inlineStr">
+      <c r="E116" s="11" t="inlineStr">
         <is>
           <t>2027-07-17</t>
         </is>
@@ -9788,25 +9794,25 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="10" t="inlineStr">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t>Andrés Sánchez</t>
         </is>
       </c>
-      <c r="B118" s="10" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C118" s="10" t="inlineStr">
+      <c r="C118" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D118" s="10" t="n">
+      <c r="D118" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E118" s="10" t="inlineStr">
+      <c r="E118" s="11" t="inlineStr">
         <is>
           <t>2026-11-21</t>
         </is>
@@ -9838,25 +9844,25 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="10" t="inlineStr">
+      <c r="A120" s="11" t="inlineStr">
         <is>
           <t>Francisco Muñoz Mora</t>
         </is>
       </c>
-      <c r="B120" s="10" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C120" s="10" t="inlineStr">
+      <c r="C120" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D120" s="10" t="n">
+      <c r="D120" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E120" s="10" t="inlineStr">
+      <c r="E120" s="11" t="inlineStr">
         <is>
           <t>2027-09-22</t>
         </is>
@@ -9888,25 +9894,25 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="10" t="inlineStr">
+      <c r="A122" s="11" t="inlineStr">
         <is>
           <t>Julián Ramírez</t>
         </is>
       </c>
-      <c r="B122" s="10" t="inlineStr">
+      <c r="B122" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C122" s="10" t="inlineStr">
+      <c r="C122" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D122" s="10" t="n">
+      <c r="D122" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E122" s="10" t="inlineStr">
+      <c r="E122" s="11" t="inlineStr">
         <is>
           <t>2027-05-09</t>
         </is>
@@ -9938,25 +9944,25 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="10" t="inlineStr">
+      <c r="A124" s="11" t="inlineStr">
         <is>
           <t>Diego Vargas</t>
         </is>
       </c>
-      <c r="B124" s="10" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="C124" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D124" s="10" t="n">
+      <c r="D124" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E124" s="10" t="inlineStr">
+      <c r="E124" s="11" t="inlineStr">
         <is>
           <t>2027-06-07</t>
         </is>
@@ -9988,25 +9994,25 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="10" t="inlineStr">
+      <c r="A126" s="11" t="inlineStr">
         <is>
           <t>Daniel Cárdenas</t>
         </is>
       </c>
-      <c r="B126" s="10" t="inlineStr">
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C126" s="10" t="inlineStr">
+      <c r="C126" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D126" s="10" t="n">
+      <c r="D126" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E126" s="10" t="inlineStr">
+      <c r="E126" s="11" t="inlineStr">
         <is>
           <t>2027-04-16</t>
         </is>
@@ -10038,25 +10044,25 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="10" t="inlineStr">
+      <c r="A128" s="11" t="inlineStr">
         <is>
           <t>Sofía Franco López</t>
         </is>
       </c>
-      <c r="B128" s="10" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C128" s="10" t="inlineStr">
+      <c r="C128" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D128" s="10" t="n">
+      <c r="D128" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E128" s="10" t="inlineStr">
+      <c r="E128" s="11" t="inlineStr">
         <is>
           <t>2027-10-25</t>
         </is>
@@ -10088,25 +10094,25 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="10" t="inlineStr">
+      <c r="A130" s="11" t="inlineStr">
         <is>
           <t>Sofía Londono</t>
         </is>
       </c>
-      <c r="B130" s="10" t="inlineStr">
+      <c r="B130" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C130" s="10" t="inlineStr">
+      <c r="C130" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D130" s="10" t="n">
+      <c r="D130" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E130" s="10" t="inlineStr">
+      <c r="E130" s="11" t="inlineStr">
         <is>
           <t>2027-09-10</t>
         </is>
@@ -10138,25 +10144,25 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="10" t="inlineStr">
+      <c r="A132" s="11" t="inlineStr">
         <is>
           <t>Angela Henao</t>
         </is>
       </c>
-      <c r="B132" s="10" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C132" s="10" t="inlineStr">
+      <c r="C132" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D132" s="10" t="n">
+      <c r="D132" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E132" s="10" t="inlineStr">
+      <c r="E132" s="11" t="inlineStr">
         <is>
           <t>2026-12-01</t>
         </is>
@@ -10188,25 +10194,25 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="10" t="inlineStr">
+      <c r="A134" s="11" t="inlineStr">
         <is>
           <t>Martín Gutiérrez Ríos</t>
         </is>
       </c>
-      <c r="B134" s="10" t="inlineStr">
+      <c r="B134" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C134" s="10" t="inlineStr">
+      <c r="C134" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D134" s="10" t="n">
+      <c r="D134" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E134" s="10" t="inlineStr">
+      <c r="E134" s="11" t="inlineStr">
         <is>
           <t>2027-09-12</t>
         </is>
@@ -10238,25 +10244,25 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="10" t="inlineStr">
+      <c r="A136" s="11" t="inlineStr">
         <is>
           <t>Victoria Jiménez Valencia</t>
         </is>
       </c>
-      <c r="B136" s="10" t="inlineStr">
+      <c r="B136" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C136" s="10" t="inlineStr">
+      <c r="C136" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D136" s="10" t="n">
+      <c r="D136" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E136" s="10" t="inlineStr">
+      <c r="E136" s="11" t="inlineStr">
         <is>
           <t>2027-04-29</t>
         </is>
@@ -10288,25 +10294,25 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="10" t="inlineStr">
+      <c r="A138" s="11" t="inlineStr">
         <is>
           <t>Isabela Jiménez</t>
         </is>
       </c>
-      <c r="B138" s="10" t="inlineStr">
+      <c r="B138" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C138" s="10" t="inlineStr">
+      <c r="C138" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D138" s="10" t="n">
+      <c r="D138" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E138" s="10" t="inlineStr">
+      <c r="E138" s="11" t="inlineStr">
         <is>
           <t>2027-09-02</t>
         </is>
@@ -10338,25 +10344,25 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="10" t="inlineStr">
+      <c r="A140" s="11" t="inlineStr">
         <is>
           <t>David Pérez Cárdenas</t>
         </is>
       </c>
-      <c r="B140" s="10" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C140" s="10" t="inlineStr">
+      <c r="C140" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D140" s="10" t="n">
+      <c r="D140" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="E140" s="10" t="inlineStr">
+      <c r="E140" s="11" t="inlineStr">
         <is>
           <t>2026-12-01</t>
         </is>
@@ -10388,25 +10394,25 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="10" t="inlineStr">
+      <c r="A142" s="11" t="inlineStr">
         <is>
           <t>Lucía Patiño</t>
         </is>
       </c>
-      <c r="B142" s="10" t="inlineStr">
+      <c r="B142" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C142" s="10" t="inlineStr">
+      <c r="C142" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D142" s="10" t="n">
+      <c r="D142" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E142" s="10" t="inlineStr">
+      <c r="E142" s="11" t="inlineStr">
         <is>
           <t>2027-09-02</t>
         </is>
@@ -10438,25 +10444,25 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="10" t="inlineStr">
+      <c r="A144" s="11" t="inlineStr">
         <is>
           <t>Valentina Salazar</t>
         </is>
       </c>
-      <c r="B144" s="10" t="inlineStr">
+      <c r="B144" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C144" s="10" t="inlineStr">
+      <c r="C144" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D144" s="10" t="n">
+      <c r="D144" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E144" s="10" t="inlineStr">
+      <c r="E144" s="11" t="inlineStr">
         <is>
           <t>2026-11-21</t>
         </is>
@@ -10488,25 +10494,25 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="10" t="inlineStr">
+      <c r="A146" s="11" t="inlineStr">
         <is>
           <t>Mateo Franco Henao</t>
         </is>
       </c>
-      <c r="B146" s="10" t="inlineStr">
+      <c r="B146" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C146" s="10" t="inlineStr">
+      <c r="C146" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D146" s="10" t="n">
+      <c r="D146" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E146" s="10" t="inlineStr">
+      <c r="E146" s="11" t="inlineStr">
         <is>
           <t>2027-08-15</t>
         </is>
@@ -10538,25 +10544,25 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="10" t="inlineStr">
+      <c r="A148" s="11" t="inlineStr">
         <is>
           <t>Victoria Cardona Velasco</t>
         </is>
       </c>
-      <c r="B148" s="10" t="inlineStr">
+      <c r="B148" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C148" s="10" t="inlineStr">
+      <c r="C148" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D148" s="10" t="n">
+      <c r="D148" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E148" s="10" t="inlineStr">
+      <c r="E148" s="11" t="inlineStr">
         <is>
           <t>2027-01-18</t>
         </is>
@@ -10588,25 +10594,25 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="10" t="inlineStr">
+      <c r="A150" s="11" t="inlineStr">
         <is>
           <t>Gabriela Pérez Gómez</t>
         </is>
       </c>
-      <c r="B150" s="10" t="inlineStr">
+      <c r="B150" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C150" s="10" t="inlineStr">
+      <c r="C150" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D150" s="10" t="n">
+      <c r="D150" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E150" s="10" t="inlineStr">
+      <c r="E150" s="11" t="inlineStr">
         <is>
           <t>2027-02-05</t>
         </is>
@@ -10638,25 +10644,25 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="10" t="inlineStr">
+      <c r="A152" s="11" t="inlineStr">
         <is>
           <t>Victoria López</t>
         </is>
       </c>
-      <c r="B152" s="10" t="inlineStr">
+      <c r="B152" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C152" s="10" t="inlineStr">
+      <c r="C152" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D152" s="10" t="n">
+      <c r="D152" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E152" s="10" t="inlineStr">
+      <c r="E152" s="11" t="inlineStr">
         <is>
           <t>2027-06-07</t>
         </is>
@@ -10688,25 +10694,25 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="10" t="inlineStr">
+      <c r="A154" s="11" t="inlineStr">
         <is>
           <t>Natalia Salazar</t>
         </is>
       </c>
-      <c r="B154" s="10" t="inlineStr">
+      <c r="B154" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C154" s="10" t="inlineStr">
+      <c r="C154" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D154" s="10" t="n">
+      <c r="D154" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E154" s="10" t="inlineStr">
+      <c r="E154" s="11" t="inlineStr">
         <is>
           <t>2027-10-28</t>
         </is>
@@ -10738,25 +10744,25 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="10" t="inlineStr">
+      <c r="A156" s="11" t="inlineStr">
         <is>
           <t>Pedro Mora Ramírez</t>
         </is>
       </c>
-      <c r="B156" s="10" t="inlineStr">
+      <c r="B156" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C156" s="10" t="inlineStr">
+      <c r="C156" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D156" s="10" t="n">
+      <c r="D156" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E156" s="10" t="inlineStr">
+      <c r="E156" s="11" t="inlineStr">
         <is>
           <t>2027-05-11</t>
         </is>
@@ -10788,25 +10794,25 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="10" t="inlineStr">
+      <c r="A158" s="11" t="inlineStr">
         <is>
           <t>Daniela López Cardona</t>
         </is>
       </c>
-      <c r="B158" s="10" t="inlineStr">
+      <c r="B158" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C158" s="10" t="inlineStr">
+      <c r="C158" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D158" s="10" t="n">
+      <c r="D158" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E158" s="10" t="inlineStr">
+      <c r="E158" s="11" t="inlineStr">
         <is>
           <t>2026-12-15</t>
         </is>
@@ -10838,25 +10844,25 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="10" t="inlineStr">
+      <c r="A160" s="11" t="inlineStr">
         <is>
           <t>Andrés Velasco</t>
         </is>
       </c>
-      <c r="B160" s="10" t="inlineStr">
+      <c r="B160" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C160" s="10" t="inlineStr">
+      <c r="C160" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D160" s="10" t="n">
+      <c r="D160" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E160" s="10" t="inlineStr">
+      <c r="E160" s="11" t="inlineStr">
         <is>
           <t>2027-08-21</t>
         </is>
@@ -10888,25 +10894,25 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="10" t="inlineStr">
+      <c r="A162" s="11" t="inlineStr">
         <is>
           <t>Valentina Sánchez</t>
         </is>
       </c>
-      <c r="B162" s="10" t="inlineStr">
+      <c r="B162" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C162" s="10" t="inlineStr">
+      <c r="C162" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D162" s="10" t="n">
+      <c r="D162" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E162" s="10" t="inlineStr">
+      <c r="E162" s="11" t="inlineStr">
         <is>
           <t>2027-08-07</t>
         </is>
@@ -10938,25 +10944,25 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="10" t="inlineStr">
+      <c r="A164" s="11" t="inlineStr">
         <is>
           <t>Miguel Patiño Velasco</t>
         </is>
       </c>
-      <c r="B164" s="10" t="inlineStr">
+      <c r="B164" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C164" s="10" t="inlineStr">
+      <c r="C164" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D164" s="10" t="n">
+      <c r="D164" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E164" s="10" t="inlineStr">
+      <c r="E164" s="11" t="inlineStr">
         <is>
           <t>2027-07-30</t>
         </is>
@@ -10988,25 +10994,25 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="10" t="inlineStr">
+      <c r="A166" s="11" t="inlineStr">
         <is>
           <t>Elena Martínez</t>
         </is>
       </c>
-      <c r="B166" s="10" t="inlineStr">
+      <c r="B166" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C166" s="10" t="inlineStr">
+      <c r="C166" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D166" s="10" t="n">
+      <c r="D166" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E166" s="10" t="inlineStr">
+      <c r="E166" s="11" t="inlineStr">
         <is>
           <t>2027-02-19</t>
         </is>
@@ -11038,25 +11044,25 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="10" t="inlineStr">
+      <c r="A168" s="11" t="inlineStr">
         <is>
           <t>Héctor Díaz</t>
         </is>
       </c>
-      <c r="B168" s="10" t="inlineStr">
+      <c r="B168" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C168" s="10" t="inlineStr">
+      <c r="C168" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D168" s="10" t="n">
+      <c r="D168" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E168" s="10" t="inlineStr">
+      <c r="E168" s="11" t="inlineStr">
         <is>
           <t>2027-10-05</t>
         </is>
@@ -11088,25 +11094,25 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="10" t="inlineStr">
+      <c r="A170" s="11" t="inlineStr">
         <is>
           <t>Héctor Vargas</t>
         </is>
       </c>
-      <c r="B170" s="10" t="inlineStr">
+      <c r="B170" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C170" s="10" t="inlineStr">
+      <c r="C170" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D170" s="10" t="n">
+      <c r="D170" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E170" s="10" t="inlineStr">
+      <c r="E170" s="11" t="inlineStr">
         <is>
           <t>2026-12-22</t>
         </is>
@@ -11138,25 +11144,25 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="10" t="inlineStr">
+      <c r="A172" s="11" t="inlineStr">
         <is>
           <t>Sofía Mora Torres</t>
         </is>
       </c>
-      <c r="B172" s="10" t="inlineStr">
+      <c r="B172" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C172" s="10" t="inlineStr">
+      <c r="C172" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D172" s="10" t="n">
+      <c r="D172" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E172" s="10" t="inlineStr">
+      <c r="E172" s="11" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
@@ -11188,25 +11194,25 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="10" t="inlineStr">
+      <c r="A174" s="11" t="inlineStr">
         <is>
           <t>Laura Castillo</t>
         </is>
       </c>
-      <c r="B174" s="10" t="inlineStr">
+      <c r="B174" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C174" s="10" t="inlineStr">
+      <c r="C174" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D174" s="10" t="n">
+      <c r="D174" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E174" s="10" t="inlineStr">
+      <c r="E174" s="11" t="inlineStr">
         <is>
           <t>2027-05-11</t>
         </is>
@@ -11238,25 +11244,25 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="10" t="inlineStr">
+      <c r="A176" s="11" t="inlineStr">
         <is>
           <t>Daniel Muñoz</t>
         </is>
       </c>
-      <c r="B176" s="10" t="inlineStr">
+      <c r="B176" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C176" s="10" t="inlineStr">
+      <c r="C176" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D176" s="10" t="n">
+      <c r="D176" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E176" s="10" t="inlineStr">
+      <c r="E176" s="11" t="inlineStr">
         <is>
           <t>2027-03-03</t>
         </is>
@@ -11288,25 +11294,25 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="10" t="inlineStr">
+      <c r="A178" s="11" t="inlineStr">
         <is>
           <t>Martín Torres Muñoz</t>
         </is>
       </c>
-      <c r="B178" s="10" t="inlineStr">
+      <c r="B178" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C178" s="10" t="inlineStr">
+      <c r="C178" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D178" s="10" t="n">
+      <c r="D178" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E178" s="10" t="inlineStr">
+      <c r="E178" s="11" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
@@ -11338,25 +11344,25 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="10" t="inlineStr">
+      <c r="A180" s="11" t="inlineStr">
         <is>
           <t>Andrea Velasco</t>
         </is>
       </c>
-      <c r="B180" s="10" t="inlineStr">
+      <c r="B180" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C180" s="10" t="inlineStr">
+      <c r="C180" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D180" s="10" t="n">
+      <c r="D180" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E180" s="10" t="inlineStr">
+      <c r="E180" s="11" t="inlineStr">
         <is>
           <t>2027-09-10</t>
         </is>
@@ -11388,25 +11394,25 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="10" t="inlineStr">
+      <c r="A182" s="11" t="inlineStr">
         <is>
           <t>Andrés Torres Gutiérrez</t>
         </is>
       </c>
-      <c r="B182" s="10" t="inlineStr">
+      <c r="B182" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C182" s="10" t="inlineStr">
+      <c r="C182" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D182" s="10" t="n">
+      <c r="D182" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E182" s="10" t="inlineStr">
+      <c r="E182" s="11" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
@@ -11438,25 +11444,25 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="10" t="inlineStr">
+      <c r="A184" s="11" t="inlineStr">
         <is>
           <t>Daniela Cardona</t>
         </is>
       </c>
-      <c r="B184" s="10" t="inlineStr">
+      <c r="B184" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C184" s="10" t="inlineStr">
+      <c r="C184" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D184" s="10" t="n">
+      <c r="D184" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E184" s="10" t="inlineStr">
+      <c r="E184" s="11" t="inlineStr">
         <is>
           <t>2027-10-17</t>
         </is>
@@ -11488,25 +11494,25 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="10" t="inlineStr">
+      <c r="A186" s="11" t="inlineStr">
         <is>
           <t>Sofía Mendoza</t>
         </is>
       </c>
-      <c r="B186" s="10" t="inlineStr">
+      <c r="B186" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C186" s="10" t="inlineStr">
+      <c r="C186" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D186" s="10" t="n">
+      <c r="D186" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E186" s="10" t="inlineStr">
+      <c r="E186" s="11" t="inlineStr">
         <is>
           <t>2027-07-05</t>
         </is>
@@ -11538,25 +11544,25 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="10" t="inlineStr">
+      <c r="A188" s="11" t="inlineStr">
         <is>
           <t>Victoria Pérez Mora</t>
         </is>
       </c>
-      <c r="B188" s="10" t="inlineStr">
+      <c r="B188" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C188" s="10" t="inlineStr">
+      <c r="C188" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D188" s="10" t="n">
+      <c r="D188" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E188" s="10" t="inlineStr">
+      <c r="E188" s="11" t="inlineStr">
         <is>
           <t>2027-04-02</t>
         </is>
@@ -11588,25 +11594,25 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="10" t="inlineStr">
+      <c r="A190" s="11" t="inlineStr">
         <is>
           <t>Felipe García</t>
         </is>
       </c>
-      <c r="B190" s="10" t="inlineStr">
+      <c r="B190" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C190" s="10" t="inlineStr">
+      <c r="C190" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D190" s="10" t="n">
+      <c r="D190" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E190" s="10" t="inlineStr">
+      <c r="E190" s="11" t="inlineStr">
         <is>
           <t>2027-08-16</t>
         </is>
@@ -11638,25 +11644,25 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="10" t="inlineStr">
+      <c r="A192" s="11" t="inlineStr">
         <is>
           <t>Sofía Vargas</t>
         </is>
       </c>
-      <c r="B192" s="10" t="inlineStr">
+      <c r="B192" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C192" s="10" t="inlineStr">
+      <c r="C192" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D192" s="10" t="n">
+      <c r="D192" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E192" s="10" t="inlineStr">
+      <c r="E192" s="11" t="inlineStr">
         <is>
           <t>2027-09-03</t>
         </is>
@@ -11688,25 +11694,25 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="10" t="inlineStr">
+      <c r="A194" s="11" t="inlineStr">
         <is>
           <t>Miguel Patiño</t>
         </is>
       </c>
-      <c r="B194" s="10" t="inlineStr">
+      <c r="B194" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C194" s="10" t="inlineStr">
+      <c r="C194" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D194" s="10" t="n">
+      <c r="D194" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E194" s="10" t="inlineStr">
+      <c r="E194" s="11" t="inlineStr">
         <is>
           <t>2026-12-25</t>
         </is>
@@ -11738,25 +11744,25 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="10" t="inlineStr">
+      <c r="A196" s="11" t="inlineStr">
         <is>
           <t>Carolina Valencia</t>
         </is>
       </c>
-      <c r="B196" s="10" t="inlineStr">
+      <c r="B196" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C196" s="10" t="inlineStr">
+      <c r="C196" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D196" s="10" t="n">
+      <c r="D196" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E196" s="10" t="inlineStr">
+      <c r="E196" s="11" t="inlineStr">
         <is>
           <t>2027-05-01</t>
         </is>
@@ -11788,25 +11794,25 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="10" t="inlineStr">
+      <c r="A198" s="11" t="inlineStr">
         <is>
           <t>Valentina Mora</t>
         </is>
       </c>
-      <c r="B198" s="10" t="inlineStr">
+      <c r="B198" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C198" s="10" t="inlineStr">
+      <c r="C198" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D198" s="10" t="n">
+      <c r="D198" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E198" s="10" t="inlineStr">
+      <c r="E198" s="11" t="inlineStr">
         <is>
           <t>2027-07-16</t>
         </is>
@@ -11838,25 +11844,25 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="10" t="inlineStr">
+      <c r="A200" s="11" t="inlineStr">
         <is>
           <t>Santiago Arias</t>
         </is>
       </c>
-      <c r="B200" s="10" t="inlineStr">
+      <c r="B200" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C200" s="10" t="inlineStr">
+      <c r="C200" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D200" s="10" t="n">
+      <c r="D200" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E200" s="10" t="inlineStr">
+      <c r="E200" s="11" t="inlineStr">
         <is>
           <t>2027-09-18</t>
         </is>
@@ -11888,25 +11894,25 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="10" t="inlineStr">
+      <c r="A202" s="11" t="inlineStr">
         <is>
           <t>Natalia Cárdenas</t>
         </is>
       </c>
-      <c r="B202" s="10" t="inlineStr">
+      <c r="B202" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C202" s="10" t="inlineStr">
+      <c r="C202" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D202" s="10" t="n">
+      <c r="D202" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E202" s="10" t="inlineStr">
+      <c r="E202" s="11" t="inlineStr">
         <is>
           <t>2026-12-11</t>
         </is>
@@ -11938,25 +11944,25 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="10" t="inlineStr">
+      <c r="A204" s="11" t="inlineStr">
         <is>
           <t>Pedro Martínez</t>
         </is>
       </c>
-      <c r="B204" s="10" t="inlineStr">
+      <c r="B204" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C204" s="10" t="inlineStr">
+      <c r="C204" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D204" s="10" t="n">
+      <c r="D204" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E204" s="10" t="inlineStr">
+      <c r="E204" s="11" t="inlineStr">
         <is>
           <t>2027-05-22</t>
         </is>
@@ -11988,25 +11994,25 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="10" t="inlineStr">
+      <c r="A206" s="11" t="inlineStr">
         <is>
           <t>Valeria Gómez Gómez</t>
         </is>
       </c>
-      <c r="B206" s="10" t="inlineStr">
+      <c r="B206" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C206" s="10" t="inlineStr">
+      <c r="C206" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D206" s="10" t="n">
+      <c r="D206" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E206" s="10" t="inlineStr">
+      <c r="E206" s="11" t="inlineStr">
         <is>
           <t>2027-10-14</t>
         </is>
@@ -12038,25 +12044,25 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="10" t="inlineStr">
+      <c r="A208" s="11" t="inlineStr">
         <is>
           <t>Fernanda Duque</t>
         </is>
       </c>
-      <c r="B208" s="10" t="inlineStr">
+      <c r="B208" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C208" s="10" t="inlineStr">
+      <c r="C208" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D208" s="10" t="n">
+      <c r="D208" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E208" s="10" t="inlineStr">
+      <c r="E208" s="11" t="inlineStr">
         <is>
           <t>2027-03-13</t>
         </is>
@@ -12088,25 +12094,25 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="10" t="inlineStr">
+      <c r="A210" s="11" t="inlineStr">
         <is>
           <t>Mateo Henao</t>
         </is>
       </c>
-      <c r="B210" s="10" t="inlineStr">
+      <c r="B210" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C210" s="10" t="inlineStr">
+      <c r="C210" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D210" s="10" t="n">
+      <c r="D210" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E210" s="10" t="inlineStr">
+      <c r="E210" s="11" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
@@ -12138,25 +12144,25 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="10" t="inlineStr">
+      <c r="A212" s="11" t="inlineStr">
         <is>
           <t>Daniel Muñoz</t>
         </is>
       </c>
-      <c r="B212" s="10" t="inlineStr">
+      <c r="B212" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C212" s="10" t="inlineStr">
+      <c r="C212" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D212" s="10" t="n">
+      <c r="D212" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E212" s="10" t="inlineStr">
+      <c r="E212" s="11" t="inlineStr">
         <is>
           <t>2027-09-02</t>
         </is>
@@ -12188,25 +12194,25 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="10" t="inlineStr">
+      <c r="A214" s="11" t="inlineStr">
         <is>
           <t>David Moreno</t>
         </is>
       </c>
-      <c r="B214" s="10" t="inlineStr">
+      <c r="B214" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C214" s="10" t="inlineStr">
+      <c r="C214" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D214" s="10" t="n">
+      <c r="D214" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E214" s="10" t="inlineStr">
+      <c r="E214" s="11" t="inlineStr">
         <is>
           <t>2027-10-06</t>
         </is>
@@ -12238,25 +12244,25 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="10" t="inlineStr">
+      <c r="A216" s="11" t="inlineStr">
         <is>
           <t>Elena Moreno</t>
         </is>
       </c>
-      <c r="B216" s="10" t="inlineStr">
+      <c r="B216" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C216" s="10" t="inlineStr">
+      <c r="C216" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D216" s="10" t="n">
+      <c r="D216" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E216" s="10" t="inlineStr">
+      <c r="E216" s="11" t="inlineStr">
         <is>
           <t>2027-02-07</t>
         </is>
@@ -12288,25 +12294,25 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="10" t="inlineStr">
+      <c r="A218" s="11" t="inlineStr">
         <is>
           <t>Martín Acosta Duque</t>
         </is>
       </c>
-      <c r="B218" s="10" t="inlineStr">
+      <c r="B218" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C218" s="10" t="inlineStr">
+      <c r="C218" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D218" s="10" t="n">
+      <c r="D218" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E218" s="10" t="inlineStr">
+      <c r="E218" s="11" t="inlineStr">
         <is>
           <t>2027-08-20</t>
         </is>
@@ -12338,25 +12344,25 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="10" t="inlineStr">
+      <c r="A220" s="11" t="inlineStr">
         <is>
           <t>Laura Arias</t>
         </is>
       </c>
-      <c r="B220" s="10" t="inlineStr">
+      <c r="B220" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C220" s="10" t="inlineStr">
+      <c r="C220" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D220" s="10" t="n">
+      <c r="D220" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="E220" s="10" t="inlineStr">
+      <c r="E220" s="11" t="inlineStr">
         <is>
           <t>2027-04-23</t>
         </is>
@@ -12388,25 +12394,25 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="10" t="inlineStr">
+      <c r="A222" s="11" t="inlineStr">
         <is>
           <t>Héctor Martínez Duque</t>
         </is>
       </c>
-      <c r="B222" s="10" t="inlineStr">
+      <c r="B222" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C222" s="10" t="inlineStr">
+      <c r="C222" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D222" s="10" t="n">
+      <c r="D222" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E222" s="10" t="inlineStr">
+      <c r="E222" s="11" t="inlineStr">
         <is>
           <t>2026-11-28</t>
         </is>
@@ -12438,25 +12444,25 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="10" t="inlineStr">
+      <c r="A224" s="11" t="inlineStr">
         <is>
           <t>Carlos Vargas</t>
         </is>
       </c>
-      <c r="B224" s="10" t="inlineStr">
+      <c r="B224" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C224" s="10" t="inlineStr">
+      <c r="C224" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D224" s="10" t="n">
+      <c r="D224" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E224" s="10" t="inlineStr">
+      <c r="E224" s="11" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
         </is>
@@ -12488,25 +12494,25 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="10" t="inlineStr">
+      <c r="A226" s="11" t="inlineStr">
         <is>
           <t>Felipe Jimenez</t>
         </is>
       </c>
-      <c r="B226" s="10" t="inlineStr">
+      <c r="B226" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C226" s="10" t="inlineStr">
+      <c r="C226" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D226" s="10" t="n">
+      <c r="D226" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E226" s="10" t="inlineStr">
+      <c r="E226" s="11" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
         </is>
@@ -12538,25 +12544,25 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="10" t="inlineStr">
+      <c r="A228" s="11" t="inlineStr">
         <is>
           <t>Maria Silva</t>
         </is>
       </c>
-      <c r="B228" s="10" t="inlineStr">
+      <c r="B228" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C228" s="10" t="inlineStr">
+      <c r="C228" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D228" s="10" t="n">
+      <c r="D228" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E228" s="10" t="inlineStr">
+      <c r="E228" s="11" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
         </is>
@@ -12588,25 +12594,25 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="10" t="inlineStr">
+      <c r="A230" s="11" t="inlineStr">
         <is>
           <t>Carlos Moreno</t>
         </is>
       </c>
-      <c r="B230" s="10" t="inlineStr">
+      <c r="B230" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C230" s="10" t="inlineStr">
+      <c r="C230" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D230" s="10" t="n">
+      <c r="D230" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E230" s="10" t="inlineStr">
+      <c r="E230" s="11" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
         </is>
@@ -12638,25 +12644,25 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="10" t="inlineStr">
+      <c r="A232" s="11" t="inlineStr">
         <is>
           <t>Sebastian Rodriguez</t>
         </is>
       </c>
-      <c r="B232" s="10" t="inlineStr">
+      <c r="B232" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C232" s="10" t="inlineStr">
+      <c r="C232" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D232" s="10" t="n">
+      <c r="D232" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E232" s="10" t="inlineStr">
+      <c r="E232" s="11" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
         </is>
@@ -12688,25 +12694,25 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="10" t="inlineStr">
+      <c r="A234" s="11" t="inlineStr">
         <is>
           <t>Felipe Rios</t>
         </is>
       </c>
-      <c r="B234" s="10" t="inlineStr">
+      <c r="B234" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C234" s="10" t="inlineStr">
+      <c r="C234" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D234" s="10" t="n">
+      <c r="D234" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E234" s="10" t="inlineStr">
+      <c r="E234" s="11" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
         </is>
@@ -12738,25 +12744,25 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="10" t="inlineStr">
+      <c r="A236" s="11" t="inlineStr">
         <is>
           <t>Juliana Hernandez</t>
         </is>
       </c>
-      <c r="B236" s="10" t="inlineStr">
+      <c r="B236" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C236" s="10" t="inlineStr">
+      <c r="C236" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D236" s="10" t="n">
+      <c r="D236" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E236" s="10" t="inlineStr">
+      <c r="E236" s="11" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
         </is>
@@ -12788,25 +12794,25 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="10" t="inlineStr">
+      <c r="A238" s="11" t="inlineStr">
         <is>
           <t>Natalia Vega</t>
         </is>
       </c>
-      <c r="B238" s="10" t="inlineStr">
+      <c r="B238" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C238" s="10" t="inlineStr">
+      <c r="C238" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D238" s="10" t="n">
+      <c r="D238" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E238" s="10" t="inlineStr">
+      <c r="E238" s="11" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
         </is>
@@ -12838,25 +12844,25 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="10" t="inlineStr">
+      <c r="A240" s="11" t="inlineStr">
         <is>
           <t>Diana Lopez</t>
         </is>
       </c>
-      <c r="B240" s="10" t="inlineStr">
+      <c r="B240" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C240" s="10" t="inlineStr">
+      <c r="C240" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D240" s="10" t="n">
+      <c r="D240" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E240" s="10" t="inlineStr">
+      <c r="E240" s="11" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
         </is>
@@ -12888,25 +12894,25 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="10" t="inlineStr">
+      <c r="A242" s="11" t="inlineStr">
         <is>
           <t>Gabriela Cruz</t>
         </is>
       </c>
-      <c r="B242" s="10" t="inlineStr">
+      <c r="B242" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C242" s="10" t="inlineStr">
+      <c r="C242" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D242" s="10" t="n">
+      <c r="D242" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E242" s="10" t="inlineStr">
+      <c r="E242" s="11" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
         </is>
@@ -12938,25 +12944,25 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="10" t="inlineStr">
+      <c r="A244" s="11" t="inlineStr">
         <is>
           <t>Juan Pena</t>
         </is>
       </c>
-      <c r="B244" s="10" t="inlineStr">
+      <c r="B244" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C244" s="10" t="inlineStr">
+      <c r="C244" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D244" s="10" t="n">
+      <c r="D244" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E244" s="10" t="inlineStr">
+      <c r="E244" s="11" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
         </is>
@@ -12988,25 +12994,25 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="10" t="inlineStr">
+      <c r="A246" s="11" t="inlineStr">
         <is>
           <t>Valentina Moreno</t>
         </is>
       </c>
-      <c r="B246" s="10" t="inlineStr">
+      <c r="B246" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C246" s="10" t="inlineStr">
+      <c r="C246" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D246" s="10" t="n">
+      <c r="D246" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E246" s="10" t="inlineStr">
+      <c r="E246" s="11" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
         </is>
@@ -13038,25 +13044,25 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="10" t="inlineStr">
+      <c r="A248" s="11" t="inlineStr">
         <is>
           <t>Juan Pena</t>
         </is>
       </c>
-      <c r="B248" s="10" t="inlineStr">
+      <c r="B248" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C248" s="10" t="inlineStr">
+      <c r="C248" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D248" s="10" t="n">
+      <c r="D248" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E248" s="10" t="inlineStr">
+      <c r="E248" s="11" t="inlineStr">
         <is>
           <t>2026-10-19 10:00:00</t>
         </is>
@@ -13088,25 +13094,25 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="10" t="inlineStr">
+      <c r="A250" s="11" t="inlineStr">
         <is>
           <t>Elena Martínez</t>
         </is>
       </c>
-      <c r="B250" s="10" t="inlineStr">
+      <c r="B250" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C250" s="10" t="inlineStr">
+      <c r="C250" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D250" s="10" t="n">
+      <c r="D250" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E250" s="10" t="inlineStr">
+      <c r="E250" s="11" t="inlineStr">
         <is>
           <t>2027-08-31</t>
         </is>
@@ -13138,25 +13144,25 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="10" t="inlineStr">
+      <c r="A252" s="11" t="inlineStr">
         <is>
           <t>Carlos Acosta</t>
         </is>
       </c>
-      <c r="B252" s="10" t="inlineStr">
+      <c r="B252" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C252" s="10" t="inlineStr">
+      <c r="C252" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D252" s="10" t="n">
+      <c r="D252" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E252" s="10" t="inlineStr">
+      <c r="E252" s="11" t="inlineStr">
         <is>
           <t>2027-01-13</t>
         </is>
@@ -13188,25 +13194,25 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="10" t="inlineStr">
+      <c r="A254" s="11" t="inlineStr">
         <is>
           <t>Angela Acosta</t>
         </is>
       </c>
-      <c r="B254" s="10" t="inlineStr">
+      <c r="B254" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C254" s="10" t="inlineStr">
+      <c r="C254" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D254" s="10" t="n">
+      <c r="D254" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E254" s="10" t="inlineStr">
+      <c r="E254" s="11" t="inlineStr">
         <is>
           <t>2027-09-21</t>
         </is>
@@ -13238,25 +13244,25 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="10" t="inlineStr">
+      <c r="A256" s="11" t="inlineStr">
         <is>
           <t>Isabela Velasco</t>
         </is>
       </c>
-      <c r="B256" s="10" t="inlineStr">
+      <c r="B256" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C256" s="10" t="inlineStr">
+      <c r="C256" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D256" s="10" t="n">
+      <c r="D256" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E256" s="10" t="inlineStr">
+      <c r="E256" s="11" t="inlineStr">
         <is>
           <t>2027-04-13</t>
         </is>
@@ -13288,25 +13294,25 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="10" t="inlineStr">
+      <c r="A258" s="11" t="inlineStr">
         <is>
           <t>Alejandro Salazar Acosta</t>
         </is>
       </c>
-      <c r="B258" s="10" t="inlineStr">
+      <c r="B258" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C258" s="10" t="inlineStr">
+      <c r="C258" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D258" s="10" t="n">
+      <c r="D258" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E258" s="10" t="inlineStr">
+      <c r="E258" s="11" t="inlineStr">
         <is>
           <t>2027-08-05</t>
         </is>
@@ -13338,25 +13344,25 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="10" t="inlineStr">
+      <c r="A260" s="11" t="inlineStr">
         <is>
           <t>Carlos Franco Arias</t>
         </is>
       </c>
-      <c r="B260" s="10" t="inlineStr">
+      <c r="B260" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C260" s="10" t="inlineStr">
+      <c r="C260" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D260" s="10" t="n">
+      <c r="D260" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E260" s="10" t="inlineStr">
+      <c r="E260" s="11" t="inlineStr">
         <is>
           <t>2026-11-21</t>
         </is>
@@ -13388,25 +13394,25 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="10" t="inlineStr">
+      <c r="A262" s="11" t="inlineStr">
         <is>
           <t>Carlos Ríos</t>
         </is>
       </c>
-      <c r="B262" s="10" t="inlineStr">
+      <c r="B262" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C262" s="10" t="inlineStr">
+      <c r="C262" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D262" s="10" t="n">
+      <c r="D262" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E262" s="10" t="inlineStr">
+      <c r="E262" s="11" t="inlineStr">
         <is>
           <t>2027-06-28</t>
         </is>
@@ -13438,25 +13444,25 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="10" t="inlineStr">
+      <c r="A264" s="11" t="inlineStr">
         <is>
           <t>Mariana Valencia</t>
         </is>
       </c>
-      <c r="B264" s="10" t="inlineStr">
+      <c r="B264" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C264" s="10" t="inlineStr">
+      <c r="C264" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D264" s="10" t="n">
+      <c r="D264" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E264" s="10" t="inlineStr">
+      <c r="E264" s="11" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
@@ -13488,25 +13494,25 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="10" t="inlineStr">
+      <c r="A266" s="11" t="inlineStr">
         <is>
           <t>Carlos Velasco</t>
         </is>
       </c>
-      <c r="B266" s="10" t="inlineStr">
+      <c r="B266" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C266" s="10" t="inlineStr">
+      <c r="C266" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D266" s="10" t="n">
+      <c r="D266" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E266" s="10" t="inlineStr">
+      <c r="E266" s="11" t="inlineStr">
         <is>
           <t>2027-03-26</t>
         </is>
@@ -13538,25 +13544,25 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="10" t="inlineStr">
+      <c r="A268" s="11" t="inlineStr">
         <is>
           <t>Lucía Vargas</t>
         </is>
       </c>
-      <c r="B268" s="10" t="inlineStr">
+      <c r="B268" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C268" s="10" t="inlineStr">
+      <c r="C268" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D268" s="10" t="n">
+      <c r="D268" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E268" s="10" t="inlineStr">
+      <c r="E268" s="11" t="inlineStr">
         <is>
           <t>2027-01-09</t>
         </is>
@@ -13588,25 +13594,25 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="10" t="inlineStr">
+      <c r="A270" s="11" t="inlineStr">
         <is>
           <t>Daniela Díaz García</t>
         </is>
       </c>
-      <c r="B270" s="10" t="inlineStr">
+      <c r="B270" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C270" s="10" t="inlineStr">
+      <c r="C270" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D270" s="10" t="n">
+      <c r="D270" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E270" s="10" t="inlineStr">
+      <c r="E270" s="11" t="inlineStr">
         <is>
           <t>2027-06-22</t>
         </is>
@@ -13638,25 +13644,25 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="10" t="inlineStr">
+      <c r="A272" s="11" t="inlineStr">
         <is>
           <t>Santiago Gómez</t>
         </is>
       </c>
-      <c r="B272" s="10" t="inlineStr">
+      <c r="B272" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C272" s="10" t="inlineStr">
+      <c r="C272" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D272" s="10" t="n">
+      <c r="D272" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E272" s="10" t="inlineStr">
+      <c r="E272" s="11" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
@@ -13688,25 +13694,25 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="10" t="inlineStr">
+      <c r="A274" s="11" t="inlineStr">
         <is>
           <t>Paula Cárdenas</t>
         </is>
       </c>
-      <c r="B274" s="10" t="inlineStr">
+      <c r="B274" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C274" s="10" t="inlineStr">
+      <c r="C274" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D274" s="10" t="n">
+      <c r="D274" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E274" s="10" t="inlineStr">
+      <c r="E274" s="11" t="inlineStr">
         <is>
           <t>2027-02-25</t>
         </is>
@@ -13738,25 +13744,25 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="10" t="inlineStr">
+      <c r="A276" s="11" t="inlineStr">
         <is>
           <t>Carlos Patiño</t>
         </is>
       </c>
-      <c r="B276" s="10" t="inlineStr">
+      <c r="B276" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C276" s="10" t="inlineStr">
+      <c r="C276" s="11" t="inlineStr">
         <is>
           <t>Venta</t>
         </is>
       </c>
-      <c r="D276" s="10" t="n">
+      <c r="D276" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E276" s="10" t="inlineStr">
+      <c r="E276" s="11" t="inlineStr">
         <is>
           <t>2027-06-13</t>
         </is>
@@ -13788,25 +13794,25 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="10" t="inlineStr">
+      <c r="A278" s="11" t="inlineStr">
         <is>
           <t>Angela Martínez Sánchez</t>
         </is>
       </c>
-      <c r="B278" s="10" t="inlineStr">
+      <c r="B278" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C278" s="10" t="inlineStr">
+      <c r="C278" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D278" s="10" t="n">
+      <c r="D278" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E278" s="10" t="inlineStr">
+      <c r="E278" s="11" t="inlineStr">
         <is>
           <t>2027-05-04</t>
         </is>
@@ -13838,25 +13844,25 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="10" t="inlineStr">
+      <c r="A280" s="11" t="inlineStr">
         <is>
           <t>Santiago Gómez</t>
         </is>
       </c>
-      <c r="B280" s="10" t="inlineStr">
+      <c r="B280" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C280" s="10" t="inlineStr">
+      <c r="C280" s="11" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="D280" s="10" t="n">
+      <c r="D280" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E280" s="10" t="inlineStr">
+      <c r="E280" s="11" t="inlineStr">
         <is>
           <t>2027-09-17</t>
         </is>
@@ -13888,25 +13894,25 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="10" t="inlineStr">
+      <c r="A282" s="11" t="inlineStr">
         <is>
           <t>Santiago Duque</t>
         </is>
       </c>
-      <c r="B282" s="10" t="inlineStr">
+      <c r="B282" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C282" s="10" t="inlineStr">
+      <c r="C282" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D282" s="10" t="n">
+      <c r="D282" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E282" s="10" t="inlineStr">
+      <c r="E282" s="11" t="inlineStr">
         <is>
           <t>2027-03-10</t>
         </is>
@@ -13938,25 +13944,25 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="10" t="inlineStr">
+      <c r="A284" s="11" t="inlineStr">
         <is>
           <t>Diego Franco</t>
         </is>
       </c>
-      <c r="B284" s="10" t="inlineStr">
+      <c r="B284" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C284" s="10" t="inlineStr">
+      <c r="C284" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D284" s="10" t="n">
+      <c r="D284" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E284" s="10" t="inlineStr">
+      <c r="E284" s="11" t="inlineStr">
         <is>
           <t>2027-02-18</t>
         </is>
@@ -13988,25 +13994,25 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="10" t="inlineStr">
+      <c r="A286" s="11" t="inlineStr">
         <is>
           <t>Pedro Pérez</t>
         </is>
       </c>
-      <c r="B286" s="10" t="inlineStr">
+      <c r="B286" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C286" s="10" t="inlineStr">
+      <c r="C286" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D286" s="10" t="n">
+      <c r="D286" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E286" s="10" t="inlineStr">
+      <c r="E286" s="11" t="inlineStr">
         <is>
           <t>2027-10-15</t>
         </is>
@@ -14038,25 +14044,25 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="10" t="inlineStr">
+      <c r="A288" s="11" t="inlineStr">
         <is>
           <t>Daniel Franco</t>
         </is>
       </c>
-      <c r="B288" s="10" t="inlineStr">
+      <c r="B288" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C288" s="10" t="inlineStr">
+      <c r="C288" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D288" s="10" t="n">
+      <c r="D288" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E288" s="10" t="inlineStr">
+      <c r="E288" s="11" t="inlineStr">
         <is>
           <t>2027-07-16</t>
         </is>
@@ -14088,25 +14094,25 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="10" t="inlineStr">
+      <c r="A290" s="11" t="inlineStr">
         <is>
           <t>Isabela Valencia</t>
         </is>
       </c>
-      <c r="B290" s="10" t="inlineStr">
+      <c r="B290" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C290" s="10" t="inlineStr">
+      <c r="C290" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D290" s="10" t="n">
+      <c r="D290" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E290" s="10" t="inlineStr">
+      <c r="E290" s="11" t="inlineStr">
         <is>
           <t>2027-04-10</t>
         </is>
@@ -14138,25 +14144,25 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="10" t="inlineStr">
+      <c r="A292" s="11" t="inlineStr">
         <is>
           <t>Santiago Vargas Mendoza</t>
         </is>
       </c>
-      <c r="B292" s="10" t="inlineStr">
+      <c r="B292" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C292" s="10" t="inlineStr">
+      <c r="C292" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D292" s="10" t="n">
+      <c r="D292" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E292" s="10" t="inlineStr">
+      <c r="E292" s="11" t="inlineStr">
         <is>
           <t>2026-11-21</t>
         </is>
@@ -14188,25 +14194,25 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="10" t="inlineStr">
+      <c r="A294" s="11" t="inlineStr">
         <is>
           <t>Felipe García</t>
         </is>
       </c>
-      <c r="B294" s="10" t="inlineStr">
+      <c r="B294" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C294" s="10" t="inlineStr">
+      <c r="C294" s="11" t="inlineStr">
         <is>
           <t>Opción o separación</t>
         </is>
       </c>
-      <c r="D294" s="10" t="n">
+      <c r="D294" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E294" s="10" t="inlineStr">
+      <c r="E294" s="11" t="inlineStr">
         <is>
           <t>2027-04-30</t>
         </is>
@@ -14238,25 +14244,25 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="10" t="inlineStr">
+      <c r="A296" s="11" t="inlineStr">
         <is>
           <t>Carlos Torres Ramírez</t>
         </is>
       </c>
-      <c r="B296" s="10" t="inlineStr">
+      <c r="B296" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C296" s="10" t="inlineStr">
+      <c r="C296" s="11" t="inlineStr">
         <is>
           <t>Oportunidad (SQL)</t>
         </is>
       </c>
-      <c r="D296" s="10" t="n">
+      <c r="D296" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E296" s="10" t="inlineStr">
+      <c r="E296" s="11" t="inlineStr">
         <is>
           <t>2027-01-13</t>
         </is>
@@ -14288,25 +14294,25 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="10" t="inlineStr">
+      <c r="A298" s="11" t="inlineStr">
         <is>
           <t>Natalia Velasco Vargas</t>
         </is>
       </c>
-      <c r="B298" s="10" t="inlineStr">
+      <c r="B298" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C298" s="10" t="inlineStr">
+      <c r="C298" s="11" t="inlineStr">
         <is>
           <t>Lead calificado (MQL)</t>
         </is>
       </c>
-      <c r="D298" s="10" t="n">
+      <c r="D298" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E298" s="10" t="inlineStr">
+      <c r="E298" s="11" t="inlineStr">
         <is>
           <t>2027-04-13</t>
         </is>
@@ -14338,25 +14344,25 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="10" t="inlineStr">
+      <c r="A300" s="11" t="inlineStr">
         <is>
           <t>Francisco Ramírez Henao</t>
         </is>
       </c>
-      <c r="B300" s="10" t="inlineStr">
+      <c r="B300" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C300" s="10" t="inlineStr">
+      <c r="C300" s="11" t="inlineStr">
         <is>
           <t>Reunión o visita</t>
         </is>
       </c>
-      <c r="D300" s="10" t="n">
+      <c r="D300" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="E300" s="10" t="inlineStr">
+      <c r="E300" s="11" t="inlineStr">
         <is>
           <t>2027-04-27</t>
         </is>

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -5869,11 +5869,11 @@
         <v>740</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>2100</v>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Por debajo de la meta (muestra)</t>
+        <v>220</v>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -5869,11 +5869,11 @@
         <v>740</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>220</v>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Cumple</t>
+        <v>2220</v>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Por debajo de la meta (muestra)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fecha del informe: 22/10/2026</t>
+          <t>Fecha del informe: 23/10/2026</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>6 ventas mensuales presupuestadas × 350 M COP</t>
+          <t>6 ventas mensuales presupuestadas × 370 M COP</t>
         </is>
       </c>
     </row>

--- a/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
+++ b/Informe_KPIs_CRM_ibis_Styles_Armenia.xlsx
@@ -5459,13 +5459,13 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>69623.5</v>
+        <v>69997.5</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>397.8</v>
+        <v>397.7</v>
       </c>
     </row>
     <row r="6">
@@ -5491,13 +5491,13 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>1148</v>
+        <v>774</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>382.7</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
